--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8339,7 +8339,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>892000</v>
+        <v>887000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8544,7 +8544,7 @@
         <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>561000</v>
+        <v>556000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8585,7 +8585,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>871000</v>
+        <v>909000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
         <v>1010</v>
       </c>
       <c r="F13" t="n">
-        <v>998000</v>
+        <v>996000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8708,7 +8708,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>664000</v>
+        <v>637000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8790,7 +8790,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>611000</v>
+        <v>612000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>832000</v>
+        <v>800000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8872,7 +8872,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>519000</v>
+        <v>511000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8913,7 +8913,7 @@
         <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>363000</v>
+        <v>372000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8995,7 +8995,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>613000</v>
+        <v>634000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9118,7 +9118,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>411000</v>
+        <v>449000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9159,7 +9159,7 @@
         <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>446000</v>
+        <v>443000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -9200,7 +9200,7 @@
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>586000</v>
+        <v>578000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
         <v>130</v>
       </c>
       <c r="F28" t="n">
-        <v>860000</v>
+        <v>849000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>807000</v>
+        <v>794000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9487,7 +9487,7 @@
         <v>1010</v>
       </c>
       <c r="F33" t="n">
-        <v>632000</v>
+        <v>616000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>665000</v>
+        <v>636000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9692,7 +9692,7 @@
         <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>643000</v>
+        <v>632000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9733,7 +9733,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>901000</v>
+        <v>889000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9856,7 +9856,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>915000</v>
+        <v>900000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9979,7 +9979,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>603000</v>
+        <v>609000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
         <v>150</v>
       </c>
       <c r="F48" t="n">
-        <v>548000</v>
+        <v>560000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10184,7 +10184,7 @@
         <v>160</v>
       </c>
       <c r="F50" t="n">
-        <v>855000</v>
+        <v>862000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -10307,7 +10307,7 @@
         <v>130</v>
       </c>
       <c r="F53" t="n">
-        <v>1009000</v>
+        <v>1000000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>557000</v>
+        <v>566000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10389,7 +10389,7 @@
         <v>140</v>
       </c>
       <c r="F55" t="n">
-        <v>955000</v>
+        <v>943000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -10512,7 +10512,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>718000</v>
+        <v>724000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>373000</v>
+        <v>353000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>1000</v>
       </c>
       <c r="F70" t="n">
-        <v>1043000</v>
+        <v>1059000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -11045,7 +11045,7 @@
         <v>150</v>
       </c>
       <c r="F71" t="n">
-        <v>582000</v>
+        <v>573000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -11127,7 +11127,7 @@
         <v>70</v>
       </c>
       <c r="F73" t="n">
-        <v>459000</v>
+        <v>446000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11168,7 +11168,7 @@
         <v>1000</v>
       </c>
       <c r="F74" t="n">
-        <v>745000</v>
+        <v>761000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11209,7 +11209,7 @@
         <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>691000</v>
+        <v>668000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -11250,7 +11250,7 @@
         <v>130</v>
       </c>
       <c r="F76" t="n">
-        <v>646000</v>
+        <v>656000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>501000</v>
+        <v>513000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11414,7 +11414,7 @@
         <v>110</v>
       </c>
       <c r="F80" t="n">
-        <v>478000</v>
+        <v>482000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -11455,7 +11455,7 @@
         <v>110</v>
       </c>
       <c r="F81" t="n">
-        <v>806000</v>
+        <v>789000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>150</v>
       </c>
       <c r="F83" t="n">
-        <v>477000</v>
+        <v>456000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11578,7 +11578,7 @@
         <v>120</v>
       </c>
       <c r="F84" t="n">
-        <v>643000</v>
+        <v>627000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -11824,7 +11824,7 @@
         <v>70</v>
       </c>
       <c r="F90" t="n">
-        <v>699000</v>
+        <v>684000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11906,7 +11906,7 @@
         <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>449000</v>
+        <v>445000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -12029,7 +12029,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>640000</v>
+        <v>615000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12070,7 +12070,7 @@
         <v>140</v>
       </c>
       <c r="F96" t="n">
-        <v>564000</v>
+        <v>583000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -12111,7 +12111,7 @@
         <v>1000</v>
       </c>
       <c r="F97" t="n">
-        <v>697000</v>
+        <v>685000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -12152,7 +12152,7 @@
         <v>160</v>
       </c>
       <c r="F98" t="n">
-        <v>864000</v>
+        <v>873000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -12398,7 +12398,7 @@
         <v>70</v>
       </c>
       <c r="F104" t="n">
-        <v>592000</v>
+        <v>590000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12480,7 +12480,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>752000</v>
+        <v>774000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12603,7 +12603,7 @@
         <v>160</v>
       </c>
       <c r="F109" t="n">
-        <v>740000</v>
+        <v>743000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -12644,7 +12644,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>447000</v>
+        <v>463000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -12685,7 +12685,7 @@
         <v>130</v>
       </c>
       <c r="F111" t="n">
-        <v>368000</v>
+        <v>385000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -12726,7 +12726,7 @@
         <v>1010</v>
       </c>
       <c r="F112" t="n">
-        <v>484000</v>
+        <v>463000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         <v>1000</v>
       </c>
       <c r="F113" t="n">
-        <v>397000</v>
+        <v>386000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -12808,7 +12808,7 @@
         <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>448000</v>
+        <v>465000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -12890,7 +12890,7 @@
         <v>70</v>
       </c>
       <c r="F116" t="n">
-        <v>555000</v>
+        <v>568000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -12931,7 +12931,7 @@
         <v>1010</v>
       </c>
       <c r="F117" t="n">
-        <v>994000</v>
+        <v>1006000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -12972,7 +12972,7 @@
         <v>90</v>
       </c>
       <c r="F118" t="n">
-        <v>751000</v>
+        <v>756000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>50</v>
       </c>
       <c r="F119" t="n">
-        <v>654000</v>
+        <v>660000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -13177,7 +13177,7 @@
         <v>110</v>
       </c>
       <c r="F123" t="n">
-        <v>468000</v>
+        <v>471000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -13300,7 +13300,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>827000</v>
+        <v>814000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
         <v>130</v>
       </c>
       <c r="F127" t="n">
-        <v>603000</v>
+        <v>583000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13382,7 +13382,7 @@
         <v>160</v>
       </c>
       <c r="F128" t="n">
-        <v>686000</v>
+        <v>658000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -13423,7 +13423,7 @@
         <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>585000</v>
+        <v>591000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13464,7 +13464,7 @@
         <v>90</v>
       </c>
       <c r="F130" t="n">
-        <v>865000</v>
+        <v>846000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -13587,7 +13587,7 @@
         <v>120</v>
       </c>
       <c r="F133" t="n">
-        <v>577000</v>
+        <v>569000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13792,7 +13792,7 @@
         <v>110</v>
       </c>
       <c r="F138" t="n">
-        <v>785000</v>
+        <v>793000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13833,7 +13833,7 @@
         <v>70</v>
       </c>
       <c r="F139" t="n">
-        <v>843000</v>
+        <v>836000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13915,7 +13915,7 @@
         <v>90</v>
       </c>
       <c r="F141" t="n">
-        <v>230000</v>
+        <v>234000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13956,7 +13956,7 @@
         <v>10</v>
       </c>
       <c r="F142" t="n">
-        <v>539000</v>
+        <v>540000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14038,7 +14038,7 @@
         <v>1000</v>
       </c>
       <c r="F144" t="n">
-        <v>390000</v>
+        <v>389000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14079,7 +14079,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>482000</v>
+        <v>485000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14120,7 +14120,7 @@
         <v>1010</v>
       </c>
       <c r="F146" t="n">
-        <v>505000</v>
+        <v>486000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14161,7 +14161,7 @@
         <v>100</v>
       </c>
       <c r="F147" t="n">
-        <v>579000</v>
+        <v>590000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>70</v>
       </c>
       <c r="F148" t="n">
-        <v>961000</v>
+        <v>973000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -14366,7 +14366,7 @@
         <v>20</v>
       </c>
       <c r="F152" t="n">
-        <v>929000</v>
+        <v>955000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14448,7 +14448,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>542000</v>
+        <v>543000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14530,7 +14530,7 @@
         <v>160</v>
       </c>
       <c r="F156" t="n">
-        <v>742000</v>
+        <v>763000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14612,7 +14612,7 @@
         <v>90</v>
       </c>
       <c r="F158" t="n">
-        <v>593000</v>
+        <v>614000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>752000</v>
+        <v>720000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>872000</v>
+        <v>836000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14776,7 +14776,7 @@
         <v>150</v>
       </c>
       <c r="F162" t="n">
-        <v>445000</v>
+        <v>437000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14858,7 +14858,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>365000</v>
+        <v>366000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14899,7 +14899,7 @@
         <v>150</v>
       </c>
       <c r="F165" t="n">
-        <v>612000</v>
+        <v>598000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>722000</v>
+        <v>719000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15104,7 +15104,7 @@
         <v>140</v>
       </c>
       <c r="F170" t="n">
-        <v>508000</v>
+        <v>487000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -15186,7 +15186,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>605000</v>
+        <v>629000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15637,7 +15637,7 @@
         <v>150</v>
       </c>
       <c r="F183" t="n">
-        <v>475000</v>
+        <v>477000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15719,7 +15719,7 @@
         <v>130</v>
       </c>
       <c r="F185" t="n">
-        <v>727000</v>
+        <v>725000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -15760,7 +15760,7 @@
         <v>10</v>
       </c>
       <c r="F186" t="n">
-        <v>252000</v>
+        <v>306000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15883,7 +15883,7 @@
         <v>50</v>
       </c>
       <c r="F189" t="n">
-        <v>1030000</v>
+        <v>942000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -16006,7 +16006,7 @@
         <v>20</v>
       </c>
       <c r="F192" t="n">
-        <v>603000</v>
+        <v>589000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16047,7 +16047,7 @@
         <v>70</v>
       </c>
       <c r="F193" t="n">
-        <v>598000</v>
+        <v>575000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -16129,7 +16129,7 @@
         <v>110</v>
       </c>
       <c r="F195" t="n">
-        <v>268000</v>
+        <v>263000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -16334,7 +16334,7 @@
         <v>130</v>
       </c>
       <c r="F200" t="n">
-        <v>395000</v>
+        <v>406000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -16375,7 +16375,7 @@
         <v>70</v>
       </c>
       <c r="F201" t="n">
-        <v>654000</v>
+        <v>655000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16539,7 +16539,7 @@
         <v>150</v>
       </c>
       <c r="F205" t="n">
-        <v>329000</v>
+        <v>336000</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -16621,7 +16621,7 @@
         <v>20</v>
       </c>
       <c r="F207" t="n">
-        <v>292000</v>
+        <v>329000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -16662,7 +16662,7 @@
         <v>50</v>
       </c>
       <c r="F208" t="n">
-        <v>373000</v>
+        <v>387000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -16703,7 +16703,7 @@
         <v>150</v>
       </c>
       <c r="F209" t="n">
-        <v>463000</v>
+        <v>466000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -17318,7 +17318,7 @@
         <v>1000</v>
       </c>
       <c r="F224" t="n">
-        <v>437000</v>
+        <v>456000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17359,7 +17359,7 @@
         <v>150</v>
       </c>
       <c r="F225" t="n">
-        <v>652000</v>
+        <v>633000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -17482,7 +17482,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>661000</v>
+        <v>655000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17646,7 +17646,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>649000</v>
+        <v>679000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>140</v>
       </c>
       <c r="F235" t="n">
-        <v>396000</v>
+        <v>397000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -17933,7 +17933,7 @@
         <v>150</v>
       </c>
       <c r="F239" t="n">
-        <v>681000</v>
+        <v>679000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -18015,7 +18015,7 @@
         <v>120</v>
       </c>
       <c r="F241" t="n">
-        <v>230000</v>
+        <v>252000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
         <v>50</v>
       </c>
       <c r="F244" t="n">
-        <v>640000</v>
+        <v>664000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -18343,7 +18343,7 @@
         <v>120</v>
       </c>
       <c r="F249" t="n">
-        <v>560000</v>
+        <v>555000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -18425,7 +18425,7 @@
         <v>160</v>
       </c>
       <c r="F251" t="n">
-        <v>342000</v>
+        <v>350000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -19010,7 +19010,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>561000</v>
+        <v>598000</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -19092,7 +19092,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>528000</v>
+        <v>499000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19133,7 +19133,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>682000</v>
+        <v>664000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19215,7 +19215,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>572000</v>
+        <v>579000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19338,7 +19338,7 @@
         <v>140</v>
       </c>
       <c r="F10" t="n">
-        <v>767000</v>
+        <v>700000</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -19461,7 +19461,7 @@
         <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>796000</v>
+        <v>762000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19625,7 +19625,7 @@
         <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>834000</v>
+        <v>791000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19666,7 +19666,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>642000</v>
+        <v>640000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19789,7 +19789,7 @@
         <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>616000</v>
+        <v>595000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19830,7 +19830,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>716000</v>
+        <v>699000</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -19871,7 +19871,7 @@
         <v>1010</v>
       </c>
       <c r="F23" t="n">
-        <v>803000</v>
+        <v>811000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19912,7 +19912,7 @@
         <v>130</v>
       </c>
       <c r="F24" t="n">
-        <v>799000</v>
+        <v>786000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -19953,7 +19953,7 @@
         <v>150</v>
       </c>
       <c r="F25" t="n">
-        <v>805000</v>
+        <v>815000</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -19994,7 +19994,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>618000</v>
+        <v>572000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20035,7 +20035,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>523000</v>
+        <v>510000</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -20076,7 +20076,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>752000</v>
+        <v>746000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20240,7 +20240,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>925000</v>
+        <v>887000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20281,7 +20281,7 @@
         <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>797000</v>
+        <v>805000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20322,7 +20322,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>832000</v>
+        <v>825000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20527,7 +20527,7 @@
         <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>709000</v>
+        <v>691000</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -20568,7 +20568,7 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>656000</v>
+        <v>629000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20732,7 +20732,7 @@
         <v>130</v>
       </c>
       <c r="F44" t="n">
-        <v>394000</v>
+        <v>386000</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -20773,7 +20773,7 @@
         <v>130</v>
       </c>
       <c r="F45" t="n">
-        <v>788000</v>
+        <v>756000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20814,7 +20814,7 @@
         <v>70</v>
       </c>
       <c r="F46" t="n">
-        <v>741000</v>
+        <v>715000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20855,7 +20855,7 @@
         <v>1000</v>
       </c>
       <c r="F47" t="n">
-        <v>502000</v>
+        <v>480000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20896,7 +20896,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>638000</v>
+        <v>632000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -20937,7 +20937,7 @@
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>576000</v>
+        <v>562000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21060,7 +21060,7 @@
         <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>763000</v>
+        <v>753000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21224,7 +21224,7 @@
         <v>150</v>
       </c>
       <c r="F56" t="n">
-        <v>752000</v>
+        <v>781000</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -21265,7 +21265,7 @@
         <v>160</v>
       </c>
       <c r="F57" t="n">
-        <v>635000</v>
+        <v>671000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21470,7 +21470,7 @@
         <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>477000</v>
+        <v>495000</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -21593,7 +21593,7 @@
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>645000</v>
+        <v>639000</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -21716,7 +21716,7 @@
         <v>140</v>
       </c>
       <c r="F68" t="n">
-        <v>445000</v>
+        <v>440000</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -21839,7 +21839,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="n">
-        <v>560000</v>
+        <v>566000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21880,7 +21880,7 @@
         <v>90</v>
       </c>
       <c r="F72" t="n">
-        <v>874000</v>
+        <v>864000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -22044,7 +22044,7 @@
         <v>140</v>
       </c>
       <c r="F76" t="n">
-        <v>549000</v>
+        <v>580000</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -22167,7 +22167,7 @@
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>495000</v>
+        <v>498000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22249,7 +22249,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="n">
-        <v>560000</v>
+        <v>557000</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -22372,7 +22372,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="n">
-        <v>610000</v>
+        <v>581000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22413,7 +22413,7 @@
         <v>120</v>
       </c>
       <c r="F85" t="n">
-        <v>616000</v>
+        <v>618000</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -22454,7 +22454,7 @@
         <v>1010</v>
       </c>
       <c r="F86" t="n">
-        <v>711000</v>
+        <v>742000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22495,7 +22495,7 @@
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>446000</v>
+        <v>454000</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -22536,7 +22536,7 @@
         <v>20</v>
       </c>
       <c r="F88" t="n">
-        <v>848000</v>
+        <v>856000</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -22577,7 +22577,7 @@
         <v>140</v>
       </c>
       <c r="F89" t="n">
-        <v>607000</v>
+        <v>589000</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -22618,7 +22618,7 @@
         <v>100</v>
       </c>
       <c r="F90" t="n">
-        <v>693000</v>
+        <v>684000</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -22700,7 +22700,7 @@
         <v>160</v>
       </c>
       <c r="F92" t="n">
-        <v>589000</v>
+        <v>574000</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -22782,7 +22782,7 @@
         <v>130</v>
       </c>
       <c r="F94" t="n">
-        <v>475000</v>
+        <v>525000</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -22987,7 +22987,7 @@
         <v>110</v>
       </c>
       <c r="F99" t="n">
-        <v>494000</v>
+        <v>466000</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -23110,7 +23110,7 @@
         <v>90</v>
       </c>
       <c r="F102" t="n">
-        <v>691000</v>
+        <v>688000</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -23151,7 +23151,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>616000</v>
+        <v>624000</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -23192,7 +23192,7 @@
         <v>150</v>
       </c>
       <c r="F104" t="n">
-        <v>706000</v>
+        <v>687000</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -23233,7 +23233,7 @@
         <v>160</v>
       </c>
       <c r="F105" t="n">
-        <v>485000</v>
+        <v>450000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23315,7 +23315,7 @@
         <v>150</v>
       </c>
       <c r="F107" t="n">
-        <v>795000</v>
+        <v>793000</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -23356,7 +23356,7 @@
         <v>140</v>
       </c>
       <c r="F108" t="n">
-        <v>559000</v>
+        <v>563000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23520,7 +23520,7 @@
         <v>1000</v>
       </c>
       <c r="F112" t="n">
-        <v>447000</v>
+        <v>466000</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -23684,7 +23684,7 @@
         <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>559000</v>
+        <v>569000</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -23725,7 +23725,7 @@
         <v>160</v>
       </c>
       <c r="F117" t="n">
-        <v>489000</v>
+        <v>463000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23807,7 +23807,7 @@
         <v>1010</v>
       </c>
       <c r="F119" t="n">
-        <v>601000</v>
+        <v>624000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23930,7 +23930,7 @@
         <v>110</v>
       </c>
       <c r="F122" t="n">
-        <v>716000</v>
+        <v>753000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -23971,7 +23971,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>635000</v>
+        <v>632000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24012,7 +24012,7 @@
         <v>140</v>
       </c>
       <c r="F124" t="n">
-        <v>725000</v>
+        <v>707000</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -24094,7 +24094,7 @@
         <v>110</v>
       </c>
       <c r="F126" t="n">
-        <v>532000</v>
+        <v>517000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24135,7 +24135,7 @@
         <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>869000</v>
+        <v>908000</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -24217,7 +24217,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>506000</v>
+        <v>503000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24299,7 +24299,7 @@
         <v>90</v>
       </c>
       <c r="F131" t="n">
-        <v>570000</v>
+        <v>594000</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -24627,7 +24627,7 @@
         <v>120</v>
       </c>
       <c r="F139" t="n">
-        <v>368000</v>
+        <v>363000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24668,7 +24668,7 @@
         <v>110</v>
       </c>
       <c r="F140" t="n">
-        <v>671000</v>
+        <v>661000</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -24791,7 +24791,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>870000</v>
+        <v>876000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24873,7 +24873,7 @@
         <v>50</v>
       </c>
       <c r="F145" t="n">
-        <v>509000</v>
+        <v>468000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -24914,7 +24914,7 @@
         <v>140</v>
       </c>
       <c r="F146" t="n">
-        <v>444000</v>
+        <v>433000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25078,7 +25078,7 @@
         <v>160</v>
       </c>
       <c r="F150" t="n">
-        <v>834000</v>
+        <v>863000</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -25119,7 +25119,7 @@
         <v>10</v>
       </c>
       <c r="F151" t="n">
-        <v>509000</v>
+        <v>506000</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -25201,7 +25201,7 @@
         <v>90</v>
       </c>
       <c r="F153" t="n">
-        <v>513000</v>
+        <v>531000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25365,7 +25365,7 @@
         <v>70</v>
       </c>
       <c r="F157" t="n">
-        <v>575000</v>
+        <v>566000</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -25529,7 +25529,7 @@
         <v>160</v>
       </c>
       <c r="F161" t="n">
-        <v>541000</v>
+        <v>597000</v>
       </c>
       <c r="G161" t="n">
         <v>1</v>
@@ -25570,7 +25570,7 @@
         <v>160</v>
       </c>
       <c r="F162" t="n">
-        <v>552000</v>
+        <v>551000</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
@@ -25734,7 +25734,7 @@
         <v>140</v>
       </c>
       <c r="F166" t="n">
-        <v>414000</v>
+        <v>413000</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
@@ -25775,7 +25775,7 @@
         <v>20</v>
       </c>
       <c r="F167" t="n">
-        <v>582000</v>
+        <v>552000</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -25816,7 +25816,7 @@
         <v>1010</v>
       </c>
       <c r="F168" t="n">
-        <v>491000</v>
+        <v>497000</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
@@ -25980,7 +25980,7 @@
         <v>50</v>
       </c>
       <c r="F172" t="n">
-        <v>692000</v>
+        <v>723000</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
@@ -26021,7 +26021,7 @@
         <v>50</v>
       </c>
       <c r="F173" t="n">
-        <v>619000</v>
+        <v>616000</v>
       </c>
       <c r="G173" t="n">
         <v>1</v>
@@ -26144,7 +26144,7 @@
         <v>70</v>
       </c>
       <c r="F176" t="n">
-        <v>627000</v>
+        <v>630000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26226,7 +26226,7 @@
         <v>10</v>
       </c>
       <c r="F178" t="n">
-        <v>706000</v>
+        <v>704000</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
@@ -26267,7 +26267,7 @@
         <v>10</v>
       </c>
       <c r="F179" t="n">
-        <v>571000</v>
+        <v>599000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26349,7 +26349,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>639000</v>
+        <v>669000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26390,7 +26390,7 @@
         <v>120</v>
       </c>
       <c r="F182" t="n">
-        <v>589000</v>
+        <v>624000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26677,7 +26677,7 @@
         <v>90</v>
       </c>
       <c r="F189" t="n">
-        <v>522000</v>
+        <v>506000</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
@@ -26759,7 +26759,7 @@
         <v>140</v>
       </c>
       <c r="F191" t="n">
-        <v>882000</v>
+        <v>858000</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -26841,7 +26841,7 @@
         <v>130</v>
       </c>
       <c r="F193" t="n">
-        <v>516000</v>
+        <v>541000</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -26964,7 +26964,7 @@
         <v>10</v>
       </c>
       <c r="F196" t="n">
-        <v>678000</v>
+        <v>681000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27087,7 +27087,7 @@
         <v>1010</v>
       </c>
       <c r="F199" t="n">
-        <v>655000</v>
+        <v>657000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27251,7 +27251,7 @@
         <v>140</v>
       </c>
       <c r="F203" t="n">
-        <v>488000</v>
+        <v>499000</v>
       </c>
       <c r="G203" t="n">
         <v>1</v>
@@ -27374,7 +27374,7 @@
         <v>130</v>
       </c>
       <c r="F206" t="n">
-        <v>849000</v>
+        <v>853000</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -27456,7 +27456,7 @@
         <v>70</v>
       </c>
       <c r="F208" t="n">
-        <v>339000</v>
+        <v>351000</v>
       </c>
       <c r="G208" t="n">
         <v>1</v>
@@ -27497,7 +27497,7 @@
         <v>90</v>
       </c>
       <c r="F209" t="n">
-        <v>372000</v>
+        <v>380000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27579,7 +27579,7 @@
         <v>10</v>
       </c>
       <c r="F211" t="n">
-        <v>455000</v>
+        <v>446000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27620,7 +27620,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>442000</v>
+        <v>460000</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -27661,7 +27661,7 @@
         <v>110</v>
       </c>
       <c r="F213" t="n">
-        <v>291000</v>
+        <v>302000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27702,7 +27702,7 @@
         <v>120</v>
       </c>
       <c r="F214" t="n">
-        <v>280000</v>
+        <v>290000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -28030,7 +28030,7 @@
         <v>120</v>
       </c>
       <c r="F222" t="n">
-        <v>523000</v>
+        <v>526000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28112,7 +28112,7 @@
         <v>130</v>
       </c>
       <c r="F224" t="n">
-        <v>555000</v>
+        <v>549000</v>
       </c>
       <c r="G224" t="n">
         <v>1</v>
@@ -28153,7 +28153,7 @@
         <v>120</v>
       </c>
       <c r="F225" t="n">
-        <v>618000</v>
+        <v>589000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28358,7 +28358,7 @@
         <v>100</v>
       </c>
       <c r="F230" t="n">
-        <v>380000</v>
+        <v>357000</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -28440,7 +28440,7 @@
         <v>1000</v>
       </c>
       <c r="F232" t="n">
-        <v>603000</v>
+        <v>559000</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
@@ -28481,7 +28481,7 @@
         <v>100</v>
       </c>
       <c r="F233" t="n">
-        <v>1043000</v>
+        <v>1049000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28522,7 +28522,7 @@
         <v>100</v>
       </c>
       <c r="F234" t="n">
-        <v>407000</v>
+        <v>399000</v>
       </c>
       <c r="G234" t="n">
         <v>1</v>
@@ -28645,7 +28645,7 @@
         <v>90</v>
       </c>
       <c r="F237" t="n">
-        <v>618000</v>
+        <v>632000</v>
       </c>
       <c r="G237" t="n">
         <v>1</v>
@@ -28686,7 +28686,7 @@
         <v>1000</v>
       </c>
       <c r="F238" t="n">
-        <v>445000</v>
+        <v>444000</v>
       </c>
       <c r="G238" t="n">
         <v>1</v>
@@ -28727,7 +28727,7 @@
         <v>130</v>
       </c>
       <c r="F239" t="n">
-        <v>313000</v>
+        <v>326000</v>
       </c>
       <c r="G239" t="n">
         <v>1</v>
@@ -28768,7 +28768,7 @@
         <v>130</v>
       </c>
       <c r="F240" t="n">
-        <v>241000</v>
+        <v>262000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28809,7 +28809,7 @@
         <v>160</v>
       </c>
       <c r="F241" t="n">
-        <v>488000</v>
+        <v>515000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28891,7 +28891,7 @@
         <v>100</v>
       </c>
       <c r="F243" t="n">
-        <v>728000</v>
+        <v>685000</v>
       </c>
       <c r="G243" t="n">
         <v>1</v>
@@ -28932,7 +28932,7 @@
         <v>90</v>
       </c>
       <c r="F244" t="n">
-        <v>249000</v>
+        <v>264000</v>
       </c>
       <c r="G244" t="n">
         <v>1</v>
@@ -29424,7 +29424,7 @@
         <v>140</v>
       </c>
       <c r="F256" t="n">
-        <v>734000</v>
+        <v>705000</v>
       </c>
       <c r="G256" t="n">
         <v>1</v>
@@ -29547,7 +29547,7 @@
         <v>130</v>
       </c>
       <c r="F259" t="n">
-        <v>801000</v>
+        <v>813000</v>
       </c>
       <c r="G259" t="n">
         <v>1</v>
@@ -29588,7 +29588,7 @@
         <v>110</v>
       </c>
       <c r="F260" t="n">
-        <v>522000</v>
+        <v>496000</v>
       </c>
       <c r="G260" t="n">
         <v>1</v>
@@ -29629,7 +29629,7 @@
         <v>50</v>
       </c>
       <c r="F261" t="n">
-        <v>592000</v>
+        <v>571000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29711,7 +29711,7 @@
         <v>1010</v>
       </c>
       <c r="F263" t="n">
-        <v>725000</v>
+        <v>742000</v>
       </c>
       <c r="G263" t="n">
         <v>1</v>
@@ -29834,7 +29834,7 @@
         <v>20</v>
       </c>
       <c r="F266" t="n">
-        <v>658000</v>
+        <v>686000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -30162,7 +30162,7 @@
         <v>110</v>
       </c>
       <c r="F274" t="n">
-        <v>550000</v>
+        <v>552000</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
@@ -30203,7 +30203,7 @@
         <v>120</v>
       </c>
       <c r="F275" t="n">
-        <v>268000</v>
+        <v>326000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30490,7 +30490,7 @@
         <v>150</v>
       </c>
       <c r="F282" t="n">
-        <v>430000</v>
+        <v>439000</v>
       </c>
       <c r="G282" t="n">
         <v>1</v>
@@ -30859,7 +30859,7 @@
         <v>50</v>
       </c>
       <c r="F291" t="n">
-        <v>451000</v>
+        <v>449000</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -30900,7 +30900,7 @@
         <v>1000</v>
       </c>
       <c r="F292" t="n">
-        <v>525000</v>
+        <v>524000</v>
       </c>
       <c r="G292" t="n">
         <v>1</v>
@@ -30941,7 +30941,7 @@
         <v>1000</v>
       </c>
       <c r="F293" t="n">
-        <v>406000</v>
+        <v>392000</v>
       </c>
       <c r="G293" t="n">
         <v>1</v>
@@ -31064,7 +31064,7 @@
         <v>140</v>
       </c>
       <c r="F296" t="n">
-        <v>424000</v>
+        <v>449000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31187,7 +31187,7 @@
         <v>50</v>
       </c>
       <c r="F299" t="n">
-        <v>249000</v>
+        <v>265000</v>
       </c>
       <c r="G299" t="n">
         <v>1</v>
@@ -31228,7 +31228,7 @@
         <v>130</v>
       </c>
       <c r="F300" t="n">
-        <v>408000</v>
+        <v>391000</v>
       </c>
       <c r="G300" t="n">
         <v>1</v>
@@ -31433,7 +31433,7 @@
         <v>150</v>
       </c>
       <c r="F305" t="n">
-        <v>421000</v>
+        <v>457000</v>
       </c>
       <c r="G305" t="n">
         <v>1</v>
@@ -31474,7 +31474,7 @@
         <v>100</v>
       </c>
       <c r="F306" t="n">
-        <v>510000</v>
+        <v>505000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31597,7 +31597,7 @@
         <v>1010</v>
       </c>
       <c r="F309" t="n">
-        <v>587000</v>
+        <v>613000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31638,7 +31638,7 @@
         <v>110</v>
       </c>
       <c r="F310" t="n">
-        <v>434000</v>
+        <v>410000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -32499,7 +32499,7 @@
         <v>20</v>
       </c>
       <c r="F331" t="n">
-        <v>402000</v>
+        <v>424000</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -32581,7 +32581,7 @@
         <v>140</v>
       </c>
       <c r="F333" t="n">
-        <v>445000</v>
+        <v>415000</v>
       </c>
       <c r="G333" t="n">
         <v>1</v>
@@ -33073,7 +33073,7 @@
         <v>50</v>
       </c>
       <c r="F345" t="n">
-        <v>625000</v>
+        <v>614000</v>
       </c>
       <c r="G345" t="n">
         <v>1</v>
@@ -33371,7 +33371,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>1003000</v>
+        <v>986000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33494,7 +33494,7 @@
         <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>702000</v>
+        <v>667000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33576,7 +33576,7 @@
         <v>130</v>
       </c>
       <c r="F11" t="n">
-        <v>739000</v>
+        <v>741000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -33617,7 +33617,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>843000</v>
+        <v>829000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -33740,7 +33740,7 @@
         <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>1001000</v>
+        <v>989000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -33863,7 +33863,7 @@
         <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>1068000</v>
+        <v>1073000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -33945,7 +33945,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1087000</v>
+        <v>1108000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -33986,7 +33986,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1114000</v>
+        <v>1161000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34109,7 +34109,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>807000</v>
+        <v>801000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -34150,7 +34150,7 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>654000</v>
+        <v>662000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -34191,7 +34191,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>644000</v>
+        <v>635000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -34232,7 +34232,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>971000</v>
+        <v>980000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34314,7 +34314,7 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>760000</v>
+        <v>723000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34355,7 +34355,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>804000</v>
+        <v>852000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34396,7 +34396,7 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>955000</v>
+        <v>966000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -34519,7 +34519,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>793000</v>
+        <v>779000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34642,7 +34642,7 @@
         <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>832000</v>
+        <v>843000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34888,7 +34888,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>887000</v>
+        <v>875000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -34929,7 +34929,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>647000</v>
+        <v>659000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -35011,7 +35011,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>536000</v>
+        <v>540000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35052,7 +35052,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>864000</v>
+        <v>863000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35175,7 +35175,7 @@
         <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>657000</v>
+        <v>685000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -35257,7 +35257,7 @@
         <v>110</v>
       </c>
       <c r="F52" t="n">
-        <v>1010000</v>
+        <v>987000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -35298,7 +35298,7 @@
         <v>160</v>
       </c>
       <c r="F53" t="n">
-        <v>652000</v>
+        <v>634000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -35339,7 +35339,7 @@
         <v>70</v>
       </c>
       <c r="F54" t="n">
-        <v>1149000</v>
+        <v>1127000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -35503,7 +35503,7 @@
         <v>140</v>
       </c>
       <c r="F58" t="n">
-        <v>957000</v>
+        <v>980000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35667,7 +35667,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>967000</v>
+        <v>995000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -35708,7 +35708,7 @@
         <v>1000</v>
       </c>
       <c r="F63" t="n">
-        <v>891000</v>
+        <v>893000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -35790,7 +35790,7 @@
         <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>570000</v>
+        <v>550000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -35954,7 +35954,7 @@
         <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>293000</v>
+        <v>304000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>790000</v>
+        <v>747000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36077,7 +36077,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>895000</v>
+        <v>898000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36200,7 +36200,7 @@
         <v>1000</v>
       </c>
       <c r="F75" t="n">
-        <v>616000</v>
+        <v>596000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -36282,7 +36282,7 @@
         <v>1010</v>
       </c>
       <c r="F77" t="n">
-        <v>594000</v>
+        <v>574000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
         <v>150</v>
       </c>
       <c r="F78" t="n">
-        <v>230000</v>
+        <v>259000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -36364,7 +36364,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>378000</v>
+        <v>410000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -36528,7 +36528,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>230000</v>
+        <v>277000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36692,7 +36692,7 @@
         <v>160</v>
       </c>
       <c r="F87" t="n">
-        <v>660000</v>
+        <v>634000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -36733,7 +36733,7 @@
         <v>150</v>
       </c>
       <c r="F88" t="n">
-        <v>502000</v>
+        <v>485000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -36856,7 +36856,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>463000</v>
+        <v>470000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -36938,7 +36938,7 @@
         <v>20</v>
       </c>
       <c r="F93" t="n">
-        <v>398000</v>
+        <v>420000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37184,7 +37184,7 @@
         <v>1010</v>
       </c>
       <c r="F99" t="n">
-        <v>924000</v>
+        <v>932000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37225,7 +37225,7 @@
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>684000</v>
+        <v>674000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -37307,7 +37307,7 @@
         <v>150</v>
       </c>
       <c r="F102" t="n">
-        <v>783000</v>
+        <v>761000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -37348,7 +37348,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>867000</v>
+        <v>903000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37430,7 +37430,7 @@
         <v>70</v>
       </c>
       <c r="F105" t="n">
-        <v>419000</v>
+        <v>421000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -37512,7 +37512,7 @@
         <v>50</v>
       </c>
       <c r="F107" t="n">
-        <v>638000</v>
+        <v>665000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -37553,7 +37553,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>595000</v>
+        <v>621000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -37676,7 +37676,7 @@
         <v>70</v>
       </c>
       <c r="F111" t="n">
-        <v>720000</v>
+        <v>727000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -37799,7 +37799,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>459000</v>
+        <v>472000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -37922,7 +37922,7 @@
         <v>50</v>
       </c>
       <c r="F117" t="n">
-        <v>388000</v>
+        <v>423000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -38127,7 +38127,7 @@
         <v>1010</v>
       </c>
       <c r="F122" t="n">
-        <v>357000</v>
+        <v>350000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -38250,7 +38250,7 @@
         <v>90</v>
       </c>
       <c r="F125" t="n">
-        <v>656000</v>
+        <v>666000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -38291,7 +38291,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="n">
-        <v>746000</v>
+        <v>708000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38537,7 +38537,7 @@
         <v>1000</v>
       </c>
       <c r="F132" t="n">
-        <v>291000</v>
+        <v>333000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38660,7 +38660,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="n">
-        <v>579000</v>
+        <v>585000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -38742,7 +38742,7 @@
         <v>140</v>
       </c>
       <c r="F137" t="n">
-        <v>230000</v>
+        <v>238000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -38865,7 +38865,7 @@
         <v>150</v>
       </c>
       <c r="F140" t="n">
-        <v>530000</v>
+        <v>488000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -38988,7 +38988,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>230000</v>
+        <v>253000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -39696,7 +39696,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>1014000</v>
+        <v>1030000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39778,7 +39778,7 @@
         <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>1032000</v>
+        <v>997000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -39819,7 +39819,7 @@
         <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>521000</v>
+        <v>509000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -39942,7 +39942,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>603000</v>
+        <v>597000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -40065,7 +40065,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>750000</v>
+        <v>759000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40311,7 +40311,7 @@
         <v>140</v>
       </c>
       <c r="F19" t="n">
-        <v>881000</v>
+        <v>853000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40352,7 +40352,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>636000</v>
+        <v>642000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -40393,7 +40393,7 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>952000</v>
+        <v>924000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -40434,7 +40434,7 @@
         <v>1010</v>
       </c>
       <c r="F22" t="n">
-        <v>681000</v>
+        <v>717000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40516,7 +40516,7 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>570000</v>
+        <v>561000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -40721,7 +40721,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>679000</v>
+        <v>693000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40762,7 +40762,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>790000</v>
+        <v>815000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -40844,7 +40844,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>438000</v>
+        <v>474000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -41377,7 +41377,7 @@
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>230000</v>
+        <v>238000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -41500,7 +41500,7 @@
         <v>120</v>
       </c>
       <c r="F48" t="n">
-        <v>328000</v>
+        <v>346000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2605" uniqueCount="2605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="2607">
   <si>
     <t xml:space="preserve">first_name</t>
   </si>
@@ -7830,6 +7830,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://fantasy.afl.com.au/assets/media/players/afl/1039499_450.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fantasy.afl.com.au/assets/media/players/afl/1048567_450.webp</t>
   </si>
 </sst>
 </file>
@@ -41606,6 +41612,47 @@
         <v>2463</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>937</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D51" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F51" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>2606</v>
+      </c>
+      <c r="L51" t="s">
+        <v>2462</v>
+      </c>
+      <c r="M51" t="s">
+        <v>2463</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8345,7 +8345,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>887000</v>
+        <v>899000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>753000</v>
+        <v>751000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>580000</v>
+        <v>566000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>909000</v>
+        <v>935000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>1010</v>
       </c>
       <c r="F13" t="n">
-        <v>996000</v>
+        <v>976000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>637000</v>
+        <v>624000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>465000</v>
+        <v>452000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>612000</v>
+        <v>597000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>800000</v>
+        <v>834000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>511000</v>
+        <v>506000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>668000</v>
+        <v>659000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>634000</v>
+        <v>645000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>872000</v>
+        <v>816000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9165,7 +9165,7 @@
         <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>443000</v>
+        <v>442000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -9206,7 +9206,7 @@
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>578000</v>
+        <v>575000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>130</v>
       </c>
       <c r="F28" t="n">
-        <v>849000</v>
+        <v>867000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>80</v>
       </c>
       <c r="F29" t="n">
-        <v>895000</v>
+        <v>892000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>861000</v>
+        <v>847000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>849000</v>
+        <v>864000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>1010</v>
       </c>
       <c r="F33" t="n">
-        <v>616000</v>
+        <v>587000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>636000</v>
+        <v>611000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
         <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>337000</v>
+        <v>351000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>427000</v>
+        <v>381000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>632000</v>
+        <v>592000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>889000</v>
+        <v>880000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>488000</v>
+        <v>486000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>900000</v>
+        <v>886000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>609000</v>
+        <v>613000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>701000</v>
+        <v>673000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>783000</v>
+        <v>745000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
         <v>130</v>
       </c>
       <c r="F53" t="n">
-        <v>1000000</v>
+        <v>910000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10395,7 +10395,7 @@
         <v>140</v>
       </c>
       <c r="F55" t="n">
-        <v>943000</v>
+        <v>935000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         <v>60</v>
       </c>
       <c r="F57" t="n">
-        <v>541000</v>
+        <v>524000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>790000</v>
+        <v>752000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>781000</v>
+        <v>740000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>707000</v>
+        <v>678000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>816000</v>
+        <v>819000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
         <v>1000</v>
       </c>
       <c r="F70" t="n">
-        <v>1059000</v>
+        <v>1045000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>70</v>
       </c>
       <c r="F73" t="n">
-        <v>446000</v>
+        <v>451000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>1000</v>
       </c>
       <c r="F74" t="n">
-        <v>761000</v>
+        <v>743000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
         <v>130</v>
       </c>
       <c r="F76" t="n">
-        <v>656000</v>
+        <v>670000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
         <v>110</v>
       </c>
       <c r="F80" t="n">
-        <v>482000</v>
+        <v>486000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>120</v>
       </c>
       <c r="F84" t="n">
-        <v>627000</v>
+        <v>612000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>70</v>
       </c>
       <c r="F90" t="n">
-        <v>684000</v>
+        <v>669000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11953,7 +11953,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>859000</v>
+        <v>867000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>615000</v>
+        <v>574000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>140</v>
       </c>
       <c r="F96" t="n">
-        <v>583000</v>
+        <v>611000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -12117,7 +12117,7 @@
         <v>1000</v>
       </c>
       <c r="F97" t="n">
-        <v>685000</v>
+        <v>718000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
         <v>60</v>
       </c>
       <c r="F101" t="n">
-        <v>755000</v>
+        <v>739000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>70</v>
       </c>
       <c r="F104" t="n">
-        <v>590000</v>
+        <v>575000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>774000</v>
+        <v>777000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>40</v>
       </c>
       <c r="F107" t="n">
-        <v>715000</v>
+        <v>714000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>463000</v>
+        <v>496000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -12691,7 +12691,7 @@
         <v>130</v>
       </c>
       <c r="F111" t="n">
-        <v>385000</v>
+        <v>406000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>1010</v>
       </c>
       <c r="F112" t="n">
-        <v>463000</v>
+        <v>459000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
         <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>465000</v>
+        <v>493000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>70</v>
       </c>
       <c r="F116" t="n">
-        <v>568000</v>
+        <v>563000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>1010</v>
       </c>
       <c r="F117" t="n">
-        <v>1006000</v>
+        <v>1003000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         <v>90</v>
       </c>
       <c r="F118" t="n">
-        <v>756000</v>
+        <v>750000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -13183,7 +13183,7 @@
         <v>110</v>
       </c>
       <c r="F123" t="n">
-        <v>471000</v>
+        <v>466000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>130</v>
       </c>
       <c r="F127" t="n">
-        <v>583000</v>
+        <v>587000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13470,7 +13470,7 @@
         <v>90</v>
       </c>
       <c r="F130" t="n">
-        <v>846000</v>
+        <v>830000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>120</v>
       </c>
       <c r="F133" t="n">
-        <v>569000</v>
+        <v>589000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13634,7 +13634,7 @@
         <v>60</v>
       </c>
       <c r="F134" t="n">
-        <v>653000</v>
+        <v>629000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>110</v>
       </c>
       <c r="F138" t="n">
-        <v>793000</v>
+        <v>810000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>70</v>
       </c>
       <c r="F139" t="n">
-        <v>836000</v>
+        <v>834000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>10</v>
       </c>
       <c r="F140" t="n">
-        <v>575000</v>
+        <v>615000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="F142" t="n">
-        <v>540000</v>
+        <v>574000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>130</v>
       </c>
       <c r="F143" t="n">
-        <v>1028000</v>
+        <v>1049000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>1000</v>
       </c>
       <c r="F144" t="n">
-        <v>389000</v>
+        <v>381000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>485000</v>
+        <v>498000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>1010</v>
       </c>
       <c r="F146" t="n">
-        <v>486000</v>
+        <v>478000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>100</v>
       </c>
       <c r="F147" t="n">
-        <v>590000</v>
+        <v>602000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14208,7 +14208,7 @@
         <v>70</v>
       </c>
       <c r="F148" t="n">
-        <v>973000</v>
+        <v>971000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="F150" t="n">
-        <v>345000</v>
+        <v>393000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>543000</v>
+        <v>562000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>90</v>
       </c>
       <c r="F158" t="n">
-        <v>614000</v>
+        <v>607000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>720000</v>
+        <v>721000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14700,7 +14700,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>836000</v>
+        <v>809000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>548000</v>
+        <v>544000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>719000</v>
+        <v>711000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>140</v>
       </c>
       <c r="F170" t="n">
-        <v>487000</v>
+        <v>469000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>629000</v>
+        <v>656000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         <v>60</v>
       </c>
       <c r="F174" t="n">
-        <v>715000</v>
+        <v>712000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>30</v>
       </c>
       <c r="F175" t="n">
-        <v>623000</v>
+        <v>636000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>130</v>
       </c>
       <c r="F185" t="n">
-        <v>725000</v>
+        <v>750000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>10</v>
       </c>
       <c r="F186" t="n">
-        <v>306000</v>
+        <v>400000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>70</v>
       </c>
       <c r="F193" t="n">
-        <v>575000</v>
+        <v>552000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>110</v>
       </c>
       <c r="F195" t="n">
-        <v>263000</v>
+        <v>245000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>30</v>
       </c>
       <c r="F198" t="n">
-        <v>570000</v>
+        <v>596000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>90</v>
       </c>
       <c r="F199" t="n">
-        <v>589000</v>
+        <v>574000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>130</v>
       </c>
       <c r="F200" t="n">
-        <v>406000</v>
+        <v>415000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -16381,7 +16381,7 @@
         <v>70</v>
       </c>
       <c r="F201" t="n">
-        <v>655000</v>
+        <v>657000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>80</v>
       </c>
       <c r="F203" t="n">
-        <v>642000</v>
+        <v>660000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -16791,7 +16791,7 @@
         <v>100</v>
       </c>
       <c r="F211" t="n">
-        <v>718000</v>
+        <v>725000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
         <v>80</v>
       </c>
       <c r="F223" t="n">
-        <v>307000</v>
+        <v>321000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>1000</v>
       </c>
       <c r="F224" t="n">
-        <v>456000</v>
+        <v>477000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17488,7 +17488,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>655000</v>
+        <v>666000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>679000</v>
+        <v>707000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17775,7 +17775,7 @@
         <v>140</v>
       </c>
       <c r="F235" t="n">
-        <v>397000</v>
+        <v>415000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         <v>30</v>
       </c>
       <c r="F240" t="n">
-        <v>460000</v>
+        <v>473000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>120</v>
       </c>
       <c r="F241" t="n">
-        <v>252000</v>
+        <v>293000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>120</v>
       </c>
       <c r="F249" t="n">
-        <v>555000</v>
+        <v>527000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>110</v>
       </c>
       <c r="F257" t="n">
-        <v>458000</v>
+        <v>462000</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>598000</v>
+        <v>611000</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -19057,7 +19057,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>515000</v>
+        <v>483000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19098,7 +19098,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>499000</v>
+        <v>446000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>664000</v>
+        <v>655000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19221,7 +19221,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>579000</v>
+        <v>584000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>557000</v>
+        <v>539000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19631,7 +19631,7 @@
         <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>791000</v>
+        <v>724000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>640000</v>
+        <v>610000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19713,7 +19713,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>514000</v>
+        <v>518000</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -19795,7 +19795,7 @@
         <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>595000</v>
+        <v>618000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>1010</v>
       </c>
       <c r="F23" t="n">
-        <v>811000</v>
+        <v>805000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>130</v>
       </c>
       <c r="F24" t="n">
-        <v>786000</v>
+        <v>808000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20000,7 +20000,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>572000</v>
+        <v>541000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>510000</v>
+        <v>503000</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -20082,7 +20082,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>746000</v>
+        <v>737000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>516000</v>
+        <v>512000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>1000</v>
       </c>
       <c r="F30" t="n">
-        <v>383000</v>
+        <v>384000</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -20205,7 +20205,7 @@
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>548000</v>
+        <v>568000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>887000</v>
+        <v>856000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20287,7 +20287,7 @@
         <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>805000</v>
+        <v>787000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>825000</v>
+        <v>816000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>703000</v>
+        <v>750000</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -20697,7 +20697,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>481000</v>
+        <v>505000</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -20738,7 +20738,7 @@
         <v>130</v>
       </c>
       <c r="F44" t="n">
-        <v>386000</v>
+        <v>379000</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -20779,7 +20779,7 @@
         <v>130</v>
       </c>
       <c r="F45" t="n">
-        <v>756000</v>
+        <v>748000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>70</v>
       </c>
       <c r="F46" t="n">
-        <v>715000</v>
+        <v>665000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>1000</v>
       </c>
       <c r="F47" t="n">
-        <v>480000</v>
+        <v>513000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>632000</v>
+        <v>633000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>60</v>
       </c>
       <c r="F51" t="n">
-        <v>807000</v>
+        <v>795000</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -21066,7 +21066,7 @@
         <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>753000</v>
+        <v>752000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21148,7 +21148,7 @@
         <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>892000</v>
+        <v>927000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>768000</v>
+        <v>758000</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -21517,7 +21517,7 @@
         <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>728000</v>
+        <v>720000</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>639000</v>
+        <v>617000</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -21681,7 +21681,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>424000</v>
+        <v>400000</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -21722,7 +21722,7 @@
         <v>140</v>
       </c>
       <c r="F68" t="n">
-        <v>440000</v>
+        <v>448000</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -21763,7 +21763,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>571000</v>
+        <v>546000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="n">
-        <v>566000</v>
+        <v>580000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>90</v>
       </c>
       <c r="F72" t="n">
-        <v>864000</v>
+        <v>861000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -22009,7 +22009,7 @@
         <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>710000</v>
+        <v>707000</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -22050,7 +22050,7 @@
         <v>140</v>
       </c>
       <c r="F76" t="n">
-        <v>580000</v>
+        <v>590000</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -22091,7 +22091,7 @@
         <v>80</v>
       </c>
       <c r="F77" t="n">
-        <v>591000</v>
+        <v>541000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>736000</v>
+        <v>742000</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -22173,7 +22173,7 @@
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>498000</v>
+        <v>512000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>918000</v>
+        <v>919000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>90</v>
       </c>
       <c r="F81" t="n">
-        <v>557000</v>
+        <v>540000</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -22296,7 +22296,7 @@
         <v>130</v>
       </c>
       <c r="F82" t="n">
-        <v>525000</v>
+        <v>508000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>120</v>
       </c>
       <c r="F85" t="n">
-        <v>618000</v>
+        <v>620000</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -22460,7 +22460,7 @@
         <v>1010</v>
       </c>
       <c r="F86" t="n">
-        <v>742000</v>
+        <v>760000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22501,7 +22501,7 @@
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>454000</v>
+        <v>485000</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -22583,7 +22583,7 @@
         <v>140</v>
       </c>
       <c r="F89" t="n">
-        <v>589000</v>
+        <v>561000</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -22665,7 +22665,7 @@
         <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>716000</v>
+        <v>723000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>110</v>
       </c>
       <c r="F93" t="n">
-        <v>664000</v>
+        <v>647000</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -22788,7 +22788,7 @@
         <v>130</v>
       </c>
       <c r="F94" t="n">
-        <v>525000</v>
+        <v>527000</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -22870,7 +22870,7 @@
         <v>40</v>
       </c>
       <c r="F96" t="n">
-        <v>612000</v>
+        <v>580000</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -22911,7 +22911,7 @@
         <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>258000</v>
+        <v>287000</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -22993,7 +22993,7 @@
         <v>110</v>
       </c>
       <c r="F99" t="n">
-        <v>466000</v>
+        <v>448000</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>90</v>
       </c>
       <c r="F102" t="n">
-        <v>688000</v>
+        <v>692000</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -23362,7 +23362,7 @@
         <v>140</v>
       </c>
       <c r="F108" t="n">
-        <v>563000</v>
+        <v>556000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>1000</v>
       </c>
       <c r="F112" t="n">
-        <v>466000</v>
+        <v>459000</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>80</v>
       </c>
       <c r="F114" t="n">
-        <v>709000</v>
+        <v>701000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>569000</v>
+        <v>559000</v>
       </c>
       <c r="G116" t="n">
         <v>1</v>
@@ -23813,7 +23813,7 @@
         <v>1010</v>
       </c>
       <c r="F119" t="n">
-        <v>624000</v>
+        <v>622000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>30</v>
       </c>
       <c r="F120" t="n">
-        <v>560000</v>
+        <v>554000</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -23936,7 +23936,7 @@
         <v>110</v>
       </c>
       <c r="F122" t="n">
-        <v>753000</v>
+        <v>763000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -23977,7 +23977,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>632000</v>
+        <v>625000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24018,7 +24018,7 @@
         <v>140</v>
       </c>
       <c r="F124" t="n">
-        <v>707000</v>
+        <v>692000</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -24100,7 +24100,7 @@
         <v>110</v>
       </c>
       <c r="F126" t="n">
-        <v>517000</v>
+        <v>514000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24141,7 +24141,7 @@
         <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>908000</v>
+        <v>899000</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>503000</v>
+        <v>486000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24346,7 +24346,7 @@
         <v>140</v>
       </c>
       <c r="F132" t="n">
-        <v>423000</v>
+        <v>430000</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -24387,7 +24387,7 @@
         <v>30</v>
       </c>
       <c r="F133" t="n">
-        <v>603000</v>
+        <v>609000</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -24551,7 +24551,7 @@
         <v>40</v>
       </c>
       <c r="F137" t="n">
-        <v>426000</v>
+        <v>432000</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -24633,7 +24633,7 @@
         <v>120</v>
       </c>
       <c r="F139" t="n">
-        <v>363000</v>
+        <v>348000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24674,7 +24674,7 @@
         <v>110</v>
       </c>
       <c r="F140" t="n">
-        <v>661000</v>
+        <v>669000</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -24797,7 +24797,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>876000</v>
+        <v>907000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -25166,7 +25166,7 @@
         <v>60</v>
       </c>
       <c r="F152" t="n">
-        <v>808000</v>
+        <v>802000</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>80</v>
       </c>
       <c r="F156" t="n">
-        <v>758000</v>
+        <v>753000</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -25371,7 +25371,7 @@
         <v>70</v>
       </c>
       <c r="F157" t="n">
-        <v>566000</v>
+        <v>553000</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -25740,7 +25740,7 @@
         <v>140</v>
       </c>
       <c r="F166" t="n">
-        <v>413000</v>
+        <v>404000</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
@@ -25822,7 +25822,7 @@
         <v>1010</v>
       </c>
       <c r="F168" t="n">
-        <v>497000</v>
+        <v>490000</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>40</v>
       </c>
       <c r="F171" t="n">
-        <v>345000</v>
+        <v>368000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26150,7 +26150,7 @@
         <v>70</v>
       </c>
       <c r="F176" t="n">
-        <v>630000</v>
+        <v>633000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26232,7 +26232,7 @@
         <v>10</v>
       </c>
       <c r="F178" t="n">
-        <v>704000</v>
+        <v>709000</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
@@ -26273,7 +26273,7 @@
         <v>10</v>
       </c>
       <c r="F179" t="n">
-        <v>599000</v>
+        <v>607000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26355,7 +26355,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>669000</v>
+        <v>650000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>120</v>
       </c>
       <c r="F182" t="n">
-        <v>624000</v>
+        <v>620000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>40</v>
       </c>
       <c r="F183" t="n">
-        <v>694000</v>
+        <v>668000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26560,7 +26560,7 @@
         <v>30</v>
       </c>
       <c r="F186" t="n">
-        <v>546000</v>
+        <v>517000</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
@@ -26683,7 +26683,7 @@
         <v>90</v>
       </c>
       <c r="F189" t="n">
-        <v>506000</v>
+        <v>515000</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
@@ -26724,7 +26724,7 @@
         <v>60</v>
       </c>
       <c r="F190" t="n">
-        <v>662000</v>
+        <v>700000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>140</v>
       </c>
       <c r="F191" t="n">
-        <v>858000</v>
+        <v>828000</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -26847,7 +26847,7 @@
         <v>130</v>
       </c>
       <c r="F193" t="n">
-        <v>541000</v>
+        <v>565000</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -26970,7 +26970,7 @@
         <v>10</v>
       </c>
       <c r="F196" t="n">
-        <v>681000</v>
+        <v>693000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27093,7 +27093,7 @@
         <v>1010</v>
       </c>
       <c r="F199" t="n">
-        <v>657000</v>
+        <v>630000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27257,7 +27257,7 @@
         <v>140</v>
       </c>
       <c r="F203" t="n">
-        <v>499000</v>
+        <v>507000</v>
       </c>
       <c r="G203" t="n">
         <v>1</v>
@@ -27298,7 +27298,7 @@
         <v>60</v>
       </c>
       <c r="F204" t="n">
-        <v>637000</v>
+        <v>652000</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -27380,7 +27380,7 @@
         <v>130</v>
       </c>
       <c r="F206" t="n">
-        <v>853000</v>
+        <v>838000</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -27462,7 +27462,7 @@
         <v>70</v>
       </c>
       <c r="F208" t="n">
-        <v>351000</v>
+        <v>368000</v>
       </c>
       <c r="G208" t="n">
         <v>1</v>
@@ -27503,7 +27503,7 @@
         <v>90</v>
       </c>
       <c r="F209" t="n">
-        <v>380000</v>
+        <v>379000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>460000</v>
+        <v>489000</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -27667,7 +27667,7 @@
         <v>110</v>
       </c>
       <c r="F213" t="n">
-        <v>302000</v>
+        <v>313000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>120</v>
       </c>
       <c r="F214" t="n">
-        <v>290000</v>
+        <v>302000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -28036,7 +28036,7 @@
         <v>120</v>
       </c>
       <c r="F222" t="n">
-        <v>526000</v>
+        <v>506000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28118,7 +28118,7 @@
         <v>130</v>
       </c>
       <c r="F224" t="n">
-        <v>549000</v>
+        <v>544000</v>
       </c>
       <c r="G224" t="n">
         <v>1</v>
@@ -28159,7 +28159,7 @@
         <v>120</v>
       </c>
       <c r="F225" t="n">
-        <v>589000</v>
+        <v>582000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28241,7 +28241,7 @@
         <v>80</v>
       </c>
       <c r="F227" t="n">
-        <v>609000</v>
+        <v>622000</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -28282,7 +28282,7 @@
         <v>90</v>
       </c>
       <c r="F228" t="n">
-        <v>396000</v>
+        <v>399000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28364,7 +28364,7 @@
         <v>100</v>
       </c>
       <c r="F230" t="n">
-        <v>357000</v>
+        <v>340000</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>1000</v>
       </c>
       <c r="F232" t="n">
-        <v>559000</v>
+        <v>527000</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
@@ -28487,7 +28487,7 @@
         <v>100</v>
       </c>
       <c r="F233" t="n">
-        <v>1049000</v>
+        <v>1056000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28528,7 +28528,7 @@
         <v>100</v>
       </c>
       <c r="F234" t="n">
-        <v>399000</v>
+        <v>419000</v>
       </c>
       <c r="G234" t="n">
         <v>1</v>
@@ -28651,7 +28651,7 @@
         <v>90</v>
       </c>
       <c r="F237" t="n">
-        <v>632000</v>
+        <v>629000</v>
       </c>
       <c r="G237" t="n">
         <v>1</v>
@@ -28692,7 +28692,7 @@
         <v>1000</v>
       </c>
       <c r="F238" t="n">
-        <v>444000</v>
+        <v>457000</v>
       </c>
       <c r="G238" t="n">
         <v>1</v>
@@ -28733,7 +28733,7 @@
         <v>130</v>
       </c>
       <c r="F239" t="n">
-        <v>326000</v>
+        <v>339000</v>
       </c>
       <c r="G239" t="n">
         <v>1</v>
@@ -28774,7 +28774,7 @@
         <v>130</v>
       </c>
       <c r="F240" t="n">
-        <v>262000</v>
+        <v>300000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>100</v>
       </c>
       <c r="F243" t="n">
-        <v>685000</v>
+        <v>666000</v>
       </c>
       <c r="G243" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>140</v>
       </c>
       <c r="F256" t="n">
-        <v>705000</v>
+        <v>695000</v>
       </c>
       <c r="G256" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>130</v>
       </c>
       <c r="F259" t="n">
-        <v>813000</v>
+        <v>829000</v>
       </c>
       <c r="G259" t="n">
         <v>1</v>
@@ -29594,7 +29594,7 @@
         <v>110</v>
       </c>
       <c r="F260" t="n">
-        <v>496000</v>
+        <v>469000</v>
       </c>
       <c r="G260" t="n">
         <v>1</v>
@@ -29717,7 +29717,7 @@
         <v>1010</v>
       </c>
       <c r="F263" t="n">
-        <v>742000</v>
+        <v>743000</v>
       </c>
       <c r="G263" t="n">
         <v>1</v>
@@ -30004,7 +30004,7 @@
         <v>60</v>
       </c>
       <c r="F270" t="n">
-        <v>802000</v>
+        <v>820000</v>
       </c>
       <c r="G270" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>30</v>
       </c>
       <c r="F272" t="n">
-        <v>738000</v>
+        <v>726000</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
@@ -30168,7 +30168,7 @@
         <v>110</v>
       </c>
       <c r="F274" t="n">
-        <v>552000</v>
+        <v>525000</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
@@ -30209,7 +30209,7 @@
         <v>120</v>
       </c>
       <c r="F275" t="n">
-        <v>326000</v>
+        <v>365000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>1000</v>
       </c>
       <c r="F292" t="n">
-        <v>524000</v>
+        <v>522000</v>
       </c>
       <c r="G292" t="n">
         <v>1</v>
@@ -31070,7 +31070,7 @@
         <v>140</v>
       </c>
       <c r="F296" t="n">
-        <v>449000</v>
+        <v>494000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31480,7 +31480,7 @@
         <v>100</v>
       </c>
       <c r="F306" t="n">
-        <v>505000</v>
+        <v>540000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31603,7 +31603,7 @@
         <v>1010</v>
       </c>
       <c r="F309" t="n">
-        <v>613000</v>
+        <v>602000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>110</v>
       </c>
       <c r="F310" t="n">
-        <v>410000</v>
+        <v>405000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>120</v>
       </c>
       <c r="F312" t="n">
-        <v>485000</v>
+        <v>458000</v>
       </c>
       <c r="G312" t="n">
         <v>1</v>
@@ -31849,7 +31849,7 @@
         <v>80</v>
       </c>
       <c r="F315" t="n">
-        <v>341000</v>
+        <v>368000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>30</v>
       </c>
       <c r="F336" t="n">
-        <v>340000</v>
+        <v>343000</v>
       </c>
       <c r="G336" t="n">
         <v>1</v>
@@ -33254,7 +33254,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>568000</v>
+        <v>589000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33295,7 +33295,7 @@
         <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>1003000</v>
+        <v>965000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33418,7 +33418,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>873000</v>
+        <v>816000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33459,7 +33459,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>809000</v>
+        <v>848000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33582,7 +33582,7 @@
         <v>130</v>
       </c>
       <c r="F11" t="n">
-        <v>741000</v>
+        <v>732000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>829000</v>
+        <v>801000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>780000</v>
+        <v>801000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>989000</v>
+        <v>1000000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -33910,7 +33910,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>887000</v>
+        <v>884000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -33992,7 +33992,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1161000</v>
+        <v>1166000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>635000</v>
+        <v>629000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>980000</v>
+        <v>979000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34361,7 +34361,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>852000</v>
+        <v>866000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34443,7 +34443,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>695000</v>
+        <v>677000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>713000</v>
+        <v>695000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34525,7 +34525,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>779000</v>
+        <v>790000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34648,7 +34648,7 @@
         <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>843000</v>
+        <v>870000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>866000</v>
+        <v>892000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -34771,7 +34771,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>752000</v>
+        <v>741000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>875000</v>
+        <v>843000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>807000</v>
+        <v>806000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>540000</v>
+        <v>532000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35058,7 +35058,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>863000</v>
+        <v>831000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>915000</v>
+        <v>913000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>110</v>
       </c>
       <c r="F52" t="n">
-        <v>987000</v>
+        <v>968000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -35550,7 +35550,7 @@
         <v>80</v>
       </c>
       <c r="F59" t="n">
-        <v>800000</v>
+        <v>816000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>995000</v>
+        <v>1038000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -35714,7 +35714,7 @@
         <v>1000</v>
       </c>
       <c r="F63" t="n">
-        <v>893000</v>
+        <v>901000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>60</v>
       </c>
       <c r="F64" t="n">
-        <v>822000</v>
+        <v>810000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -35878,7 +35878,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>864000</v>
+        <v>837000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -36042,7 +36042,7 @@
         <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>747000</v>
+        <v>737000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>898000</v>
+        <v>911000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
         <v>60</v>
       </c>
       <c r="F74" t="n">
-        <v>677000</v>
+        <v>672000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>1010</v>
       </c>
       <c r="F77" t="n">
-        <v>574000</v>
+        <v>556000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         <v>60</v>
       </c>
       <c r="F81" t="n">
-        <v>526000</v>
+        <v>558000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -36534,7 +36534,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>277000</v>
+        <v>326000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36575,7 +36575,7 @@
         <v>80</v>
       </c>
       <c r="F84" t="n">
-        <v>759000</v>
+        <v>773000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>60</v>
       </c>
       <c r="F86" t="n">
-        <v>655000</v>
+        <v>686000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -36821,7 +36821,7 @@
         <v>80</v>
       </c>
       <c r="F90" t="n">
-        <v>810000</v>
+        <v>832000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>470000</v>
+        <v>521000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>489000</v>
+        <v>497000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37149,7 +37149,7 @@
         <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>1106000</v>
+        <v>1128000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37190,7 +37190,7 @@
         <v>1010</v>
       </c>
       <c r="F99" t="n">
-        <v>932000</v>
+        <v>939000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>674000</v>
+        <v>673000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -37272,7 +37272,7 @@
         <v>80</v>
       </c>
       <c r="F101" t="n">
-        <v>755000</v>
+        <v>750000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>70</v>
       </c>
       <c r="F105" t="n">
-        <v>421000</v>
+        <v>442000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -37559,7 +37559,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>621000</v>
+        <v>645000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -37682,7 +37682,7 @@
         <v>70</v>
       </c>
       <c r="F111" t="n">
-        <v>727000</v>
+        <v>705000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -37805,7 +37805,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>472000</v>
+        <v>500000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -38010,7 +38010,7 @@
         <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>574000</v>
+        <v>563000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>130</v>
       </c>
       <c r="F121" t="n">
-        <v>793000</v>
+        <v>833000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -38256,7 +38256,7 @@
         <v>90</v>
       </c>
       <c r="F125" t="n">
-        <v>666000</v>
+        <v>662000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>1000</v>
       </c>
       <c r="F132" t="n">
-        <v>333000</v>
+        <v>404000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38666,7 +38666,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="n">
-        <v>585000</v>
+        <v>577000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>140</v>
       </c>
       <c r="F137" t="n">
-        <v>238000</v>
+        <v>262000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>1000</v>
       </c>
       <c r="F139" t="n">
-        <v>282000</v>
+        <v>310000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>253000</v>
+        <v>303000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>30</v>
       </c>
       <c r="F145" t="n">
-        <v>376000</v>
+        <v>383000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39363,7 +39363,7 @@
         <v>40</v>
       </c>
       <c r="F152" t="n">
-        <v>230000</v>
+        <v>255000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>1030000</v>
+        <v>1043000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39743,7 +39743,7 @@
         <v>1000</v>
       </c>
       <c r="F5" t="n">
-        <v>698000</v>
+        <v>638000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -39825,7 +39825,7 @@
         <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>509000</v>
+        <v>503000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -39907,7 +39907,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>918000</v>
+        <v>873000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -39989,7 +39989,7 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>632000</v>
+        <v>629000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -40030,7 +40030,7 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>852000</v>
+        <v>831000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>759000</v>
+        <v>780000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40235,7 +40235,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>592000</v>
+        <v>595000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -40276,7 +40276,7 @@
         <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>529000</v>
+        <v>521000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>140</v>
       </c>
       <c r="F19" t="n">
-        <v>853000</v>
+        <v>842000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40358,7 +40358,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>642000</v>
+        <v>623000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -40399,7 +40399,7 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>924000</v>
+        <v>907000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>1010</v>
       </c>
       <c r="F22" t="n">
-        <v>717000</v>
+        <v>742000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>961000</v>
+        <v>987000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40727,7 +40727,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>693000</v>
+        <v>682000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>815000</v>
+        <v>821000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -40850,7 +40850,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>474000</v>
+        <v>490000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -41383,7 +41383,7 @@
         <v>100</v>
       </c>
       <c r="F45" t="n">
-        <v>238000</v>
+        <v>248000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8345,7 +8345,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>899000</v>
+        <v>919000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>751000</v>
+        <v>726000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>761000</v>
+        <v>727000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>556000</v>
+        <v>524000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>935000</v>
+        <v>934000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>1010</v>
       </c>
       <c r="F13" t="n">
-        <v>976000</v>
+        <v>963000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>624000</v>
+        <v>618000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>452000</v>
+        <v>443000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>597000</v>
+        <v>602000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>834000</v>
+        <v>899000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>506000</v>
+        <v>515000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>372000</v>
+        <v>386000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>659000</v>
+        <v>674000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>645000</v>
+        <v>623000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>449000</v>
+        <v>473000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>80</v>
       </c>
       <c r="F29" t="n">
-        <v>892000</v>
+        <v>871000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>847000</v>
+        <v>841000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>864000</v>
+        <v>886000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>794000</v>
+        <v>749000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
         <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>351000</v>
+        <v>353000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>381000</v>
+        <v>340000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>486000</v>
+        <v>494000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>886000</v>
+        <v>859000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>613000</v>
+        <v>622000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>673000</v>
+        <v>675000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>150</v>
       </c>
       <c r="F48" t="n">
-        <v>560000</v>
+        <v>551000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10190,7 +10190,7 @@
         <v>160</v>
       </c>
       <c r="F50" t="n">
-        <v>862000</v>
+        <v>875000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>40</v>
       </c>
       <c r="F52" t="n">
-        <v>745000</v>
+        <v>760000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>566000</v>
+        <v>573000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         <v>60</v>
       </c>
       <c r="F57" t="n">
-        <v>524000</v>
+        <v>519000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -10518,7 +10518,7 @@
         <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>724000</v>
+        <v>760000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -10682,7 +10682,7 @@
         <v>50</v>
       </c>
       <c r="F62" t="n">
-        <v>646000</v>
+        <v>639000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>752000</v>
+        <v>714000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>80</v>
       </c>
       <c r="F65" t="n">
-        <v>740000</v>
+        <v>726000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>678000</v>
+        <v>659000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>819000</v>
+        <v>821000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
         <v>1000</v>
       </c>
       <c r="F70" t="n">
-        <v>1045000</v>
+        <v>998000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>668000</v>
+        <v>673000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>513000</v>
+        <v>509000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11543,7 +11543,7 @@
         <v>150</v>
       </c>
       <c r="F83" t="n">
-        <v>456000</v>
+        <v>427000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         <v>120</v>
       </c>
       <c r="F84" t="n">
-        <v>612000</v>
+        <v>609000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -11707,7 +11707,7 @@
         <v>110</v>
       </c>
       <c r="F87" t="n">
-        <v>496000</v>
+        <v>485000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
         <v>110</v>
       </c>
       <c r="F88" t="n">
-        <v>543000</v>
+        <v>509000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>445000</v>
+        <v>455000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11953,7 +11953,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>867000</v>
+        <v>899000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>574000</v>
+        <v>549000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12117,7 +12117,7 @@
         <v>1000</v>
       </c>
       <c r="F97" t="n">
-        <v>718000</v>
+        <v>723000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -12158,7 +12158,7 @@
         <v>160</v>
       </c>
       <c r="F98" t="n">
-        <v>873000</v>
+        <v>848000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
         <v>60</v>
       </c>
       <c r="F101" t="n">
-        <v>739000</v>
+        <v>741000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>160</v>
       </c>
       <c r="F103" t="n">
-        <v>666000</v>
+        <v>654000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>1000</v>
       </c>
       <c r="F105" t="n">
-        <v>710000</v>
+        <v>681000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>777000</v>
+        <v>773000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>40</v>
       </c>
       <c r="F107" t="n">
-        <v>714000</v>
+        <v>699000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12568,7 +12568,7 @@
         <v>160</v>
       </c>
       <c r="F108" t="n">
-        <v>799000</v>
+        <v>761000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -12609,7 +12609,7 @@
         <v>160</v>
       </c>
       <c r="F109" t="n">
-        <v>743000</v>
+        <v>744000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>1000</v>
       </c>
       <c r="F113" t="n">
-        <v>386000</v>
+        <v>356000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
         <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>493000</v>
+        <v>511000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>1010</v>
       </c>
       <c r="F117" t="n">
-        <v>1003000</v>
+        <v>989000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -13019,7 +13019,7 @@
         <v>50</v>
       </c>
       <c r="F119" t="n">
-        <v>660000</v>
+        <v>653000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -13183,7 +13183,7 @@
         <v>110</v>
       </c>
       <c r="F123" t="n">
-        <v>466000</v>
+        <v>470000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>80</v>
       </c>
       <c r="F124" t="n">
-        <v>395000</v>
+        <v>385000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>814000</v>
+        <v>809000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>591000</v>
+        <v>597000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>120</v>
       </c>
       <c r="F133" t="n">
-        <v>589000</v>
+        <v>594000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13634,7 +13634,7 @@
         <v>60</v>
       </c>
       <c r="F134" t="n">
-        <v>629000</v>
+        <v>607000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>10</v>
       </c>
       <c r="F140" t="n">
-        <v>615000</v>
+        <v>635000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="F142" t="n">
-        <v>574000</v>
+        <v>583000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>498000</v>
+        <v>530000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>1010</v>
       </c>
       <c r="F146" t="n">
-        <v>478000</v>
+        <v>453000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>100</v>
       </c>
       <c r="F147" t="n">
-        <v>602000</v>
+        <v>615000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="F150" t="n">
-        <v>393000</v>
+        <v>426000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>20</v>
       </c>
       <c r="F152" t="n">
-        <v>955000</v>
+        <v>932000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>562000</v>
+        <v>563000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>160</v>
       </c>
       <c r="F156" t="n">
-        <v>763000</v>
+        <v>740000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>100</v>
       </c>
       <c r="F157" t="n">
-        <v>235000</v>
+        <v>265000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>721000</v>
+        <v>723000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14700,7 +14700,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>809000</v>
+        <v>790000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>544000</v>
+        <v>558000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>150</v>
       </c>
       <c r="F162" t="n">
-        <v>437000</v>
+        <v>421000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>366000</v>
+        <v>362000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14905,7 +14905,7 @@
         <v>150</v>
       </c>
       <c r="F165" t="n">
-        <v>598000</v>
+        <v>569000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>711000</v>
+        <v>697000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         <v>60</v>
       </c>
       <c r="F174" t="n">
-        <v>712000</v>
+        <v>720000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>30</v>
       </c>
       <c r="F175" t="n">
-        <v>636000</v>
+        <v>654000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         <v>150</v>
       </c>
       <c r="F183" t="n">
-        <v>477000</v>
+        <v>475000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>10</v>
       </c>
       <c r="F186" t="n">
-        <v>400000</v>
+        <v>469000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -16012,7 +16012,7 @@
         <v>20</v>
       </c>
       <c r="F192" t="n">
-        <v>589000</v>
+        <v>601000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>30</v>
       </c>
       <c r="F198" t="n">
-        <v>596000</v>
+        <v>638000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -16668,7 +16668,7 @@
         <v>50</v>
       </c>
       <c r="F208" t="n">
-        <v>387000</v>
+        <v>404000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -16709,7 +16709,7 @@
         <v>150</v>
       </c>
       <c r="F209" t="n">
-        <v>466000</v>
+        <v>485000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -16791,7 +16791,7 @@
         <v>100</v>
       </c>
       <c r="F211" t="n">
-        <v>725000</v>
+        <v>732000</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>100</v>
       </c>
       <c r="F218" t="n">
-        <v>367000</v>
+        <v>356000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>1010</v>
       </c>
       <c r="F219" t="n">
-        <v>282000</v>
+        <v>300000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
         <v>80</v>
       </c>
       <c r="F223" t="n">
-        <v>321000</v>
+        <v>346000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>1000</v>
       </c>
       <c r="F224" t="n">
-        <v>477000</v>
+        <v>520000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>150</v>
       </c>
       <c r="F225" t="n">
-        <v>633000</v>
+        <v>612000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -17488,7 +17488,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>666000</v>
+        <v>663000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>707000</v>
+        <v>740000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         <v>30</v>
       </c>
       <c r="F240" t="n">
-        <v>473000</v>
+        <v>504000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>120</v>
       </c>
       <c r="F241" t="n">
-        <v>293000</v>
+        <v>327000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18144,7 +18144,7 @@
         <v>50</v>
       </c>
       <c r="F244" t="n">
-        <v>664000</v>
+        <v>691000</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>150</v>
       </c>
       <c r="F247" t="n">
-        <v>878000</v>
+        <v>883000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>120</v>
       </c>
       <c r="F249" t="n">
-        <v>527000</v>
+        <v>508000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>110</v>
       </c>
       <c r="F257" t="n">
-        <v>462000</v>
+        <v>481000</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>483000</v>
+        <v>479000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>655000</v>
+        <v>644000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19221,7 +19221,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>584000</v>
+        <v>590000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>539000</v>
+        <v>529000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19467,7 +19467,7 @@
         <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>762000</v>
+        <v>727000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>610000</v>
+        <v>575000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19713,7 +19713,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>518000</v>
+        <v>533000</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -19836,7 +19836,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>699000</v>
+        <v>672000</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>1010</v>
       </c>
       <c r="F23" t="n">
-        <v>805000</v>
+        <v>813000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -20082,7 +20082,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>737000</v>
+        <v>722000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>512000</v>
+        <v>517000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>1000</v>
       </c>
       <c r="F30" t="n">
-        <v>384000</v>
+        <v>395000</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>856000</v>
+        <v>809000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>816000</v>
+        <v>802000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20574,7 +20574,7 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>629000</v>
+        <v>612000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>150</v>
       </c>
       <c r="F41" t="n">
-        <v>784000</v>
+        <v>750000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>750000</v>
+        <v>757000</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -20697,7 +20697,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>505000</v>
+        <v>536000</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>1000</v>
       </c>
       <c r="F47" t="n">
-        <v>513000</v>
+        <v>521000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>633000</v>
+        <v>625000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>562000</v>
+        <v>535000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>60</v>
       </c>
       <c r="F51" t="n">
-        <v>795000</v>
+        <v>803000</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -21066,7 +21066,7 @@
         <v>100</v>
       </c>
       <c r="F52" t="n">
-        <v>752000</v>
+        <v>742000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>80</v>
       </c>
       <c r="F53" t="n">
-        <v>536000</v>
+        <v>551000</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -21148,7 +21148,7 @@
         <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>927000</v>
+        <v>952000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>150</v>
       </c>
       <c r="F56" t="n">
-        <v>781000</v>
+        <v>784000</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -21271,7 +21271,7 @@
         <v>160</v>
       </c>
       <c r="F57" t="n">
-        <v>671000</v>
+        <v>698000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>758000</v>
+        <v>752000</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -21394,7 +21394,7 @@
         <v>160</v>
       </c>
       <c r="F60" t="n">
-        <v>568000</v>
+        <v>578000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21476,7 +21476,7 @@
         <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>495000</v>
+        <v>526000</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -21517,7 +21517,7 @@
         <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>720000</v>
+        <v>746000</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>100</v>
       </c>
       <c r="F65" t="n">
-        <v>617000</v>
+        <v>606000</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -21763,7 +21763,7 @@
         <v>60</v>
       </c>
       <c r="F69" t="n">
-        <v>546000</v>
+        <v>539000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="n">
-        <v>580000</v>
+        <v>599000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -22009,7 +22009,7 @@
         <v>40</v>
       </c>
       <c r="F75" t="n">
-        <v>707000</v>
+        <v>719000</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -22091,7 +22091,7 @@
         <v>80</v>
       </c>
       <c r="F77" t="n">
-        <v>541000</v>
+        <v>508000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>742000</v>
+        <v>750000</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -22173,7 +22173,7 @@
         <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>512000</v>
+        <v>537000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>919000</v>
+        <v>870000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="n">
-        <v>581000</v>
+        <v>570000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>120</v>
       </c>
       <c r="F85" t="n">
-        <v>620000</v>
+        <v>622000</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -22460,7 +22460,7 @@
         <v>1010</v>
       </c>
       <c r="F86" t="n">
-        <v>760000</v>
+        <v>730000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22501,7 +22501,7 @@
         <v>100</v>
       </c>
       <c r="F87" t="n">
-        <v>485000</v>
+        <v>516000</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -22542,7 +22542,7 @@
         <v>20</v>
       </c>
       <c r="F88" t="n">
-        <v>856000</v>
+        <v>870000</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -22665,7 +22665,7 @@
         <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>723000</v>
+        <v>720000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>110</v>
       </c>
       <c r="F93" t="n">
-        <v>647000</v>
+        <v>623000</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -22870,7 +22870,7 @@
         <v>40</v>
       </c>
       <c r="F96" t="n">
-        <v>580000</v>
+        <v>556000</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -23157,7 +23157,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>624000</v>
+        <v>617000</v>
       </c>
       <c r="G103" t="n">
         <v>1</v>
@@ -23198,7 +23198,7 @@
         <v>150</v>
       </c>
       <c r="F104" t="n">
-        <v>687000</v>
+        <v>658000</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -23239,7 +23239,7 @@
         <v>160</v>
       </c>
       <c r="F105" t="n">
-        <v>450000</v>
+        <v>417000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>150</v>
       </c>
       <c r="F107" t="n">
-        <v>793000</v>
+        <v>781000</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>120</v>
       </c>
       <c r="F109" t="n">
-        <v>869000</v>
+        <v>849000</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>1000</v>
       </c>
       <c r="F112" t="n">
-        <v>459000</v>
+        <v>445000</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>80</v>
       </c>
       <c r="F114" t="n">
-        <v>701000</v>
+        <v>673000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23731,7 +23731,7 @@
         <v>160</v>
       </c>
       <c r="F117" t="n">
-        <v>463000</v>
+        <v>425000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23813,7 +23813,7 @@
         <v>1010</v>
       </c>
       <c r="F119" t="n">
-        <v>622000</v>
+        <v>611000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>30</v>
       </c>
       <c r="F120" t="n">
-        <v>554000</v>
+        <v>544000</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -23936,7 +23936,7 @@
         <v>110</v>
       </c>
       <c r="F122" t="n">
-        <v>763000</v>
+        <v>774000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -23977,7 +23977,7 @@
         <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>625000</v>
+        <v>626000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24059,7 +24059,7 @@
         <v>120</v>
       </c>
       <c r="F125" t="n">
-        <v>626000</v>
+        <v>646000</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -24100,7 +24100,7 @@
         <v>110</v>
       </c>
       <c r="F126" t="n">
-        <v>514000</v>
+        <v>512000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>486000</v>
+        <v>449000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24387,7 +24387,7 @@
         <v>30</v>
       </c>
       <c r="F133" t="n">
-        <v>609000</v>
+        <v>617000</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -24551,7 +24551,7 @@
         <v>40</v>
       </c>
       <c r="F137" t="n">
-        <v>432000</v>
+        <v>438000</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -24633,7 +24633,7 @@
         <v>120</v>
       </c>
       <c r="F139" t="n">
-        <v>348000</v>
+        <v>324000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24674,7 +24674,7 @@
         <v>110</v>
       </c>
       <c r="F140" t="n">
-        <v>669000</v>
+        <v>702000</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -24756,7 +24756,7 @@
         <v>60</v>
       </c>
       <c r="F142" t="n">
-        <v>397000</v>
+        <v>411000</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -24797,7 +24797,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>907000</v>
+        <v>937000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24879,7 +24879,7 @@
         <v>50</v>
       </c>
       <c r="F145" t="n">
-        <v>468000</v>
+        <v>447000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -25084,7 +25084,7 @@
         <v>160</v>
       </c>
       <c r="F150" t="n">
-        <v>863000</v>
+        <v>910000</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -25166,7 +25166,7 @@
         <v>60</v>
       </c>
       <c r="F152" t="n">
-        <v>802000</v>
+        <v>767000</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>80</v>
       </c>
       <c r="F156" t="n">
-        <v>753000</v>
+        <v>782000</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>160</v>
       </c>
       <c r="F161" t="n">
-        <v>597000</v>
+        <v>600000</v>
       </c>
       <c r="G161" t="n">
         <v>1</v>
@@ -25576,7 +25576,7 @@
         <v>160</v>
       </c>
       <c r="F162" t="n">
-        <v>551000</v>
+        <v>563000</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
@@ -25781,7 +25781,7 @@
         <v>20</v>
       </c>
       <c r="F167" t="n">
-        <v>552000</v>
+        <v>546000</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -25822,7 +25822,7 @@
         <v>1010</v>
       </c>
       <c r="F168" t="n">
-        <v>490000</v>
+        <v>504000</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>40</v>
       </c>
       <c r="F171" t="n">
-        <v>368000</v>
+        <v>387000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>50</v>
       </c>
       <c r="F172" t="n">
-        <v>723000</v>
+        <v>766000</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
@@ -26027,7 +26027,7 @@
         <v>50</v>
       </c>
       <c r="F173" t="n">
-        <v>616000</v>
+        <v>613000</v>
       </c>
       <c r="G173" t="n">
         <v>1</v>
@@ -26232,7 +26232,7 @@
         <v>10</v>
       </c>
       <c r="F178" t="n">
-        <v>709000</v>
+        <v>683000</v>
       </c>
       <c r="G178" t="n">
         <v>1</v>
@@ -26273,7 +26273,7 @@
         <v>10</v>
       </c>
       <c r="F179" t="n">
-        <v>607000</v>
+        <v>595000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>80</v>
       </c>
       <c r="F180" t="n">
-        <v>785000</v>
+        <v>790000</v>
       </c>
       <c r="G180" t="n">
         <v>1</v>
@@ -26355,7 +26355,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>650000</v>
+        <v>638000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>40</v>
       </c>
       <c r="F183" t="n">
-        <v>668000</v>
+        <v>660000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>110</v>
       </c>
       <c r="F185" t="n">
-        <v>465000</v>
+        <v>422000</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
@@ -26724,7 +26724,7 @@
         <v>60</v>
       </c>
       <c r="F190" t="n">
-        <v>700000</v>
+        <v>712000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26970,7 +26970,7 @@
         <v>10</v>
       </c>
       <c r="F196" t="n">
-        <v>693000</v>
+        <v>663000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27093,7 +27093,7 @@
         <v>1010</v>
       </c>
       <c r="F199" t="n">
-        <v>630000</v>
+        <v>618000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27298,7 +27298,7 @@
         <v>60</v>
       </c>
       <c r="F204" t="n">
-        <v>652000</v>
+        <v>640000</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>489000</v>
+        <v>531000</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -28036,7 +28036,7 @@
         <v>120</v>
       </c>
       <c r="F222" t="n">
-        <v>506000</v>
+        <v>504000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28159,7 +28159,7 @@
         <v>120</v>
       </c>
       <c r="F225" t="n">
-        <v>582000</v>
+        <v>571000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28241,7 +28241,7 @@
         <v>80</v>
       </c>
       <c r="F227" t="n">
-        <v>622000</v>
+        <v>611000</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -28364,7 +28364,7 @@
         <v>100</v>
       </c>
       <c r="F230" t="n">
-        <v>340000</v>
+        <v>326000</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>1000</v>
       </c>
       <c r="F232" t="n">
-        <v>527000</v>
+        <v>487000</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
@@ -28487,7 +28487,7 @@
         <v>100</v>
       </c>
       <c r="F233" t="n">
-        <v>1056000</v>
+        <v>1111000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28528,7 +28528,7 @@
         <v>100</v>
       </c>
       <c r="F234" t="n">
-        <v>419000</v>
+        <v>444000</v>
       </c>
       <c r="G234" t="n">
         <v>1</v>
@@ -28692,7 +28692,7 @@
         <v>1000</v>
       </c>
       <c r="F238" t="n">
-        <v>457000</v>
+        <v>460000</v>
       </c>
       <c r="G238" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>160</v>
       </c>
       <c r="F241" t="n">
-        <v>515000</v>
+        <v>503000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>100</v>
       </c>
       <c r="F243" t="n">
-        <v>666000</v>
+        <v>664000</v>
       </c>
       <c r="G243" t="n">
         <v>1</v>
@@ -29635,7 +29635,7 @@
         <v>50</v>
       </c>
       <c r="F261" t="n">
-        <v>571000</v>
+        <v>546000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>1010</v>
       </c>
       <c r="F262" t="n">
-        <v>420000</v>
+        <v>440000</v>
       </c>
       <c r="G262" t="n">
         <v>1</v>
@@ -29717,7 +29717,7 @@
         <v>1010</v>
       </c>
       <c r="F263" t="n">
-        <v>743000</v>
+        <v>731000</v>
       </c>
       <c r="G263" t="n">
         <v>1</v>
@@ -29840,7 +29840,7 @@
         <v>20</v>
       </c>
       <c r="F266" t="n">
-        <v>686000</v>
+        <v>703000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -30004,7 +30004,7 @@
         <v>60</v>
       </c>
       <c r="F270" t="n">
-        <v>820000</v>
+        <v>826000</v>
       </c>
       <c r="G270" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>30</v>
       </c>
       <c r="F272" t="n">
-        <v>726000</v>
+        <v>718000</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
@@ -30168,7 +30168,7 @@
         <v>110</v>
       </c>
       <c r="F274" t="n">
-        <v>525000</v>
+        <v>519000</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
@@ -30209,7 +30209,7 @@
         <v>120</v>
       </c>
       <c r="F275" t="n">
-        <v>365000</v>
+        <v>396000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30373,7 +30373,7 @@
         <v>50</v>
       </c>
       <c r="F279" t="n">
-        <v>460000</v>
+        <v>431000</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
@@ -30496,7 +30496,7 @@
         <v>150</v>
       </c>
       <c r="F282" t="n">
-        <v>439000</v>
+        <v>428000</v>
       </c>
       <c r="G282" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>50</v>
       </c>
       <c r="F291" t="n">
-        <v>449000</v>
+        <v>447000</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>1000</v>
       </c>
       <c r="F292" t="n">
-        <v>522000</v>
+        <v>534000</v>
       </c>
       <c r="G292" t="n">
         <v>1</v>
@@ -31193,7 +31193,7 @@
         <v>50</v>
       </c>
       <c r="F299" t="n">
-        <v>265000</v>
+        <v>281000</v>
       </c>
       <c r="G299" t="n">
         <v>1</v>
@@ -31439,7 +31439,7 @@
         <v>150</v>
       </c>
       <c r="F305" t="n">
-        <v>457000</v>
+        <v>463000</v>
       </c>
       <c r="G305" t="n">
         <v>1</v>
@@ -31480,7 +31480,7 @@
         <v>100</v>
       </c>
       <c r="F306" t="n">
-        <v>540000</v>
+        <v>577000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31603,7 +31603,7 @@
         <v>1010</v>
       </c>
       <c r="F309" t="n">
-        <v>602000</v>
+        <v>609000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>110</v>
       </c>
       <c r="F310" t="n">
-        <v>405000</v>
+        <v>413000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31685,7 +31685,7 @@
         <v>80</v>
       </c>
       <c r="F311" t="n">
-        <v>468000</v>
+        <v>460000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>120</v>
       </c>
       <c r="F312" t="n">
-        <v>458000</v>
+        <v>456000</v>
       </c>
       <c r="G312" t="n">
         <v>1</v>
@@ -32505,7 +32505,7 @@
         <v>20</v>
       </c>
       <c r="F331" t="n">
-        <v>424000</v>
+        <v>464000</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>30</v>
       </c>
       <c r="F336" t="n">
-        <v>343000</v>
+        <v>386000</v>
       </c>
       <c r="G336" t="n">
         <v>1</v>
@@ -33079,7 +33079,7 @@
         <v>50</v>
       </c>
       <c r="F345" t="n">
-        <v>614000</v>
+        <v>601000</v>
       </c>
       <c r="G345" t="n">
         <v>1</v>
@@ -33213,7 +33213,7 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>857000</v>
+        <v>820000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33254,7 +33254,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>589000</v>
+        <v>606000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33377,7 +33377,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>986000</v>
+        <v>971000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33418,7 +33418,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>816000</v>
+        <v>803000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33459,7 +33459,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>848000</v>
+        <v>876000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33500,7 +33500,7 @@
         <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>667000</v>
+        <v>663000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>801000</v>
+        <v>816000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>1073000</v>
+        <v>1084000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -33910,7 +33910,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>884000</v>
+        <v>892000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -33951,7 +33951,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1108000</v>
+        <v>1101000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -33992,7 +33992,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1166000</v>
+        <v>1157000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34074,7 +34074,7 @@
         <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>886000</v>
+        <v>883000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>801000</v>
+        <v>834000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>979000</v>
+        <v>997000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34320,7 +34320,7 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>723000</v>
+        <v>696000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34361,7 +34361,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>866000</v>
+        <v>886000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34402,7 +34402,7 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>966000</v>
+        <v>952000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>695000</v>
+        <v>679000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34525,7 +34525,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>790000</v>
+        <v>787000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34607,7 +34607,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>579000</v>
+        <v>571000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>892000</v>
+        <v>939000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -34771,7 +34771,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>741000</v>
+        <v>746000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>843000</v>
+        <v>849000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -34935,7 +34935,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>659000</v>
+        <v>669000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>806000</v>
+        <v>804000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>532000</v>
+        <v>523000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35058,7 +35058,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>831000</v>
+        <v>778000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>913000</v>
+        <v>923000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>685000</v>
+        <v>682000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -35222,7 +35222,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>707000</v>
+        <v>646000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>110</v>
       </c>
       <c r="F52" t="n">
-        <v>968000</v>
+        <v>988000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -35304,7 +35304,7 @@
         <v>160</v>
       </c>
       <c r="F53" t="n">
-        <v>634000</v>
+        <v>648000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -35550,7 +35550,7 @@
         <v>80</v>
       </c>
       <c r="F59" t="n">
-        <v>816000</v>
+        <v>827000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>1038000</v>
+        <v>1071000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -35714,7 +35714,7 @@
         <v>1000</v>
       </c>
       <c r="F63" t="n">
-        <v>901000</v>
+        <v>893000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>60</v>
       </c>
       <c r="F64" t="n">
-        <v>810000</v>
+        <v>771000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -35796,7 +35796,7 @@
         <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>550000</v>
+        <v>525000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -35878,7 +35878,7 @@
         <v>60</v>
       </c>
       <c r="F67" t="n">
-        <v>837000</v>
+        <v>809000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -35960,7 +35960,7 @@
         <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>304000</v>
+        <v>329000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>911000</v>
+        <v>912000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36124,7 +36124,7 @@
         <v>160</v>
       </c>
       <c r="F73" t="n">
-        <v>1098000</v>
+        <v>1066000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -36165,7 +36165,7 @@
         <v>60</v>
       </c>
       <c r="F74" t="n">
-        <v>672000</v>
+        <v>662000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>1010</v>
       </c>
       <c r="F77" t="n">
-        <v>556000</v>
+        <v>555000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -36329,7 +36329,7 @@
         <v>150</v>
       </c>
       <c r="F78" t="n">
-        <v>259000</v>
+        <v>312000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         <v>60</v>
       </c>
       <c r="F81" t="n">
-        <v>558000</v>
+        <v>574000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -36575,7 +36575,7 @@
         <v>80</v>
       </c>
       <c r="F84" t="n">
-        <v>773000</v>
+        <v>760000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>60</v>
       </c>
       <c r="F86" t="n">
-        <v>686000</v>
+        <v>699000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>150</v>
       </c>
       <c r="F88" t="n">
-        <v>485000</v>
+        <v>471000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -36821,7 +36821,7 @@
         <v>80</v>
       </c>
       <c r="F90" t="n">
-        <v>832000</v>
+        <v>862000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>521000</v>
+        <v>548000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>20</v>
       </c>
       <c r="F93" t="n">
-        <v>420000</v>
+        <v>432000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>40</v>
       </c>
       <c r="F97" t="n">
-        <v>497000</v>
+        <v>525000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37149,7 +37149,7 @@
         <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>1128000</v>
+        <v>1163000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37190,7 +37190,7 @@
         <v>1010</v>
       </c>
       <c r="F99" t="n">
-        <v>939000</v>
+        <v>962000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>100</v>
       </c>
       <c r="F100" t="n">
-        <v>673000</v>
+        <v>667000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -37272,7 +37272,7 @@
         <v>80</v>
       </c>
       <c r="F101" t="n">
-        <v>750000</v>
+        <v>772000</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>150</v>
       </c>
       <c r="F102" t="n">
-        <v>761000</v>
+        <v>737000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -37354,7 +37354,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>903000</v>
+        <v>959000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37559,7 +37559,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>645000</v>
+        <v>654000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -37805,7 +37805,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>500000</v>
+        <v>541000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -37928,7 +37928,7 @@
         <v>50</v>
       </c>
       <c r="F117" t="n">
-        <v>423000</v>
+        <v>465000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -38010,7 +38010,7 @@
         <v>40</v>
       </c>
       <c r="F119" t="n">
-        <v>563000</v>
+        <v>537000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="n">
-        <v>708000</v>
+        <v>700000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>1000</v>
       </c>
       <c r="F132" t="n">
-        <v>404000</v>
+        <v>446000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38666,7 +38666,7 @@
         <v>120</v>
       </c>
       <c r="F135" t="n">
-        <v>577000</v>
+        <v>600000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>1000</v>
       </c>
       <c r="F139" t="n">
-        <v>310000</v>
+        <v>347000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -38871,7 +38871,7 @@
         <v>150</v>
       </c>
       <c r="F140" t="n">
-        <v>488000</v>
+        <v>461000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -38953,7 +38953,7 @@
         <v>80</v>
       </c>
       <c r="F142" t="n">
-        <v>261000</v>
+        <v>317000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>303000</v>
+        <v>343000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>30</v>
       </c>
       <c r="F145" t="n">
-        <v>383000</v>
+        <v>399000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39199,7 +39199,7 @@
         <v>150</v>
       </c>
       <c r="F148" t="n">
-        <v>777000</v>
+        <v>758000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>150</v>
       </c>
       <c r="F151" t="n">
-        <v>580000</v>
+        <v>546000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -39363,7 +39363,7 @@
         <v>40</v>
       </c>
       <c r="F152" t="n">
-        <v>255000</v>
+        <v>277000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -39743,7 +39743,7 @@
         <v>1000</v>
       </c>
       <c r="F5" t="n">
-        <v>638000</v>
+        <v>579000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>997000</v>
+        <v>958000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -39907,7 +39907,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>873000</v>
+        <v>822000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -39948,7 +39948,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>597000</v>
+        <v>607000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -39989,7 +39989,7 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>629000</v>
+        <v>624000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -40030,7 +40030,7 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>831000</v>
+        <v>806000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>780000</v>
+        <v>790000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>541000</v>
+        <v>504000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -40194,7 +40194,7 @@
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>294000</v>
+        <v>317000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -40235,7 +40235,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>595000</v>
+        <v>606000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -40276,7 +40276,7 @@
         <v>80</v>
       </c>
       <c r="F18" t="n">
-        <v>521000</v>
+        <v>518000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>1010</v>
       </c>
       <c r="F22" t="n">
-        <v>742000</v>
+        <v>734000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>987000</v>
+        <v>998000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40522,7 +40522,7 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>561000</v>
+        <v>558000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -40727,7 +40727,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>682000</v>
+        <v>649000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>821000</v>
+        <v>829000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8222,7 +8222,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>963000</v>
+        <v>929000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
         <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>508000</v>
+        <v>497000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>934000</v>
+        <v>949000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>697000</v>
+        <v>688000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>694000</v>
+        <v>665000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8509,7 +8509,7 @@
         <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>696000</v>
+        <v>690000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>508000</v>
+        <v>498000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>938000</v>
+        <v>905000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>609000</v>
+        <v>601000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>445000</v>
+        <v>449000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>600000</v>
+        <v>608000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>922000</v>
+        <v>906000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>513000</v>
+        <v>507000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>384000</v>
+        <v>348000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>695000</v>
+        <v>688000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>596000</v>
+        <v>567000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>816000</v>
+        <v>769000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9165,7 +9165,7 @@
         <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>442000</v>
+        <v>434000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -9206,7 +9206,7 @@
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>573000</v>
+        <v>584000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>130</v>
       </c>
       <c r="F28" t="n">
-        <v>887000</v>
+        <v>938000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
         <v>80</v>
       </c>
       <c r="F29" t="n">
-        <v>871000</v>
+        <v>819000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>817000</v>
+        <v>776000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>896000</v>
+        <v>910000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>739000</v>
+        <v>729000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>1010</v>
       </c>
       <c r="F33" t="n">
-        <v>587000</v>
+        <v>555000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>579000</v>
+        <v>574000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
         <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>355000</v>
+        <v>351000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>314000</v>
+        <v>296000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>580000</v>
+        <v>615000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>880000</v>
+        <v>872000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>473000</v>
+        <v>469000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>40</v>
       </c>
       <c r="F41" t="n">
-        <v>717000</v>
+        <v>714000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
         <v>140</v>
       </c>
       <c r="F43" t="n">
-        <v>784000</v>
+        <v>704000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>634000</v>
+        <v>667000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>701000</v>
+        <v>730000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>894000</v>
+        <v>901000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
         <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>765000</v>
+        <v>780000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>581000</v>
+        <v>592000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>140</v>
       </c>
       <c r="F54" t="n">
-        <v>960000</v>
+        <v>977000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>60</v>
       </c>
       <c r="F56" t="n">
-        <v>520000</v>
+        <v>494000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>776000</v>
+        <v>763000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>622000</v>
+        <v>607000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10682,7 +10682,7 @@
         <v>30</v>
       </c>
       <c r="F62" t="n">
-        <v>692000</v>
+        <v>675000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -10846,7 +10846,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>649000</v>
+        <v>647000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>90</v>
       </c>
       <c r="F67" t="n">
-        <v>605000</v>
+        <v>606000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>806000</v>
+        <v>772000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>992000</v>
+        <v>956000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
         <v>150</v>
       </c>
       <c r="F70" t="n">
-        <v>575000</v>
+        <v>581000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>130</v>
       </c>
       <c r="F74" t="n">
-        <v>649000</v>
+        <v>640000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11379,7 +11379,7 @@
         <v>110</v>
       </c>
       <c r="F79" t="n">
-        <v>789000</v>
+        <v>762000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         <v>150</v>
       </c>
       <c r="F81" t="n">
-        <v>436000</v>
+        <v>455000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11502,7 +11502,7 @@
         <v>120</v>
       </c>
       <c r="F82" t="n">
-        <v>569000</v>
+        <v>551000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -11666,7 +11666,7 @@
         <v>110</v>
       </c>
       <c r="F86" t="n">
-        <v>509000</v>
+        <v>471000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
         <v>70</v>
       </c>
       <c r="F88" t="n">
-        <v>655000</v>
+        <v>632000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>487000</v>
+        <v>513000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>913000</v>
+        <v>960000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11953,7 +11953,7 @@
         <v>1010</v>
       </c>
       <c r="F93" t="n">
-        <v>522000</v>
+        <v>538000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>1000</v>
       </c>
       <c r="F95" t="n">
-        <v>732000</v>
+        <v>737000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>160</v>
       </c>
       <c r="F96" t="n">
-        <v>837000</v>
+        <v>826000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>749000</v>
+        <v>757000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>1000</v>
       </c>
       <c r="F103" t="n">
-        <v>653000</v>
+        <v>639000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>160</v>
       </c>
       <c r="F106" t="n">
-        <v>744000</v>
+        <v>740000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12609,7 +12609,7 @@
         <v>130</v>
       </c>
       <c r="F109" t="n">
-        <v>408000</v>
+        <v>429000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>520000</v>
+        <v>503000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>110</v>
       </c>
       <c r="F113" t="n">
-        <v>603000</v>
+        <v>621000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
         <v>70</v>
       </c>
       <c r="F114" t="n">
-        <v>545000</v>
+        <v>521000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -12855,7 +12855,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>967000</v>
+        <v>964000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>744000</v>
+        <v>732000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>50</v>
       </c>
       <c r="F117" t="n">
-        <v>634000</v>
+        <v>613000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -13101,7 +13101,7 @@
         <v>110</v>
       </c>
       <c r="F121" t="n">
-        <v>487000</v>
+        <v>476000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>805000</v>
+        <v>788000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>130</v>
       </c>
       <c r="F125" t="n">
-        <v>609000</v>
+        <v>611000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>160</v>
       </c>
       <c r="F126" t="n">
-        <v>648000</v>
+        <v>640000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>70</v>
       </c>
       <c r="F127" t="n">
-        <v>737000</v>
+        <v>713000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>598000</v>
+        <v>568000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>90</v>
       </c>
       <c r="F129" t="n">
-        <v>815000</v>
+        <v>845000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>599000</v>
+        <v>604000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>60</v>
       </c>
       <c r="F133" t="n">
-        <v>574000</v>
+        <v>541000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>808000</v>
+        <v>814000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>70</v>
       </c>
       <c r="F138" t="n">
-        <v>800000</v>
+        <v>785000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>649000</v>
+        <v>621000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>586000</v>
+        <v>590000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>130</v>
       </c>
       <c r="F142" t="n">
-        <v>1100000</v>
+        <v>1138000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>1000</v>
       </c>
       <c r="F143" t="n">
-        <v>381000</v>
+        <v>360000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>100</v>
       </c>
       <c r="F144" t="n">
-        <v>555000</v>
+        <v>539000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>100</v>
       </c>
       <c r="F146" t="n">
-        <v>624000</v>
+        <v>590000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>70</v>
       </c>
       <c r="F147" t="n">
-        <v>970000</v>
+        <v>985000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14249,7 +14249,7 @@
         <v>140</v>
       </c>
       <c r="F149" t="n">
-        <v>501000</v>
+        <v>460000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="F150" t="n">
-        <v>445000</v>
+        <v>449000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>20</v>
       </c>
       <c r="F152" t="n">
-        <v>904000</v>
+        <v>872000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>557000</v>
+        <v>552000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>160</v>
       </c>
       <c r="F156" t="n">
-        <v>725000</v>
+        <v>699000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>90</v>
       </c>
       <c r="F158" t="n">
-        <v>597000</v>
+        <v>605000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>743000</v>
+        <v>741000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14700,7 +14700,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>801000</v>
+        <v>808000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>548000</v>
+        <v>550000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>150</v>
       </c>
       <c r="F162" t="n">
-        <v>424000</v>
+        <v>434000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>354000</v>
+        <v>348000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>689000</v>
+        <v>687000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>140</v>
       </c>
       <c r="F170" t="n">
-        <v>472000</v>
+        <v>495000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>664000</v>
+        <v>680000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         <v>60</v>
       </c>
       <c r="F174" t="n">
-        <v>751000</v>
+        <v>765000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>10</v>
       </c>
       <c r="F175" t="n">
-        <v>580000</v>
+        <v>606000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>30</v>
       </c>
       <c r="F176" t="n">
-        <v>644000</v>
+        <v>629000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15397,7 +15397,7 @@
         <v>80</v>
       </c>
       <c r="F177" t="n">
-        <v>257000</v>
+        <v>270000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>140</v>
       </c>
       <c r="F181" t="n">
-        <v>437000</v>
+        <v>438000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15684,7 +15684,7 @@
         <v>150</v>
       </c>
       <c r="F184" t="n">
-        <v>465000</v>
+        <v>476000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>130</v>
       </c>
       <c r="F186" t="n">
-        <v>775000</v>
+        <v>809000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15889,7 +15889,7 @@
         <v>30</v>
       </c>
       <c r="F189" t="n">
-        <v>721000</v>
+        <v>695000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -15930,7 +15930,7 @@
         <v>50</v>
       </c>
       <c r="F190" t="n">
-        <v>942000</v>
+        <v>863000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -16012,7 +16012,7 @@
         <v>100</v>
       </c>
       <c r="F192" t="n">
-        <v>451000</v>
+        <v>447000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>20</v>
       </c>
       <c r="F193" t="n">
-        <v>620000</v>
+        <v>658000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>50</v>
       </c>
       <c r="F195" t="n">
-        <v>653000</v>
+        <v>631000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>30</v>
       </c>
       <c r="F199" t="n">
-        <v>654000</v>
+        <v>663000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>90</v>
       </c>
       <c r="F200" t="n">
-        <v>546000</v>
+        <v>530000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -16381,7 +16381,7 @@
         <v>130</v>
       </c>
       <c r="F201" t="n">
-        <v>434000</v>
+        <v>443000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16422,7 +16422,7 @@
         <v>70</v>
       </c>
       <c r="F202" t="n">
-        <v>643000</v>
+        <v>631000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -16709,7 +16709,7 @@
         <v>50</v>
       </c>
       <c r="F209" t="n">
-        <v>404000</v>
+        <v>388000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -16750,7 +16750,7 @@
         <v>150</v>
       </c>
       <c r="F210" t="n">
-        <v>501000</v>
+        <v>517000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -16832,7 +16832,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>718000</v>
+        <v>692000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>130</v>
       </c>
       <c r="F218" t="n">
-        <v>476000</v>
+        <v>468000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>1010</v>
       </c>
       <c r="F220" t="n">
-        <v>303000</v>
+        <v>319000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>279000</v>
+        <v>329000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>80</v>
       </c>
       <c r="F224" t="n">
-        <v>386000</v>
+        <v>413000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>1000</v>
       </c>
       <c r="F225" t="n">
-        <v>619000</v>
+        <v>690000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>120</v>
       </c>
       <c r="F229" t="n">
-        <v>646000</v>
+        <v>644000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -17693,7 +17693,7 @@
         <v>1010</v>
       </c>
       <c r="F233" t="n">
-        <v>755000</v>
+        <v>754000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>30</v>
       </c>
       <c r="F241" t="n">
-        <v>504000</v>
+        <v>516000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>354000</v>
+        <v>374000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18103,7 +18103,7 @@
         <v>1000</v>
       </c>
       <c r="F243" t="n">
-        <v>332000</v>
+        <v>325000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
         <v>50</v>
       </c>
       <c r="F245" t="n">
-        <v>716000</v>
+        <v>714000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -18226,7 +18226,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>424000</v>
+        <v>447000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>150</v>
       </c>
       <c r="F248" t="n">
-        <v>879000</v>
+        <v>882000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>120</v>
       </c>
       <c r="F250" t="n">
-        <v>508000</v>
+        <v>498000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>50</v>
       </c>
       <c r="F251" t="n">
-        <v>307000</v>
+        <v>319000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         <v>160</v>
       </c>
       <c r="F252" t="n">
-        <v>350000</v>
+        <v>370000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>110</v>
       </c>
       <c r="F258" t="n">
-        <v>504000</v>
+        <v>525000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>663000</v>
+        <v>682000</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -19098,7 +19098,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>477000</v>
+        <v>519000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>446000</v>
+        <v>429000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19180,7 +19180,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>644000</v>
+        <v>628000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19262,7 +19262,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>579000</v>
+        <v>572000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19303,7 +19303,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>718000</v>
+        <v>713000</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -19467,7 +19467,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>530000</v>
+        <v>516000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19508,7 +19508,7 @@
         <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>665000</v>
+        <v>616000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19631,7 +19631,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>515000</v>
+        <v>483000</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>631000</v>
+        <v>602000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19713,7 +19713,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>582000</v>
+        <v>575000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19754,7 +19754,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>579000</v>
+        <v>608000</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -19836,7 +19836,7 @@
         <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>670000</v>
+        <v>739000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>653000</v>
+        <v>644000</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>1010</v>
       </c>
       <c r="F23" t="n">
-        <v>845000</v>
+        <v>882000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>130</v>
       </c>
       <c r="F24" t="n">
-        <v>879000</v>
+        <v>958000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20000,7 +20000,7 @@
         <v>150</v>
       </c>
       <c r="F25" t="n">
-        <v>801000</v>
+        <v>783000</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>517000</v>
+        <v>486000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>699000</v>
+        <v>690000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>532000</v>
+        <v>552000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20205,7 +20205,7 @@
         <v>1000</v>
       </c>
       <c r="F30" t="n">
-        <v>404000</v>
+        <v>399000</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>580000</v>
+        <v>595000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20287,7 +20287,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>781000</v>
+        <v>754000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>778000</v>
+        <v>782000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20369,7 +20369,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>816000</v>
+        <v>810000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>747000</v>
+        <v>736000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>590000</v>
+        <v>573000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>150</v>
       </c>
       <c r="F41" t="n">
-        <v>710000</v>
+        <v>691000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20697,7 +20697,7 @@
         <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>786000</v>
+        <v>794000</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -20738,7 +20738,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>547000</v>
+        <v>541000</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>130</v>
       </c>
       <c r="F45" t="n">
-        <v>775000</v>
+        <v>838000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>150</v>
       </c>
       <c r="F46" t="n">
-        <v>550000</v>
+        <v>544000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>641000</v>
+        <v>678000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20984,7 +20984,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>629000</v>
+        <v>650000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>499000</v>
+        <v>489000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>60</v>
       </c>
       <c r="F52" t="n">
-        <v>807000</v>
+        <v>812000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21148,7 +21148,7 @@
         <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>708000</v>
+        <v>726000</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>80</v>
       </c>
       <c r="F54" t="n">
-        <v>590000</v>
+        <v>624000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>932000</v>
+        <v>917000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>150</v>
       </c>
       <c r="F57" t="n">
-        <v>779000</v>
+        <v>758000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>160</v>
       </c>
       <c r="F58" t="n">
-        <v>739000</v>
+        <v>776000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21394,7 +21394,7 @@
         <v>160</v>
       </c>
       <c r="F59" t="n">
-        <v>659000</v>
+        <v>606000</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>733000</v>
+        <v>697000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21558,7 +21558,7 @@
         <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>566000</v>
+        <v>590000</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>748000</v>
+        <v>738000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21681,7 +21681,7 @@
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>583000</v>
+        <v>597000</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -21763,7 +21763,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>400000</v>
+        <v>407000</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>140</v>
       </c>
       <c r="F69" t="n">
-        <v>446000</v>
+        <v>444000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>539000</v>
+        <v>561000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21927,7 +21927,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>625000</v>
+        <v>642000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -21968,7 +21968,7 @@
         <v>90</v>
       </c>
       <c r="F73" t="n">
-        <v>865000</v>
+        <v>874000</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -22091,7 +22091,7 @@
         <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>710000</v>
+        <v>673000</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>591000</v>
+        <v>594000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22173,7 +22173,7 @@
         <v>80</v>
       </c>
       <c r="F78" t="n">
-        <v>508000</v>
+        <v>532000</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>70</v>
       </c>
       <c r="F79" t="n">
-        <v>430000</v>
+        <v>390000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>733000</v>
+        <v>704000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22296,7 +22296,7 @@
         <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>538000</v>
+        <v>572000</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>833000</v>
+        <v>852000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>130</v>
       </c>
       <c r="F84" t="n">
-        <v>498000</v>
+        <v>499000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22501,7 +22501,7 @@
         <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>602000</v>
+        <v>650000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22542,7 +22542,7 @@
         <v>120</v>
       </c>
       <c r="F87" t="n">
-        <v>649000</v>
+        <v>645000</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -22624,7 +22624,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>541000</v>
+        <v>554000</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>140</v>
       </c>
       <c r="F91" t="n">
-        <v>535000</v>
+        <v>544000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>684000</v>
+        <v>664000</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -22788,7 +22788,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>730000</v>
+        <v>749000</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -22829,7 +22829,7 @@
         <v>160</v>
       </c>
       <c r="F94" t="n">
-        <v>583000</v>
+        <v>558000</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -22870,7 +22870,7 @@
         <v>110</v>
       </c>
       <c r="F95" t="n">
-        <v>603000</v>
+        <v>568000</v>
       </c>
       <c r="G95" t="n">
         <v>1</v>
@@ -22911,7 +22911,7 @@
         <v>130</v>
       </c>
       <c r="F96" t="n">
-        <v>521000</v>
+        <v>498000</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -22993,7 +22993,7 @@
         <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>536000</v>
+        <v>498000</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -23239,7 +23239,7 @@
         <v>90</v>
       </c>
       <c r="F104" t="n">
-        <v>685000</v>
+        <v>682000</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
         <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>615000</v>
+        <v>635000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>150</v>
       </c>
       <c r="F106" t="n">
-        <v>615000</v>
+        <v>585000</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>130</v>
       </c>
       <c r="F108" t="n">
-        <v>484000</v>
+        <v>472000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23444,7 +23444,7 @@
         <v>150</v>
       </c>
       <c r="F109" t="n">
-        <v>780000</v>
+        <v>776000</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>140</v>
       </c>
       <c r="F111" t="n">
-        <v>556000</v>
+        <v>573000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>1010</v>
       </c>
       <c r="F113" t="n">
-        <v>559000</v>
+        <v>554000</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1000</v>
       </c>
       <c r="F115" t="n">
-        <v>440000</v>
+        <v>417000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>80</v>
       </c>
       <c r="F117" t="n">
-        <v>656000</v>
+        <v>667000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>540000</v>
+        <v>533000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23977,7 +23977,7 @@
         <v>1010</v>
       </c>
       <c r="F122" t="n">
-        <v>594000</v>
+        <v>609000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -24018,7 +24018,7 @@
         <v>30</v>
       </c>
       <c r="F123" t="n">
-        <v>527000</v>
+        <v>548000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24100,7 +24100,7 @@
         <v>110</v>
       </c>
       <c r="F125" t="n">
-        <v>768000</v>
+        <v>750000</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -24141,7 +24141,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>626000</v>
+        <v>620000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>120</v>
       </c>
       <c r="F128" t="n">
-        <v>648000</v>
+        <v>639000</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -24264,7 +24264,7 @@
         <v>110</v>
       </c>
       <c r="F129" t="n">
-        <v>495000</v>
+        <v>477000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24305,7 +24305,7 @@
         <v>90</v>
       </c>
       <c r="F130" t="n">
-        <v>899000</v>
+        <v>888000</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -24387,7 +24387,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>443000</v>
+        <v>422000</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -24551,7 +24551,7 @@
         <v>30</v>
       </c>
       <c r="F136" t="n">
-        <v>618000</v>
+        <v>593000</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -24715,7 +24715,7 @@
         <v>40</v>
       </c>
       <c r="F140" t="n">
-        <v>424000</v>
+        <v>389000</v>
       </c>
       <c r="G140" t="n">
         <v>1</v>
@@ -24838,7 +24838,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>712000</v>
+        <v>663000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24920,7 +24920,7 @@
         <v>60</v>
       </c>
       <c r="F145" t="n">
-        <v>431000</v>
+        <v>433000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -24961,7 +24961,7 @@
         <v>110</v>
       </c>
       <c r="F146" t="n">
-        <v>949000</v>
+        <v>950000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25043,7 +25043,7 @@
         <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>447000</v>
+        <v>439000</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -25084,7 +25084,7 @@
         <v>140</v>
       </c>
       <c r="F149" t="n">
-        <v>429000</v>
+        <v>435000</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -25248,7 +25248,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>943000</v>
+        <v>957000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>60</v>
       </c>
       <c r="F155" t="n">
-        <v>735000</v>
+        <v>736000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25371,7 +25371,7 @@
         <v>90</v>
       </c>
       <c r="F156" t="n">
-        <v>513000</v>
+        <v>485000</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -25494,7 +25494,7 @@
         <v>80</v>
       </c>
       <c r="F159" t="n">
-        <v>800000</v>
+        <v>823000</v>
       </c>
       <c r="G159" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>70</v>
       </c>
       <c r="F160" t="n">
-        <v>527000</v>
+        <v>525000</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
@@ -25740,7 +25740,7 @@
         <v>160</v>
       </c>
       <c r="F165" t="n">
-        <v>576000</v>
+        <v>589000</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>20</v>
       </c>
       <c r="F170" t="n">
-        <v>567000</v>
+        <v>592000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>1010</v>
       </c>
       <c r="F171" t="n">
-        <v>507000</v>
+        <v>533000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26150,7 +26150,7 @@
         <v>50</v>
       </c>
       <c r="F175" t="n">
-        <v>788000</v>
+        <v>800000</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
@@ -26191,7 +26191,7 @@
         <v>50</v>
       </c>
       <c r="F176" t="n">
-        <v>594000</v>
+        <v>582000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>70</v>
       </c>
       <c r="F179" t="n">
-        <v>639000</v>
+        <v>633000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>663000</v>
+        <v>657000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="F182" t="n">
-        <v>583000</v>
+        <v>560000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>80</v>
       </c>
       <c r="F183" t="n">
-        <v>779000</v>
+        <v>796000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26601,7 +26601,7 @@
         <v>40</v>
       </c>
       <c r="F186" t="n">
-        <v>668000</v>
+        <v>679000</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
@@ -26683,7 +26683,7 @@
         <v>110</v>
       </c>
       <c r="F188" t="n">
-        <v>373000</v>
+        <v>360000</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
@@ -26724,7 +26724,7 @@
         <v>30</v>
       </c>
       <c r="F189" t="n">
-        <v>550000</v>
+        <v>595000</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
@@ -26847,7 +26847,7 @@
         <v>90</v>
       </c>
       <c r="F192" t="n">
-        <v>583000</v>
+        <v>672000</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
@@ -26888,7 +26888,7 @@
         <v>60</v>
       </c>
       <c r="F193" t="n">
-        <v>705000</v>
+        <v>679000</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>130</v>
       </c>
       <c r="F196" t="n">
-        <v>566000</v>
+        <v>571000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>10</v>
       </c>
       <c r="F199" t="n">
-        <v>617000</v>
+        <v>600000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27257,7 +27257,7 @@
         <v>1010</v>
       </c>
       <c r="F202" t="n">
-        <v>617000</v>
+        <v>601000</v>
       </c>
       <c r="G202" t="n">
         <v>1</v>
@@ -27339,7 +27339,7 @@
         <v>130</v>
       </c>
       <c r="F204" t="n">
-        <v>636000</v>
+        <v>668000</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -27380,7 +27380,7 @@
         <v>150</v>
       </c>
       <c r="F205" t="n">
-        <v>474000</v>
+        <v>499000</v>
       </c>
       <c r="G205" t="n">
         <v>1</v>
@@ -27421,7 +27421,7 @@
         <v>140</v>
       </c>
       <c r="F206" t="n">
-        <v>517000</v>
+        <v>516000</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -27462,7 +27462,7 @@
         <v>60</v>
       </c>
       <c r="F207" t="n">
-        <v>604000</v>
+        <v>563000</v>
       </c>
       <c r="G207" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>130</v>
       </c>
       <c r="F209" t="n">
-        <v>878000</v>
+        <v>897000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>70</v>
       </c>
       <c r="F211" t="n">
-        <v>408000</v>
+        <v>428000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>100</v>
       </c>
       <c r="F213" t="n">
-        <v>286000</v>
+        <v>304000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n">
-        <v>440000</v>
+        <v>432000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>581000</v>
+        <v>603000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -28077,7 +28077,7 @@
         <v>90</v>
       </c>
       <c r="F222" t="n">
-        <v>327000</v>
+        <v>340000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28282,7 +28282,7 @@
         <v>130</v>
       </c>
       <c r="F227" t="n">
-        <v>567000</v>
+        <v>573000</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>582000</v>
+        <v>590000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>90</v>
       </c>
       <c r="F231" t="n">
-        <v>399000</v>
+        <v>396000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28610,7 +28610,7 @@
         <v>1000</v>
       </c>
       <c r="F235" t="n">
-        <v>478000</v>
+        <v>479000</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
@@ -28651,7 +28651,7 @@
         <v>100</v>
       </c>
       <c r="F236" t="n">
-        <v>1176000</v>
+        <v>1219000</v>
       </c>
       <c r="G236" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>90</v>
       </c>
       <c r="F240" t="n">
-        <v>608000</v>
+        <v>581000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>1000</v>
       </c>
       <c r="F241" t="n">
-        <v>451000</v>
+        <v>446000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>40</v>
       </c>
       <c r="F242" t="n">
-        <v>494000</v>
+        <v>496000</v>
       </c>
       <c r="G242" t="n">
         <v>1</v>
@@ -28938,7 +28938,7 @@
         <v>130</v>
       </c>
       <c r="F243" t="n">
-        <v>380000</v>
+        <v>406000</v>
       </c>
       <c r="G243" t="n">
         <v>1</v>
@@ -28979,7 +28979,7 @@
         <v>130</v>
       </c>
       <c r="F244" t="n">
-        <v>317000</v>
+        <v>354000</v>
       </c>
       <c r="G244" t="n">
         <v>1</v>
@@ -29020,7 +29020,7 @@
         <v>160</v>
       </c>
       <c r="F245" t="n">
-        <v>500000</v>
+        <v>476000</v>
       </c>
       <c r="G245" t="n">
         <v>1</v>
@@ -29061,7 +29061,7 @@
         <v>90</v>
       </c>
       <c r="F246" t="n">
-        <v>275000</v>
+        <v>282000</v>
       </c>
       <c r="G246" t="n">
         <v>1</v>
@@ -29102,7 +29102,7 @@
         <v>100</v>
       </c>
       <c r="F247" t="n">
-        <v>692000</v>
+        <v>706000</v>
       </c>
       <c r="G247" t="n">
         <v>1</v>
@@ -29225,7 +29225,7 @@
         <v>1000</v>
       </c>
       <c r="F250" t="n">
-        <v>455000</v>
+        <v>424000</v>
       </c>
       <c r="G250" t="n">
         <v>1</v>
@@ -29307,7 +29307,7 @@
         <v>1000</v>
       </c>
       <c r="F252" t="n">
-        <v>402000</v>
+        <v>358000</v>
       </c>
       <c r="G252" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>50</v>
       </c>
       <c r="F254" t="n">
-        <v>510000</v>
+        <v>545000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>120</v>
       </c>
       <c r="F255" t="n">
-        <v>230000</v>
+        <v>238000</v>
       </c>
       <c r="G255" t="n">
         <v>1</v>
@@ -29594,7 +29594,7 @@
         <v>160</v>
       </c>
       <c r="F259" t="n">
-        <v>364000</v>
+        <v>386000</v>
       </c>
       <c r="G259" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>140</v>
       </c>
       <c r="F261" t="n">
-        <v>690000</v>
+        <v>669000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>130</v>
       </c>
       <c r="F264" t="n">
-        <v>845000</v>
+        <v>860000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>50</v>
       </c>
       <c r="F266" t="n">
-        <v>544000</v>
+        <v>551000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -29963,7 +29963,7 @@
         <v>1010</v>
       </c>
       <c r="F268" t="n">
-        <v>716000</v>
+        <v>689000</v>
       </c>
       <c r="G268" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>20</v>
       </c>
       <c r="F271" t="n">
-        <v>711000</v>
+        <v>707000</v>
       </c>
       <c r="G271" t="n">
         <v>1</v>
@@ -30250,7 +30250,7 @@
         <v>60</v>
       </c>
       <c r="F275" t="n">
-        <v>822000</v>
+        <v>828000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30332,7 +30332,7 @@
         <v>30</v>
       </c>
       <c r="F277" t="n">
-        <v>734000</v>
+        <v>745000</v>
       </c>
       <c r="G277" t="n">
         <v>1</v>
@@ -30414,7 +30414,7 @@
         <v>110</v>
       </c>
       <c r="F279" t="n">
-        <v>492000</v>
+        <v>467000</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
@@ -30455,7 +30455,7 @@
         <v>120</v>
       </c>
       <c r="F280" t="n">
-        <v>407000</v>
+        <v>401000</v>
       </c>
       <c r="G280" t="n">
         <v>1</v>
@@ -30578,7 +30578,7 @@
         <v>100</v>
       </c>
       <c r="F283" t="n">
-        <v>230000</v>
+        <v>234000</v>
       </c>
       <c r="G283" t="n">
         <v>1</v>
@@ -30619,7 +30619,7 @@
         <v>50</v>
       </c>
       <c r="F284" t="n">
-        <v>389000</v>
+        <v>365000</v>
       </c>
       <c r="G284" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>1010</v>
       </c>
       <c r="F290" t="n">
-        <v>237000</v>
+        <v>271000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>50</v>
       </c>
       <c r="F296" t="n">
-        <v>443000</v>
+        <v>423000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31152,7 +31152,7 @@
         <v>1000</v>
       </c>
       <c r="F297" t="n">
-        <v>543000</v>
+        <v>564000</v>
       </c>
       <c r="G297" t="n">
         <v>1</v>
@@ -31316,7 +31316,7 @@
         <v>140</v>
       </c>
       <c r="F301" t="n">
-        <v>530000</v>
+        <v>541000</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -31685,7 +31685,7 @@
         <v>150</v>
       </c>
       <c r="F310" t="n">
-        <v>490000</v>
+        <v>505000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>100</v>
       </c>
       <c r="F311" t="n">
-        <v>581000</v>
+        <v>591000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31849,7 +31849,7 @@
         <v>1010</v>
       </c>
       <c r="F314" t="n">
-        <v>609000</v>
+        <v>587000</v>
       </c>
       <c r="G314" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>110</v>
       </c>
       <c r="F315" t="n">
-        <v>429000</v>
+        <v>431000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>120</v>
       </c>
       <c r="F317" t="n">
-        <v>469000</v>
+        <v>480000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>140</v>
       </c>
       <c r="F335" t="n">
-        <v>384000</v>
+        <v>395000</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -32751,7 +32751,7 @@
         <v>20</v>
       </c>
       <c r="F336" t="n">
-        <v>497000</v>
+        <v>524000</v>
       </c>
       <c r="G336" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>140</v>
       </c>
       <c r="F339" t="n">
-        <v>536000</v>
+        <v>522000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32956,7 +32956,7 @@
         <v>30</v>
       </c>
       <c r="F341" t="n">
-        <v>417000</v>
+        <v>445000</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>50</v>
       </c>
       <c r="F350" t="n">
-        <v>599000</v>
+        <v>603000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33459,7 +33459,7 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>820000</v>
+        <v>797000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33500,7 +33500,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>617000</v>
+        <v>638000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33541,7 +33541,7 @@
         <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>915000</v>
+        <v>863000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>954000</v>
+        <v>989000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>790000</v>
+        <v>764000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>911000</v>
+        <v>878000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33787,7 +33787,7 @@
         <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>631000</v>
+        <v>601000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>789000</v>
+        <v>809000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -33992,7 +33992,7 @@
         <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>974000</v>
+        <v>973000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>1084000</v>
+        <v>1060000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -34156,7 +34156,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>893000</v>
+        <v>886000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1094000</v>
+        <v>1027000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1153000</v>
+        <v>1141000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34320,7 +34320,7 @@
         <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>839000</v>
+        <v>782000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -34361,7 +34361,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>881000</v>
+        <v>898000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -34443,7 +34443,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>619000</v>
+        <v>623000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>1003000</v>
+        <v>1007000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>685000</v>
+        <v>669000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34607,7 +34607,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>895000</v>
+        <v>904000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>677000</v>
+        <v>654000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>681000</v>
+        <v>694000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34771,7 +34771,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>763000</v>
+        <v>740000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34812,7 +34812,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>745000</v>
+        <v>707000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>861000</v>
+        <v>834000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>971000</v>
+        <v>976000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>761000</v>
+        <v>814000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>859000</v>
+        <v>849000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>663000</v>
+        <v>655000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -35222,7 +35222,7 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>780000</v>
+        <v>756000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>508000</v>
+        <v>490000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35304,7 +35304,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>753000</v>
+        <v>754000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>906000</v>
+        <v>911000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35427,7 +35427,7 @@
         <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>691000</v>
+        <v>670000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>617000</v>
+        <v>606000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>818000</v>
+        <v>826000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35878,7 +35878,7 @@
         <v>1000</v>
       </c>
       <c r="F61" t="n">
-        <v>1071000</v>
+        <v>1055000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>878000</v>
+        <v>865000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -36001,7 +36001,7 @@
         <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>519000</v>
+        <v>535000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>805000</v>
+        <v>816000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -36206,7 +36206,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>484000</v>
+        <v>479000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>898000</v>
+        <v>915000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>160</v>
       </c>
       <c r="F71" t="n">
-        <v>1031000</v>
+        <v>1003000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36329,7 +36329,7 @@
         <v>60</v>
       </c>
       <c r="F72" t="n">
-        <v>646000</v>
+        <v>633000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>566000</v>
+        <v>557000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -36493,7 +36493,7 @@
         <v>150</v>
       </c>
       <c r="F76" t="n">
-        <v>375000</v>
+        <v>442000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -36575,7 +36575,7 @@
         <v>60</v>
       </c>
       <c r="F78" t="n">
-        <v>574000</v>
+        <v>587000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="n">
-        <v>390000</v>
+        <v>481000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>776000</v>
+        <v>801000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>120</v>
       </c>
       <c r="F82" t="n">
-        <v>693000</v>
+        <v>671000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>683000</v>
+        <v>676000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36821,7 +36821,7 @@
         <v>160</v>
       </c>
       <c r="F84" t="n">
-        <v>652000</v>
+        <v>645000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>80</v>
       </c>
       <c r="F87" t="n">
-        <v>873000</v>
+        <v>858000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -36985,7 +36985,7 @@
         <v>70</v>
       </c>
       <c r="F88" t="n">
-        <v>488000</v>
+        <v>491000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>1010</v>
       </c>
       <c r="F90" t="n">
-        <v>602000</v>
+        <v>603000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37190,7 +37190,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>566000</v>
+        <v>617000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>1176000</v>
+        <v>1164000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37272,7 +37272,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>968000</v>
+        <v>957000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -37354,7 +37354,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>747000</v>
+        <v>722000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>150</v>
       </c>
       <c r="F98" t="n">
-        <v>718000</v>
+        <v>717000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>20</v>
       </c>
       <c r="F99" t="n">
-        <v>1014000</v>
+        <v>1076000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>657000</v>
+        <v>666000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>70</v>
       </c>
       <c r="F106" t="n">
-        <v>693000</v>
+        <v>707000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37846,7 +37846,7 @@
         <v>120</v>
       </c>
       <c r="F109" t="n">
-        <v>557000</v>
+        <v>570000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -37887,7 +37887,7 @@
         <v>150</v>
       </c>
       <c r="F110" t="n">
-        <v>278000</v>
+        <v>344000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>130</v>
       </c>
       <c r="F115" t="n">
-        <v>882000</v>
+        <v>925000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>1010</v>
       </c>
       <c r="F118" t="n">
-        <v>239000</v>
+        <v>266000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38256,7 +38256,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>616000</v>
+        <v>598000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>715000</v>
+        <v>725000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>466000</v>
+        <v>473000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38666,7 +38666,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>608000</v>
+        <v>616000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>140</v>
       </c>
       <c r="F131" t="n">
-        <v>290000</v>
+        <v>308000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>1000</v>
       </c>
       <c r="F133" t="n">
-        <v>410000</v>
+        <v>467000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38871,7 +38871,7 @@
         <v>150</v>
       </c>
       <c r="F134" t="n">
-        <v>432000</v>
+        <v>419000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>351000</v>
+        <v>372000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -39076,7 +39076,7 @@
         <v>30</v>
       </c>
       <c r="F139" t="n">
-        <v>413000</v>
+        <v>422000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -39117,7 +39117,7 @@
         <v>80</v>
       </c>
       <c r="F140" t="n">
-        <v>230000</v>
+        <v>250000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -39199,7 +39199,7 @@
         <v>150</v>
       </c>
       <c r="F142" t="n">
-        <v>731000</v>
+        <v>724000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>150</v>
       </c>
       <c r="F145" t="n">
-        <v>521000</v>
+        <v>493000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39363,7 +39363,7 @@
         <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>318000</v>
+        <v>363000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>1037000</v>
+        <v>1029000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>955000</v>
+        <v>946000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -39825,7 +39825,7 @@
         <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>511000</v>
+        <v>523000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -39907,7 +39907,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>806000</v>
+        <v>788000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -39948,7 +39948,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>606000</v>
+        <v>603000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -40030,7 +40030,7 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>773000</v>
+        <v>785000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>787000</v>
+        <v>773000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40235,7 +40235,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>627000</v>
+        <v>690000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -40399,7 +40399,7 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>869000</v>
+        <v>892000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>1010</v>
       </c>
       <c r="F22" t="n">
-        <v>727000</v>
+        <v>768000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>999000</v>
+        <v>981000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40522,7 +40522,7 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>563000</v>
+        <v>560000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -40727,7 +40727,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>651000</v>
+        <v>673000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>839000</v>
+        <v>838000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -41178,7 +41178,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>230000</v>
+        <v>262000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8222,7 +8222,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>929000</v>
+        <v>879000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
         <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>497000</v>
+        <v>469000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>949000</v>
+        <v>926000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>665000</v>
+        <v>651000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8509,7 +8509,7 @@
         <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>690000</v>
+        <v>695000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>160</v>
       </c>
       <c r="F10" t="n">
-        <v>498000</v>
+        <v>464000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>1010</v>
       </c>
       <c r="F13" t="n">
-        <v>933000</v>
+        <v>903000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>601000</v>
+        <v>620000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>449000</v>
+        <v>457000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>608000</v>
+        <v>585000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>906000</v>
+        <v>889000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>507000</v>
+        <v>504000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>688000</v>
+        <v>682000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>567000</v>
+        <v>569000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>769000</v>
+        <v>787000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9206,7 +9206,7 @@
         <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>584000</v>
+        <v>563000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>130</v>
       </c>
       <c r="F28" t="n">
-        <v>938000</v>
+        <v>935000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>776000</v>
+        <v>761000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>910000</v>
+        <v>913000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>729000</v>
+        <v>742000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>1010</v>
       </c>
       <c r="F33" t="n">
-        <v>555000</v>
+        <v>534000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>574000</v>
+        <v>567000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
         <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>351000</v>
+        <v>342000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>296000</v>
+        <v>304000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>615000</v>
+        <v>643000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>872000</v>
+        <v>897000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>469000</v>
+        <v>454000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>40</v>
       </c>
       <c r="F41" t="n">
-        <v>714000</v>
+        <v>706000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>817000</v>
+        <v>774000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
         <v>140</v>
       </c>
       <c r="F43" t="n">
-        <v>704000</v>
+        <v>687000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>667000</v>
+        <v>686000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>730000</v>
+        <v>764000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>901000</v>
+        <v>914000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
         <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>780000</v>
+        <v>817000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>592000</v>
+        <v>620000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>60</v>
       </c>
       <c r="F56" t="n">
-        <v>494000</v>
+        <v>466000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>763000</v>
+        <v>760000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>607000</v>
+        <v>595000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10682,7 +10682,7 @@
         <v>30</v>
       </c>
       <c r="F62" t="n">
-        <v>675000</v>
+        <v>671000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>80</v>
       </c>
       <c r="F64" t="n">
-        <v>726000</v>
+        <v>734000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10846,7 +10846,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>647000</v>
+        <v>649000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>90</v>
       </c>
       <c r="F67" t="n">
-        <v>606000</v>
+        <v>585000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>772000</v>
+        <v>743000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>956000</v>
+        <v>938000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11010,7 +11010,7 @@
         <v>150</v>
       </c>
       <c r="F70" t="n">
-        <v>581000</v>
+        <v>568000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
         <v>1000</v>
       </c>
       <c r="F72" t="n">
-        <v>743000</v>
+        <v>730000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>657000</v>
+        <v>630000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>130</v>
       </c>
       <c r="F74" t="n">
-        <v>640000</v>
+        <v>631000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         <v>150</v>
       </c>
       <c r="F81" t="n">
-        <v>455000</v>
+        <v>473000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
         <v>110</v>
       </c>
       <c r="F85" t="n">
-        <v>458000</v>
+        <v>429000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11666,7 +11666,7 @@
         <v>110</v>
       </c>
       <c r="F86" t="n">
-        <v>471000</v>
+        <v>436000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
         <v>70</v>
       </c>
       <c r="F88" t="n">
-        <v>632000</v>
+        <v>619000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>513000</v>
+        <v>553000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>960000</v>
+        <v>970000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11953,7 +11953,7 @@
         <v>1010</v>
       </c>
       <c r="F93" t="n">
-        <v>538000</v>
+        <v>557000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         <v>140</v>
       </c>
       <c r="F94" t="n">
-        <v>602000</v>
+        <v>568000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>1000</v>
       </c>
       <c r="F95" t="n">
-        <v>737000</v>
+        <v>717000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>160</v>
       </c>
       <c r="F96" t="n">
-        <v>826000</v>
+        <v>807000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>757000</v>
+        <v>760000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>70</v>
       </c>
       <c r="F102" t="n">
-        <v>551000</v>
+        <v>563000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>1000</v>
       </c>
       <c r="F103" t="n">
-        <v>639000</v>
+        <v>659000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>1010</v>
       </c>
       <c r="F104" t="n">
-        <v>791000</v>
+        <v>787000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>699000</v>
+        <v>677000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>160</v>
       </c>
       <c r="F106" t="n">
-        <v>740000</v>
+        <v>748000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>160</v>
       </c>
       <c r="F107" t="n">
-        <v>744000</v>
+        <v>733000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12609,7 +12609,7 @@
         <v>130</v>
       </c>
       <c r="F109" t="n">
-        <v>429000</v>
+        <v>472000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>503000</v>
+        <v>469000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>110</v>
       </c>
       <c r="F113" t="n">
-        <v>621000</v>
+        <v>643000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -12814,7 +12814,7 @@
         <v>70</v>
       </c>
       <c r="F114" t="n">
-        <v>521000</v>
+        <v>517000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -12855,7 +12855,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>964000</v>
+        <v>951000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>732000</v>
+        <v>743000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -13101,7 +13101,7 @@
         <v>110</v>
       </c>
       <c r="F121" t="n">
-        <v>476000</v>
+        <v>482000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>788000</v>
+        <v>752000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>130</v>
       </c>
       <c r="F125" t="n">
-        <v>611000</v>
+        <v>610000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>160</v>
       </c>
       <c r="F126" t="n">
-        <v>640000</v>
+        <v>646000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>568000</v>
+        <v>543000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>90</v>
       </c>
       <c r="F129" t="n">
-        <v>845000</v>
+        <v>875000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>604000</v>
+        <v>579000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>60</v>
       </c>
       <c r="F133" t="n">
-        <v>541000</v>
+        <v>526000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>814000</v>
+        <v>835000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>70</v>
       </c>
       <c r="F138" t="n">
-        <v>785000</v>
+        <v>790000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>621000</v>
+        <v>584000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>590000</v>
+        <v>598000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>130</v>
       </c>
       <c r="F142" t="n">
-        <v>1138000</v>
+        <v>1125000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>1000</v>
       </c>
       <c r="F143" t="n">
-        <v>360000</v>
+        <v>349000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>100</v>
       </c>
       <c r="F144" t="n">
-        <v>539000</v>
+        <v>516000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>1010</v>
       </c>
       <c r="F145" t="n">
-        <v>443000</v>
+        <v>455000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>70</v>
       </c>
       <c r="F147" t="n">
-        <v>985000</v>
+        <v>964000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="F150" t="n">
-        <v>449000</v>
+        <v>439000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>20</v>
       </c>
       <c r="F152" t="n">
-        <v>872000</v>
+        <v>843000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>552000</v>
+        <v>558000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>160</v>
       </c>
       <c r="F156" t="n">
-        <v>699000</v>
+        <v>667000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>100</v>
       </c>
       <c r="F157" t="n">
-        <v>309000</v>
+        <v>349000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>741000</v>
+        <v>735000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14700,7 +14700,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>808000</v>
+        <v>821000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>550000</v>
+        <v>547000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>150</v>
       </c>
       <c r="F162" t="n">
-        <v>434000</v>
+        <v>437000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>40</v>
       </c>
       <c r="F163" t="n">
-        <v>230000</v>
+        <v>238000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>348000</v>
+        <v>331000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14905,7 +14905,7 @@
         <v>150</v>
       </c>
       <c r="F165" t="n">
-        <v>560000</v>
+        <v>557000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>687000</v>
+        <v>695000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>140</v>
       </c>
       <c r="F170" t="n">
-        <v>495000</v>
+        <v>523000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>680000</v>
+        <v>646000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         <v>60</v>
       </c>
       <c r="F174" t="n">
-        <v>765000</v>
+        <v>775000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>10</v>
       </c>
       <c r="F175" t="n">
-        <v>606000</v>
+        <v>624000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>30</v>
       </c>
       <c r="F176" t="n">
-        <v>629000</v>
+        <v>619000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15397,7 +15397,7 @@
         <v>80</v>
       </c>
       <c r="F177" t="n">
-        <v>270000</v>
+        <v>301000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>140</v>
       </c>
       <c r="F181" t="n">
-        <v>438000</v>
+        <v>456000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15684,7 +15684,7 @@
         <v>150</v>
       </c>
       <c r="F184" t="n">
-        <v>476000</v>
+        <v>474000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>130</v>
       </c>
       <c r="F186" t="n">
-        <v>809000</v>
+        <v>827000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>532000</v>
+        <v>582000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -15930,7 +15930,7 @@
         <v>50</v>
       </c>
       <c r="F190" t="n">
-        <v>863000</v>
+        <v>817000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -16012,7 +16012,7 @@
         <v>100</v>
       </c>
       <c r="F192" t="n">
-        <v>447000</v>
+        <v>449000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>20</v>
       </c>
       <c r="F193" t="n">
-        <v>658000</v>
+        <v>670000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -16094,7 +16094,7 @@
         <v>70</v>
       </c>
       <c r="F194" t="n">
-        <v>535000</v>
+        <v>540000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>50</v>
       </c>
       <c r="F195" t="n">
-        <v>631000</v>
+        <v>624000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>30</v>
       </c>
       <c r="F199" t="n">
-        <v>663000</v>
+        <v>670000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>90</v>
       </c>
       <c r="F200" t="n">
-        <v>530000</v>
+        <v>506000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -16422,7 +16422,7 @@
         <v>70</v>
       </c>
       <c r="F202" t="n">
-        <v>631000</v>
+        <v>620000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>80</v>
       </c>
       <c r="F204" t="n">
-        <v>660000</v>
+        <v>683000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -16750,7 +16750,7 @@
         <v>150</v>
       </c>
       <c r="F210" t="n">
-        <v>517000</v>
+        <v>520000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -16832,7 +16832,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>692000</v>
+        <v>681000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>130</v>
       </c>
       <c r="F218" t="n">
-        <v>468000</v>
+        <v>453000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>329000</v>
+        <v>400000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>80</v>
       </c>
       <c r="F224" t="n">
-        <v>413000</v>
+        <v>452000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>1000</v>
       </c>
       <c r="F225" t="n">
-        <v>690000</v>
+        <v>735000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>120</v>
       </c>
       <c r="F229" t="n">
-        <v>644000</v>
+        <v>607000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>110</v>
       </c>
       <c r="F232" t="n">
-        <v>230000</v>
+        <v>241000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17693,7 +17693,7 @@
         <v>1010</v>
       </c>
       <c r="F233" t="n">
-        <v>754000</v>
+        <v>734000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -17775,7 +17775,7 @@
         <v>50</v>
       </c>
       <c r="F235" t="n">
-        <v>230000</v>
+        <v>235000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>140</v>
       </c>
       <c r="F236" t="n">
-        <v>415000</v>
+        <v>398000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>30</v>
       </c>
       <c r="F241" t="n">
-        <v>516000</v>
+        <v>518000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>374000</v>
+        <v>383000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18103,7 +18103,7 @@
         <v>1000</v>
       </c>
       <c r="F243" t="n">
-        <v>325000</v>
+        <v>324000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
         <v>50</v>
       </c>
       <c r="F245" t="n">
-        <v>714000</v>
+        <v>715000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -18226,7 +18226,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>447000</v>
+        <v>462000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>150</v>
       </c>
       <c r="F248" t="n">
-        <v>882000</v>
+        <v>871000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>120</v>
       </c>
       <c r="F250" t="n">
-        <v>498000</v>
+        <v>484000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>50</v>
       </c>
       <c r="F251" t="n">
-        <v>319000</v>
+        <v>327000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>110</v>
       </c>
       <c r="F258" t="n">
-        <v>525000</v>
+        <v>529000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>682000</v>
+        <v>661000</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>429000</v>
+        <v>408000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19180,7 +19180,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>628000</v>
+        <v>636000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19262,7 +19262,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>572000</v>
+        <v>563000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19303,7 +19303,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>713000</v>
+        <v>686000</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -19467,7 +19467,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>516000</v>
+        <v>528000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19508,7 +19508,7 @@
         <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>616000</v>
+        <v>563000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19631,7 +19631,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>483000</v>
+        <v>447000</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -19713,7 +19713,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>575000</v>
+        <v>592000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19754,7 +19754,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>608000</v>
+        <v>628000</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -19836,7 +19836,7 @@
         <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>739000</v>
+        <v>784000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>644000</v>
+        <v>611000</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>1010</v>
       </c>
       <c r="F23" t="n">
-        <v>882000</v>
+        <v>858000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>130</v>
       </c>
       <c r="F24" t="n">
-        <v>958000</v>
+        <v>995000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20000,7 +20000,7 @@
         <v>150</v>
       </c>
       <c r="F25" t="n">
-        <v>783000</v>
+        <v>773000</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>690000</v>
+        <v>693000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>552000</v>
+        <v>571000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>595000</v>
+        <v>594000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20287,7 +20287,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>754000</v>
+        <v>740000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>782000</v>
+        <v>776000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20369,7 +20369,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>810000</v>
+        <v>836000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>736000</v>
+        <v>708000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20574,7 +20574,7 @@
         <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>691000</v>
+        <v>647000</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>573000</v>
+        <v>558000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>150</v>
       </c>
       <c r="F41" t="n">
-        <v>691000</v>
+        <v>676000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20697,7 +20697,7 @@
         <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>794000</v>
+        <v>790000</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -20738,7 +20738,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>541000</v>
+        <v>529000</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>130</v>
       </c>
       <c r="F45" t="n">
-        <v>838000</v>
+        <v>916000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>150</v>
       </c>
       <c r="F46" t="n">
-        <v>544000</v>
+        <v>525000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>678000</v>
+        <v>683000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>1000</v>
       </c>
       <c r="F48" t="n">
-        <v>539000</v>
+        <v>530000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -20984,7 +20984,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>650000</v>
+        <v>661000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>489000</v>
+        <v>478000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21148,7 +21148,7 @@
         <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>726000</v>
+        <v>752000</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>80</v>
       </c>
       <c r="F54" t="n">
-        <v>624000</v>
+        <v>628000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>917000</v>
+        <v>906000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>150</v>
       </c>
       <c r="F57" t="n">
-        <v>758000</v>
+        <v>735000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>160</v>
       </c>
       <c r="F58" t="n">
-        <v>776000</v>
+        <v>759000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21394,7 +21394,7 @@
         <v>160</v>
       </c>
       <c r="F59" t="n">
-        <v>606000</v>
+        <v>607000</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>697000</v>
+        <v>649000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21558,7 +21558,7 @@
         <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>590000</v>
+        <v>580000</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>738000</v>
+        <v>732000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21681,7 +21681,7 @@
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>597000</v>
+        <v>610000</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -21763,7 +21763,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>407000</v>
+        <v>406000</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>140</v>
       </c>
       <c r="F69" t="n">
-        <v>444000</v>
+        <v>453000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>561000</v>
+        <v>584000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>455000</v>
+        <v>476000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21927,7 +21927,7 @@
         <v>10</v>
       </c>
       <c r="F72" t="n">
-        <v>642000</v>
+        <v>671000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -21968,7 +21968,7 @@
         <v>90</v>
       </c>
       <c r="F73" t="n">
-        <v>874000</v>
+        <v>909000</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>594000</v>
+        <v>569000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22173,7 +22173,7 @@
         <v>80</v>
       </c>
       <c r="F78" t="n">
-        <v>532000</v>
+        <v>578000</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>70</v>
       </c>
       <c r="F79" t="n">
-        <v>390000</v>
+        <v>391000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>704000</v>
+        <v>626000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22296,7 +22296,7 @@
         <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>572000</v>
+        <v>588000</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>852000</v>
+        <v>869000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>560000</v>
+        <v>581000</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>130</v>
       </c>
       <c r="F84" t="n">
-        <v>499000</v>
+        <v>500000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22501,7 +22501,7 @@
         <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>650000</v>
+        <v>690000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22542,7 +22542,7 @@
         <v>120</v>
       </c>
       <c r="F87" t="n">
-        <v>645000</v>
+        <v>616000</v>
       </c>
       <c r="G87" t="n">
         <v>1</v>
@@ -22624,7 +22624,7 @@
         <v>100</v>
       </c>
       <c r="F89" t="n">
-        <v>554000</v>
+        <v>559000</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -22665,7 +22665,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>885000</v>
+        <v>898000</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>140</v>
       </c>
       <c r="F91" t="n">
-        <v>544000</v>
+        <v>548000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>664000</v>
+        <v>658000</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -22788,7 +22788,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>749000</v>
+        <v>755000</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -22829,7 +22829,7 @@
         <v>160</v>
       </c>
       <c r="F94" t="n">
-        <v>558000</v>
+        <v>511000</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -22911,7 +22911,7 @@
         <v>130</v>
       </c>
       <c r="F96" t="n">
-        <v>498000</v>
+        <v>484000</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -22993,7 +22993,7 @@
         <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>498000</v>
+        <v>485000</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>110</v>
       </c>
       <c r="F101" t="n">
-        <v>448000</v>
+        <v>432000</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -23239,7 +23239,7 @@
         <v>90</v>
       </c>
       <c r="F104" t="n">
-        <v>682000</v>
+        <v>671000</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
         <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>635000</v>
+        <v>638000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>150</v>
       </c>
       <c r="F106" t="n">
-        <v>585000</v>
+        <v>570000</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -23362,7 +23362,7 @@
         <v>160</v>
       </c>
       <c r="F107" t="n">
-        <v>417000</v>
+        <v>378000</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>130</v>
       </c>
       <c r="F108" t="n">
-        <v>472000</v>
+        <v>454000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23444,7 +23444,7 @@
         <v>150</v>
       </c>
       <c r="F109" t="n">
-        <v>776000</v>
+        <v>793000</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -23485,7 +23485,7 @@
         <v>160</v>
       </c>
       <c r="F110" t="n">
-        <v>650000</v>
+        <v>655000</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>140</v>
       </c>
       <c r="F111" t="n">
-        <v>573000</v>
+        <v>586000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>1010</v>
       </c>
       <c r="F113" t="n">
-        <v>554000</v>
+        <v>556000</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1000</v>
       </c>
       <c r="F115" t="n">
-        <v>417000</v>
+        <v>413000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>80</v>
       </c>
       <c r="F117" t="n">
-        <v>667000</v>
+        <v>696000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>533000</v>
+        <v>520000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23977,7 +23977,7 @@
         <v>1010</v>
       </c>
       <c r="F122" t="n">
-        <v>609000</v>
+        <v>605000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -24018,7 +24018,7 @@
         <v>30</v>
       </c>
       <c r="F123" t="n">
-        <v>548000</v>
+        <v>575000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24100,7 +24100,7 @@
         <v>110</v>
       </c>
       <c r="F125" t="n">
-        <v>750000</v>
+        <v>782000</v>
       </c>
       <c r="G125" t="n">
         <v>1</v>
@@ -24141,7 +24141,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>620000</v>
+        <v>619000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>120</v>
       </c>
       <c r="F128" t="n">
-        <v>639000</v>
+        <v>622000</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -24264,7 +24264,7 @@
         <v>110</v>
       </c>
       <c r="F129" t="n">
-        <v>477000</v>
+        <v>460000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24305,7 +24305,7 @@
         <v>90</v>
       </c>
       <c r="F130" t="n">
-        <v>888000</v>
+        <v>889000</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -24387,7 +24387,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>422000</v>
+        <v>420000</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -24510,7 +24510,7 @@
         <v>140</v>
       </c>
       <c r="F135" t="n">
-        <v>434000</v>
+        <v>431000</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -24551,7 +24551,7 @@
         <v>30</v>
       </c>
       <c r="F136" t="n">
-        <v>593000</v>
+        <v>580000</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -24920,7 +24920,7 @@
         <v>60</v>
       </c>
       <c r="F145" t="n">
-        <v>433000</v>
+        <v>458000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -25084,7 +25084,7 @@
         <v>140</v>
       </c>
       <c r="F149" t="n">
-        <v>435000</v>
+        <v>445000</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -25248,7 +25248,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>957000</v>
+        <v>955000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>60</v>
       </c>
       <c r="F155" t="n">
-        <v>736000</v>
+        <v>738000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25494,7 +25494,7 @@
         <v>80</v>
       </c>
       <c r="F159" t="n">
-        <v>823000</v>
+        <v>796000</v>
       </c>
       <c r="G159" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>70</v>
       </c>
       <c r="F160" t="n">
-        <v>525000</v>
+        <v>515000</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
@@ -25658,7 +25658,7 @@
         <v>160</v>
       </c>
       <c r="F163" t="n">
-        <v>594000</v>
+        <v>593000</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
@@ -25699,7 +25699,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>600000</v>
+        <v>577000</v>
       </c>
       <c r="G164" t="n">
         <v>1</v>
@@ -25740,7 +25740,7 @@
         <v>160</v>
       </c>
       <c r="F165" t="n">
-        <v>589000</v>
+        <v>580000</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
@@ -25904,7 +25904,7 @@
         <v>140</v>
       </c>
       <c r="F169" t="n">
-        <v>401000</v>
+        <v>374000</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>20</v>
       </c>
       <c r="F170" t="n">
-        <v>592000</v>
+        <v>653000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>1010</v>
       </c>
       <c r="F171" t="n">
-        <v>533000</v>
+        <v>573000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26109,7 +26109,7 @@
         <v>40</v>
       </c>
       <c r="F174" t="n">
-        <v>419000</v>
+        <v>448000</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
@@ -26150,7 +26150,7 @@
         <v>50</v>
       </c>
       <c r="F175" t="n">
-        <v>800000</v>
+        <v>793000</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
@@ -26232,7 +26232,7 @@
         <v>90</v>
       </c>
       <c r="F177" t="n">
-        <v>396000</v>
+        <v>385000</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>70</v>
       </c>
       <c r="F179" t="n">
-        <v>633000</v>
+        <v>608000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>657000</v>
+        <v>653000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="F182" t="n">
-        <v>560000</v>
+        <v>531000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>80</v>
       </c>
       <c r="F183" t="n">
-        <v>796000</v>
+        <v>827000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>10</v>
       </c>
       <c r="F184" t="n">
-        <v>639000</v>
+        <v>668000</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
@@ -26601,7 +26601,7 @@
         <v>40</v>
       </c>
       <c r="F186" t="n">
-        <v>679000</v>
+        <v>700000</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
@@ -26683,7 +26683,7 @@
         <v>110</v>
       </c>
       <c r="F188" t="n">
-        <v>360000</v>
+        <v>371000</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
@@ -26724,7 +26724,7 @@
         <v>30</v>
       </c>
       <c r="F189" t="n">
-        <v>595000</v>
+        <v>618000</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>1000</v>
       </c>
       <c r="F190" t="n">
-        <v>230000</v>
+        <v>235000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26847,7 +26847,7 @@
         <v>90</v>
       </c>
       <c r="F192" t="n">
-        <v>672000</v>
+        <v>719000</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
@@ -26888,7 +26888,7 @@
         <v>60</v>
       </c>
       <c r="F193" t="n">
-        <v>679000</v>
+        <v>652000</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -26929,7 +26929,7 @@
         <v>140</v>
       </c>
       <c r="F194" t="n">
-        <v>803000</v>
+        <v>778000</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>130</v>
       </c>
       <c r="F196" t="n">
-        <v>571000</v>
+        <v>562000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>10</v>
       </c>
       <c r="F199" t="n">
-        <v>600000</v>
+        <v>608000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27257,7 +27257,7 @@
         <v>1010</v>
       </c>
       <c r="F202" t="n">
-        <v>601000</v>
+        <v>572000</v>
       </c>
       <c r="G202" t="n">
         <v>1</v>
@@ -27339,7 +27339,7 @@
         <v>130</v>
       </c>
       <c r="F204" t="n">
-        <v>668000</v>
+        <v>710000</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -27380,7 +27380,7 @@
         <v>150</v>
       </c>
       <c r="F205" t="n">
-        <v>499000</v>
+        <v>490000</v>
       </c>
       <c r="G205" t="n">
         <v>1</v>
@@ -27421,7 +27421,7 @@
         <v>140</v>
       </c>
       <c r="F206" t="n">
-        <v>516000</v>
+        <v>498000</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -27462,7 +27462,7 @@
         <v>60</v>
       </c>
       <c r="F207" t="n">
-        <v>563000</v>
+        <v>548000</v>
       </c>
       <c r="G207" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>130</v>
       </c>
       <c r="F209" t="n">
-        <v>897000</v>
+        <v>912000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>70</v>
       </c>
       <c r="F211" t="n">
-        <v>428000</v>
+        <v>437000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n">
-        <v>432000</v>
+        <v>430000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>603000</v>
+        <v>633000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -28077,7 +28077,7 @@
         <v>90</v>
       </c>
       <c r="F222" t="n">
-        <v>340000</v>
+        <v>345000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28200,7 +28200,7 @@
         <v>120</v>
       </c>
       <c r="F225" t="n">
-        <v>504000</v>
+        <v>474000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28282,7 +28282,7 @@
         <v>130</v>
       </c>
       <c r="F227" t="n">
-        <v>573000</v>
+        <v>565000</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>590000</v>
+        <v>600000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28364,7 +28364,7 @@
         <v>30</v>
       </c>
       <c r="F229" t="n">
-        <v>424000</v>
+        <v>447000</v>
       </c>
       <c r="G229" t="n">
         <v>1</v>
@@ -28405,7 +28405,7 @@
         <v>80</v>
       </c>
       <c r="F230" t="n">
-        <v>611000</v>
+        <v>619000</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>90</v>
       </c>
       <c r="F231" t="n">
-        <v>396000</v>
+        <v>416000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28610,7 +28610,7 @@
         <v>1000</v>
       </c>
       <c r="F235" t="n">
-        <v>479000</v>
+        <v>484000</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
@@ -28651,7 +28651,7 @@
         <v>100</v>
       </c>
       <c r="F236" t="n">
-        <v>1219000</v>
+        <v>1238000</v>
       </c>
       <c r="G236" t="n">
         <v>1</v>
@@ -28733,7 +28733,7 @@
         <v>70</v>
       </c>
       <c r="F238" t="n">
-        <v>437000</v>
+        <v>478000</v>
       </c>
       <c r="G238" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>90</v>
       </c>
       <c r="F240" t="n">
-        <v>581000</v>
+        <v>579000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>1000</v>
       </c>
       <c r="F241" t="n">
-        <v>446000</v>
+        <v>411000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>40</v>
       </c>
       <c r="F242" t="n">
-        <v>496000</v>
+        <v>501000</v>
       </c>
       <c r="G242" t="n">
         <v>1</v>
@@ -28938,7 +28938,7 @@
         <v>130</v>
       </c>
       <c r="F243" t="n">
-        <v>406000</v>
+        <v>392000</v>
       </c>
       <c r="G243" t="n">
         <v>1</v>
@@ -28979,7 +28979,7 @@
         <v>130</v>
       </c>
       <c r="F244" t="n">
-        <v>354000</v>
+        <v>414000</v>
       </c>
       <c r="G244" t="n">
         <v>1</v>
@@ -29102,7 +29102,7 @@
         <v>100</v>
       </c>
       <c r="F247" t="n">
-        <v>706000</v>
+        <v>723000</v>
       </c>
       <c r="G247" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>50</v>
       </c>
       <c r="F254" t="n">
-        <v>545000</v>
+        <v>590000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29471,7 +29471,7 @@
         <v>40</v>
       </c>
       <c r="F256" t="n">
-        <v>248000</v>
+        <v>276000</v>
       </c>
       <c r="G256" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>70</v>
       </c>
       <c r="F258" t="n">
-        <v>230000</v>
+        <v>265000</v>
       </c>
       <c r="G258" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>140</v>
       </c>
       <c r="F261" t="n">
-        <v>669000</v>
+        <v>634000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>130</v>
       </c>
       <c r="F264" t="n">
-        <v>860000</v>
+        <v>884000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>50</v>
       </c>
       <c r="F266" t="n">
-        <v>551000</v>
+        <v>525000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -29922,7 +29922,7 @@
         <v>1010</v>
       </c>
       <c r="F267" t="n">
-        <v>440000</v>
+        <v>460000</v>
       </c>
       <c r="G267" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>20</v>
       </c>
       <c r="F271" t="n">
-        <v>707000</v>
+        <v>691000</v>
       </c>
       <c r="G271" t="n">
         <v>1</v>
@@ -30168,7 +30168,7 @@
         <v>120</v>
       </c>
       <c r="F273" t="n">
-        <v>660000</v>
+        <v>642000</v>
       </c>
       <c r="G273" t="n">
         <v>1</v>
@@ -30250,7 +30250,7 @@
         <v>60</v>
       </c>
       <c r="F275" t="n">
-        <v>828000</v>
+        <v>795000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30332,7 +30332,7 @@
         <v>30</v>
       </c>
       <c r="F277" t="n">
-        <v>745000</v>
+        <v>764000</v>
       </c>
       <c r="G277" t="n">
         <v>1</v>
@@ -30414,7 +30414,7 @@
         <v>110</v>
       </c>
       <c r="F279" t="n">
-        <v>467000</v>
+        <v>460000</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
@@ -30578,7 +30578,7 @@
         <v>100</v>
       </c>
       <c r="F283" t="n">
-        <v>234000</v>
+        <v>251000</v>
       </c>
       <c r="G283" t="n">
         <v>1</v>
@@ -30619,7 +30619,7 @@
         <v>50</v>
       </c>
       <c r="F284" t="n">
-        <v>365000</v>
+        <v>364000</v>
       </c>
       <c r="G284" t="n">
         <v>1</v>
@@ -30701,7 +30701,7 @@
         <v>110</v>
       </c>
       <c r="F286" t="n">
-        <v>517000</v>
+        <v>476000</v>
       </c>
       <c r="G286" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>1010</v>
       </c>
       <c r="F290" t="n">
-        <v>271000</v>
+        <v>304000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>50</v>
       </c>
       <c r="F296" t="n">
-        <v>423000</v>
+        <v>426000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31152,7 +31152,7 @@
         <v>1000</v>
       </c>
       <c r="F297" t="n">
-        <v>564000</v>
+        <v>589000</v>
       </c>
       <c r="G297" t="n">
         <v>1</v>
@@ -31398,7 +31398,7 @@
         <v>110</v>
       </c>
       <c r="F303" t="n">
-        <v>230000</v>
+        <v>240000</v>
       </c>
       <c r="G303" t="n">
         <v>1</v>
@@ -31439,7 +31439,7 @@
         <v>50</v>
       </c>
       <c r="F304" t="n">
-        <v>281000</v>
+        <v>308000</v>
       </c>
       <c r="G304" t="n">
         <v>1</v>
@@ -31685,7 +31685,7 @@
         <v>150</v>
       </c>
       <c r="F310" t="n">
-        <v>505000</v>
+        <v>524000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>100</v>
       </c>
       <c r="F311" t="n">
-        <v>591000</v>
+        <v>595000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>110</v>
       </c>
       <c r="F315" t="n">
-        <v>431000</v>
+        <v>444000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>120</v>
       </c>
       <c r="F317" t="n">
-        <v>480000</v>
+        <v>472000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32751,7 +32751,7 @@
         <v>20</v>
       </c>
       <c r="F336" t="n">
-        <v>524000</v>
+        <v>529000</v>
       </c>
       <c r="G336" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>140</v>
       </c>
       <c r="F339" t="n">
-        <v>522000</v>
+        <v>496000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32956,7 +32956,7 @@
         <v>30</v>
       </c>
       <c r="F341" t="n">
-        <v>445000</v>
+        <v>473000</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>50</v>
       </c>
       <c r="F350" t="n">
-        <v>603000</v>
+        <v>605000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33459,7 +33459,7 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>797000</v>
+        <v>763000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33500,7 +33500,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>638000</v>
+        <v>647000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>989000</v>
+        <v>1007000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>764000</v>
+        <v>750000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>878000</v>
+        <v>834000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>693000</v>
+        <v>711000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33787,7 +33787,7 @@
         <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>601000</v>
+        <v>579000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>809000</v>
+        <v>821000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -33910,7 +33910,7 @@
         <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>816000</v>
+        <v>808000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>1060000</v>
+        <v>1029000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -34156,7 +34156,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>886000</v>
+        <v>913000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>1027000</v>
+        <v>994000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1141000</v>
+        <v>1116000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34361,7 +34361,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>898000</v>
+        <v>934000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -34443,7 +34443,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>623000</v>
+        <v>646000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>1007000</v>
+        <v>978000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>669000</v>
+        <v>667000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34607,7 +34607,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>904000</v>
+        <v>918000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>694000</v>
+        <v>697000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34771,7 +34771,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>740000</v>
+        <v>696000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34812,7 +34812,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>707000</v>
+        <v>657000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -34853,7 +34853,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>571000</v>
+        <v>572000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>834000</v>
+        <v>822000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34935,7 +34935,7 @@
         <v>70</v>
       </c>
       <c r="F38" t="n">
-        <v>701000</v>
+        <v>718000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>976000</v>
+        <v>968000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>814000</v>
+        <v>798000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -35099,7 +35099,7 @@
         <v>130</v>
       </c>
       <c r="F42" t="n">
-        <v>635000</v>
+        <v>618000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>849000</v>
+        <v>841000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>655000</v>
+        <v>647000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -35222,7 +35222,7 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>756000</v>
+        <v>754000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>490000</v>
+        <v>479000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35304,7 +35304,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>754000</v>
+        <v>773000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35345,7 +35345,7 @@
         <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>469000</v>
+        <v>492000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>911000</v>
+        <v>923000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35427,7 +35427,7 @@
         <v>50</v>
       </c>
       <c r="F50" t="n">
-        <v>670000</v>
+        <v>630000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>606000</v>
+        <v>611000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35714,7 +35714,7 @@
         <v>140</v>
       </c>
       <c r="F57" t="n">
-        <v>972000</v>
+        <v>945000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -35878,7 +35878,7 @@
         <v>1000</v>
       </c>
       <c r="F61" t="n">
-        <v>1055000</v>
+        <v>1018000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>865000</v>
+        <v>877000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -35960,7 +35960,7 @@
         <v>60</v>
       </c>
       <c r="F63" t="n">
-        <v>713000</v>
+        <v>671000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>816000</v>
+        <v>844000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -36206,7 +36206,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>479000</v>
+        <v>485000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>915000</v>
+        <v>907000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>160</v>
       </c>
       <c r="F71" t="n">
-        <v>1003000</v>
+        <v>961000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36329,7 +36329,7 @@
         <v>60</v>
       </c>
       <c r="F72" t="n">
-        <v>633000</v>
+        <v>624000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>557000</v>
+        <v>570000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -36493,7 +36493,7 @@
         <v>150</v>
       </c>
       <c r="F76" t="n">
-        <v>442000</v>
+        <v>504000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -36575,7 +36575,7 @@
         <v>60</v>
       </c>
       <c r="F78" t="n">
-        <v>587000</v>
+        <v>613000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="n">
-        <v>481000</v>
+        <v>526000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>801000</v>
+        <v>806000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>120</v>
       </c>
       <c r="F82" t="n">
-        <v>671000</v>
+        <v>640000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>676000</v>
+        <v>684000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36821,7 +36821,7 @@
         <v>160</v>
       </c>
       <c r="F84" t="n">
-        <v>645000</v>
+        <v>641000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>80</v>
       </c>
       <c r="F87" t="n">
-        <v>858000</v>
+        <v>821000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37026,7 +37026,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>432000</v>
+        <v>458000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>1010</v>
       </c>
       <c r="F90" t="n">
-        <v>603000</v>
+        <v>597000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37190,7 +37190,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>617000</v>
+        <v>641000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>1164000</v>
+        <v>1144000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37272,7 +37272,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>957000</v>
+        <v>940000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -37354,7 +37354,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>722000</v>
+        <v>699000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>150</v>
       </c>
       <c r="F98" t="n">
-        <v>717000</v>
+        <v>709000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>20</v>
       </c>
       <c r="F99" t="n">
-        <v>1076000</v>
+        <v>1105000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>666000</v>
+        <v>664000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>70</v>
       </c>
       <c r="F106" t="n">
-        <v>707000</v>
+        <v>731000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37846,7 +37846,7 @@
         <v>120</v>
       </c>
       <c r="F109" t="n">
-        <v>570000</v>
+        <v>585000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -37887,7 +37887,7 @@
         <v>150</v>
       </c>
       <c r="F110" t="n">
-        <v>344000</v>
+        <v>422000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>130</v>
       </c>
       <c r="F115" t="n">
-        <v>925000</v>
+        <v>951000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>1010</v>
       </c>
       <c r="F118" t="n">
-        <v>266000</v>
+        <v>309000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38256,7 +38256,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>598000</v>
+        <v>583000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>725000</v>
+        <v>706000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>473000</v>
+        <v>474000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38666,7 +38666,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>616000</v>
+        <v>642000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -38707,7 +38707,7 @@
         <v>30</v>
       </c>
       <c r="F130" t="n">
-        <v>671000</v>
+        <v>667000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>1000</v>
       </c>
       <c r="F133" t="n">
-        <v>467000</v>
+        <v>499000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38871,7 +38871,7 @@
         <v>150</v>
       </c>
       <c r="F134" t="n">
-        <v>419000</v>
+        <v>432000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>372000</v>
+        <v>402000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -39117,7 +39117,7 @@
         <v>80</v>
       </c>
       <c r="F140" t="n">
-        <v>250000</v>
+        <v>304000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>150</v>
       </c>
       <c r="F145" t="n">
-        <v>493000</v>
+        <v>441000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39363,7 +39363,7 @@
         <v>40</v>
       </c>
       <c r="F146" t="n">
-        <v>363000</v>
+        <v>399000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>1029000</v>
+        <v>1014000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>946000</v>
+        <v>930000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -39907,7 +39907,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>788000</v>
+        <v>774000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -39948,7 +39948,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>603000</v>
+        <v>581000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -40030,7 +40030,7 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>785000</v>
+        <v>810000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>773000</v>
+        <v>746000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40235,7 +40235,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>690000</v>
+        <v>744000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>140</v>
       </c>
       <c r="F19" t="n">
-        <v>807000</v>
+        <v>801000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40399,7 +40399,7 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>892000</v>
+        <v>895000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>981000</v>
+        <v>942000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40522,7 +40522,7 @@
         <v>50</v>
       </c>
       <c r="F24" t="n">
-        <v>560000</v>
+        <v>598000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -40727,7 +40727,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>673000</v>
+        <v>695000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>838000</v>
+        <v>821000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         <v>1010</v>
       </c>
       <c r="F31" t="n">
-        <v>629000</v>
+        <v>639000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -40850,7 +40850,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>511000</v>
+        <v>529000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8222,7 +8222,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>879000</v>
+        <v>882000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -8304,7 +8304,7 @@
         <v>160</v>
       </c>
       <c r="F4" t="n">
-        <v>469000</v>
+        <v>432000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>926000</v>
+        <v>902000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>688000</v>
+        <v>670000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>566000</v>
+        <v>537000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>651000</v>
+        <v>649000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8509,7 +8509,7 @@
         <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>695000</v>
+        <v>713000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>1010</v>
       </c>
       <c r="F13" t="n">
-        <v>903000</v>
+        <v>890000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="n">
-        <v>620000</v>
+        <v>623000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>457000</v>
+        <v>475000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>585000</v>
+        <v>611000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>889000</v>
+        <v>857000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>120</v>
       </c>
       <c r="F18" t="n">
-        <v>504000</v>
+        <v>528000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>682000</v>
+        <v>701000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>569000</v>
+        <v>557000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>80</v>
       </c>
       <c r="F23" t="n">
-        <v>787000</v>
+        <v>850000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>130</v>
       </c>
       <c r="F28" t="n">
-        <v>935000</v>
+        <v>901000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>761000</v>
+        <v>768000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9411,7 +9411,7 @@
         <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>913000</v>
+        <v>839000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
         <v>150</v>
       </c>
       <c r="F32" t="n">
-        <v>742000</v>
+        <v>739000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>1010</v>
       </c>
       <c r="F33" t="n">
-        <v>534000</v>
+        <v>525000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>567000</v>
+        <v>575000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
         <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>342000</v>
+        <v>339000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>80</v>
       </c>
       <c r="F37" t="n">
-        <v>304000</v>
+        <v>324000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -9698,7 +9698,7 @@
         <v>140</v>
       </c>
       <c r="F38" t="n">
-        <v>643000</v>
+        <v>672000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>897000</v>
+        <v>926000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9780,7 +9780,7 @@
         <v>40</v>
       </c>
       <c r="F40" t="n">
-        <v>454000</v>
+        <v>437000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>40</v>
       </c>
       <c r="F41" t="n">
-        <v>706000</v>
+        <v>692000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>120</v>
       </c>
       <c r="F42" t="n">
-        <v>774000</v>
+        <v>783000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
         <v>140</v>
       </c>
       <c r="F43" t="n">
-        <v>687000</v>
+        <v>686000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -9944,7 +9944,7 @@
         <v>60</v>
       </c>
       <c r="F44" t="n">
-        <v>502000</v>
+        <v>508000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -9985,7 +9985,7 @@
         <v>1010</v>
       </c>
       <c r="F45" t="n">
-        <v>686000</v>
+        <v>697000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -10067,7 +10067,7 @@
         <v>80</v>
       </c>
       <c r="F47" t="n">
-        <v>764000</v>
+        <v>786000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>914000</v>
+        <v>895000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -10190,7 +10190,7 @@
         <v>60</v>
       </c>
       <c r="F50" t="n">
-        <v>639000</v>
+        <v>622000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -10231,7 +10231,7 @@
         <v>40</v>
       </c>
       <c r="F51" t="n">
-        <v>817000</v>
+        <v>815000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -10313,7 +10313,7 @@
         <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>620000</v>
+        <v>664000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10477,7 +10477,7 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>760000</v>
+        <v>747000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -10518,7 +10518,7 @@
         <v>30</v>
       </c>
       <c r="F58" t="n">
-        <v>374000</v>
+        <v>387000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -10600,7 +10600,7 @@
         <v>100</v>
       </c>
       <c r="F60" t="n">
-        <v>353000</v>
+        <v>344000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>595000</v>
+        <v>591000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10682,7 +10682,7 @@
         <v>30</v>
       </c>
       <c r="F62" t="n">
-        <v>671000</v>
+        <v>682000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>80</v>
       </c>
       <c r="F64" t="n">
-        <v>734000</v>
+        <v>739000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10846,7 +10846,7 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>649000</v>
+        <v>641000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>743000</v>
+        <v>726000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>1000</v>
       </c>
       <c r="F69" t="n">
-        <v>938000</v>
+        <v>899000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
         <v>1000</v>
       </c>
       <c r="F72" t="n">
-        <v>730000</v>
+        <v>699000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>630000</v>
+        <v>566000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11297,7 +11297,7 @@
         <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>476000</v>
+        <v>429000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -11461,7 +11461,7 @@
         <v>150</v>
       </c>
       <c r="F81" t="n">
-        <v>473000</v>
+        <v>489000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -11625,7 +11625,7 @@
         <v>110</v>
       </c>
       <c r="F85" t="n">
-        <v>429000</v>
+        <v>392000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11748,7 +11748,7 @@
         <v>70</v>
       </c>
       <c r="F88" t="n">
-        <v>619000</v>
+        <v>628000</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>553000</v>
+        <v>565000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>40</v>
       </c>
       <c r="F91" t="n">
-        <v>970000</v>
+        <v>941000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11953,7 +11953,7 @@
         <v>1010</v>
       </c>
       <c r="F93" t="n">
-        <v>557000</v>
+        <v>559000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         <v>140</v>
       </c>
       <c r="F94" t="n">
-        <v>568000</v>
+        <v>564000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12035,7 +12035,7 @@
         <v>1000</v>
       </c>
       <c r="F95" t="n">
-        <v>717000</v>
+        <v>698000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12076,7 +12076,7 @@
         <v>160</v>
       </c>
       <c r="F96" t="n">
-        <v>807000</v>
+        <v>796000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -12199,7 +12199,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>760000</v>
+        <v>750000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>70</v>
       </c>
       <c r="F102" t="n">
-        <v>563000</v>
+        <v>566000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>1000</v>
       </c>
       <c r="F103" t="n">
-        <v>659000</v>
+        <v>650000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>1010</v>
       </c>
       <c r="F104" t="n">
-        <v>787000</v>
+        <v>796000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>40</v>
       </c>
       <c r="F105" t="n">
-        <v>677000</v>
+        <v>671000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>160</v>
       </c>
       <c r="F106" t="n">
-        <v>748000</v>
+        <v>718000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>160</v>
       </c>
       <c r="F107" t="n">
-        <v>733000</v>
+        <v>702000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12568,7 +12568,7 @@
         <v>10</v>
       </c>
       <c r="F108" t="n">
-        <v>496000</v>
+        <v>503000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -12609,7 +12609,7 @@
         <v>130</v>
       </c>
       <c r="F109" t="n">
-        <v>472000</v>
+        <v>520000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -12691,7 +12691,7 @@
         <v>1000</v>
       </c>
       <c r="F111" t="n">
-        <v>356000</v>
+        <v>327000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="n">
-        <v>469000</v>
+        <v>436000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>110</v>
       </c>
       <c r="F113" t="n">
-        <v>643000</v>
+        <v>669000</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -12855,7 +12855,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>951000</v>
+        <v>946000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>90</v>
       </c>
       <c r="F116" t="n">
-        <v>743000</v>
+        <v>744000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -13101,7 +13101,7 @@
         <v>110</v>
       </c>
       <c r="F121" t="n">
-        <v>482000</v>
+        <v>488000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>752000</v>
+        <v>732000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>130</v>
       </c>
       <c r="F125" t="n">
-        <v>610000</v>
+        <v>608000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>160</v>
       </c>
       <c r="F126" t="n">
-        <v>646000</v>
+        <v>643000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>70</v>
       </c>
       <c r="F127" t="n">
-        <v>713000</v>
+        <v>716000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13388,7 +13388,7 @@
         <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>543000</v>
+        <v>515000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>90</v>
       </c>
       <c r="F129" t="n">
-        <v>875000</v>
+        <v>886000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>579000</v>
+        <v>584000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>60</v>
       </c>
       <c r="F133" t="n">
-        <v>526000</v>
+        <v>499000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>150</v>
       </c>
       <c r="F136" t="n">
-        <v>382000</v>
+        <v>375000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>835000</v>
+        <v>840000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>70</v>
       </c>
       <c r="F138" t="n">
-        <v>790000</v>
+        <v>788000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>90</v>
       </c>
       <c r="F140" t="n">
-        <v>234000</v>
+        <v>249000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>598000</v>
+        <v>581000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>130</v>
       </c>
       <c r="F142" t="n">
-        <v>1125000</v>
+        <v>1161000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>100</v>
       </c>
       <c r="F144" t="n">
-        <v>516000</v>
+        <v>495000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>1010</v>
       </c>
       <c r="F145" t="n">
-        <v>455000</v>
+        <v>452000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14290,7 +14290,7 @@
         <v>30</v>
       </c>
       <c r="F150" t="n">
-        <v>439000</v>
+        <v>451000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>20</v>
       </c>
       <c r="F152" t="n">
-        <v>843000</v>
+        <v>809000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
         <v>120</v>
       </c>
       <c r="F154" t="n">
-        <v>558000</v>
+        <v>587000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>160</v>
       </c>
       <c r="F156" t="n">
-        <v>667000</v>
+        <v>623000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>100</v>
       </c>
       <c r="F157" t="n">
-        <v>349000</v>
+        <v>371000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>90</v>
       </c>
       <c r="F158" t="n">
-        <v>605000</v>
+        <v>599000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>1000</v>
       </c>
       <c r="F159" t="n">
-        <v>735000</v>
+        <v>724000</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -14700,7 +14700,7 @@
         <v>1000</v>
       </c>
       <c r="F160" t="n">
-        <v>821000</v>
+        <v>811000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>547000</v>
+        <v>536000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>150</v>
       </c>
       <c r="F162" t="n">
-        <v>437000</v>
+        <v>456000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>40</v>
       </c>
       <c r="F163" t="n">
-        <v>238000</v>
+        <v>244000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>331000</v>
+        <v>321000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14905,7 +14905,7 @@
         <v>150</v>
       </c>
       <c r="F165" t="n">
-        <v>557000</v>
+        <v>551000</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -15028,7 +15028,7 @@
         <v>110</v>
       </c>
       <c r="F168" t="n">
-        <v>695000</v>
+        <v>686000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -15110,7 +15110,7 @@
         <v>140</v>
       </c>
       <c r="F170" t="n">
-        <v>523000</v>
+        <v>564000</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -15274,7 +15274,7 @@
         <v>60</v>
       </c>
       <c r="F174" t="n">
-        <v>775000</v>
+        <v>751000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -15315,7 +15315,7 @@
         <v>10</v>
       </c>
       <c r="F175" t="n">
-        <v>624000</v>
+        <v>650000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>30</v>
       </c>
       <c r="F176" t="n">
-        <v>619000</v>
+        <v>634000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>140</v>
       </c>
       <c r="F181" t="n">
-        <v>456000</v>
+        <v>485000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15684,7 +15684,7 @@
         <v>150</v>
       </c>
       <c r="F184" t="n">
-        <v>474000</v>
+        <v>506000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>130</v>
       </c>
       <c r="F186" t="n">
-        <v>827000</v>
+        <v>822000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15807,7 +15807,7 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>582000</v>
+        <v>613000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -15930,7 +15930,7 @@
         <v>50</v>
       </c>
       <c r="F190" t="n">
-        <v>817000</v>
+        <v>784000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         <v>20</v>
       </c>
       <c r="F193" t="n">
-        <v>670000</v>
+        <v>705000</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -16094,7 +16094,7 @@
         <v>70</v>
       </c>
       <c r="F194" t="n">
-        <v>540000</v>
+        <v>527000</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
         <v>50</v>
       </c>
       <c r="F195" t="n">
-        <v>624000</v>
+        <v>615000</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>30</v>
       </c>
       <c r="F199" t="n">
-        <v>670000</v>
+        <v>696000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16422,7 +16422,7 @@
         <v>70</v>
       </c>
       <c r="F202" t="n">
-        <v>620000</v>
+        <v>628000</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>80</v>
       </c>
       <c r="F204" t="n">
-        <v>683000</v>
+        <v>691000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
         <v>150</v>
       </c>
       <c r="F206" t="n">
-        <v>336000</v>
+        <v>346000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -16709,7 +16709,7 @@
         <v>50</v>
       </c>
       <c r="F209" t="n">
-        <v>388000</v>
+        <v>401000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -16750,7 +16750,7 @@
         <v>150</v>
       </c>
       <c r="F210" t="n">
-        <v>520000</v>
+        <v>524000</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -16832,7 +16832,7 @@
         <v>100</v>
       </c>
       <c r="F212" t="n">
-        <v>681000</v>
+        <v>674000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -16955,7 +16955,7 @@
         <v>120</v>
       </c>
       <c r="F215" t="n">
-        <v>550000</v>
+        <v>535000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>130</v>
       </c>
       <c r="F218" t="n">
-        <v>453000</v>
+        <v>437000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>400000</v>
+        <v>463000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17324,7 +17324,7 @@
         <v>80</v>
       </c>
       <c r="F224" t="n">
-        <v>452000</v>
+        <v>473000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
         <v>1000</v>
       </c>
       <c r="F225" t="n">
-        <v>735000</v>
+        <v>722000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -17406,7 +17406,7 @@
         <v>150</v>
       </c>
       <c r="F226" t="n">
-        <v>612000</v>
+        <v>610000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>110</v>
       </c>
       <c r="F232" t="n">
-        <v>241000</v>
+        <v>235000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17693,7 +17693,7 @@
         <v>1010</v>
       </c>
       <c r="F233" t="n">
-        <v>734000</v>
+        <v>706000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -17775,7 +17775,7 @@
         <v>50</v>
       </c>
       <c r="F235" t="n">
-        <v>235000</v>
+        <v>256000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>140</v>
       </c>
       <c r="F236" t="n">
-        <v>398000</v>
+        <v>423000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>30</v>
       </c>
       <c r="F241" t="n">
-        <v>518000</v>
+        <v>517000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>383000</v>
+        <v>387000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18103,7 +18103,7 @@
         <v>1000</v>
       </c>
       <c r="F243" t="n">
-        <v>324000</v>
+        <v>321000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
         <v>50</v>
       </c>
       <c r="F245" t="n">
-        <v>715000</v>
+        <v>707000</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -18226,7 +18226,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>462000</v>
+        <v>449000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>150</v>
       </c>
       <c r="F248" t="n">
-        <v>871000</v>
+        <v>861000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>120</v>
       </c>
       <c r="F250" t="n">
-        <v>484000</v>
+        <v>477000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>50</v>
       </c>
       <c r="F251" t="n">
-        <v>327000</v>
+        <v>325000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         <v>160</v>
       </c>
       <c r="F252" t="n">
-        <v>370000</v>
+        <v>380000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>110</v>
       </c>
       <c r="F258" t="n">
-        <v>529000</v>
+        <v>542000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -19057,7 +19057,7 @@
         <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>661000</v>
+        <v>622000</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -19098,7 +19098,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>519000</v>
+        <v>563000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19180,7 +19180,7 @@
         <v>120</v>
       </c>
       <c r="F5" t="n">
-        <v>636000</v>
+        <v>654000</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -19262,7 +19262,7 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>563000</v>
+        <v>554000</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -19303,7 +19303,7 @@
         <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>686000</v>
+        <v>712000</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -19467,7 +19467,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>528000</v>
+        <v>555000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19508,7 +19508,7 @@
         <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>563000</v>
+        <v>530000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19631,7 +19631,7 @@
         <v>120</v>
       </c>
       <c r="F16" t="n">
-        <v>447000</v>
+        <v>426000</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -19713,7 +19713,7 @@
         <v>1010</v>
       </c>
       <c r="F18" t="n">
-        <v>592000</v>
+        <v>610000</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -19754,7 +19754,7 @@
         <v>40</v>
       </c>
       <c r="F19" t="n">
-        <v>628000</v>
+        <v>652000</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -19836,7 +19836,7 @@
         <v>130</v>
       </c>
       <c r="F21" t="n">
-        <v>784000</v>
+        <v>800000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19877,7 +19877,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>611000</v>
+        <v>576000</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>130</v>
       </c>
       <c r="F24" t="n">
-        <v>995000</v>
+        <v>1035000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20000,7 +20000,7 @@
         <v>150</v>
       </c>
       <c r="F25" t="n">
-        <v>773000</v>
+        <v>789000</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>693000</v>
+        <v>682000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>571000</v>
+        <v>577000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>594000</v>
+        <v>614000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20287,7 +20287,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>740000</v>
+        <v>730000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>776000</v>
+        <v>768000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20369,7 +20369,7 @@
         <v>1000</v>
       </c>
       <c r="F34" t="n">
-        <v>836000</v>
+        <v>841000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>708000</v>
+        <v>682000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>20</v>
       </c>
       <c r="F40" t="n">
-        <v>558000</v>
+        <v>555000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20697,7 +20697,7 @@
         <v>110</v>
       </c>
       <c r="F42" t="n">
-        <v>790000</v>
+        <v>774000</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -20738,7 +20738,7 @@
         <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>529000</v>
+        <v>505000</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -20779,7 +20779,7 @@
         <v>130</v>
       </c>
       <c r="F44" t="n">
-        <v>379000</v>
+        <v>372000</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>150</v>
       </c>
       <c r="F46" t="n">
-        <v>525000</v>
+        <v>523000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>683000</v>
+        <v>695000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>1000</v>
       </c>
       <c r="F48" t="n">
-        <v>530000</v>
+        <v>513000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -20984,7 +20984,7 @@
         <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>661000</v>
+        <v>667000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>478000</v>
+        <v>474000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>60</v>
       </c>
       <c r="F52" t="n">
-        <v>812000</v>
+        <v>796000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21148,7 +21148,7 @@
         <v>100</v>
       </c>
       <c r="F53" t="n">
-        <v>752000</v>
+        <v>789000</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>80</v>
       </c>
       <c r="F54" t="n">
-        <v>628000</v>
+        <v>626000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>40</v>
       </c>
       <c r="F55" t="n">
-        <v>906000</v>
+        <v>892000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>150</v>
       </c>
       <c r="F57" t="n">
-        <v>735000</v>
+        <v>680000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>160</v>
       </c>
       <c r="F58" t="n">
-        <v>759000</v>
+        <v>737000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21394,7 +21394,7 @@
         <v>160</v>
       </c>
       <c r="F59" t="n">
-        <v>607000</v>
+        <v>617000</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>649000</v>
+        <v>625000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21558,7 +21558,7 @@
         <v>20</v>
       </c>
       <c r="F63" t="n">
-        <v>580000</v>
+        <v>538000</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>732000</v>
+        <v>737000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21681,7 +21681,7 @@
         <v>100</v>
       </c>
       <c r="F66" t="n">
-        <v>610000</v>
+        <v>624000</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -21763,7 +21763,7 @@
         <v>60</v>
       </c>
       <c r="F68" t="n">
-        <v>406000</v>
+        <v>427000</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>140</v>
       </c>
       <c r="F69" t="n">
-        <v>453000</v>
+        <v>473000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>60</v>
       </c>
       <c r="F70" t="n">
-        <v>584000</v>
+        <v>602000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>70</v>
       </c>
       <c r="F71" t="n">
-        <v>476000</v>
+        <v>493000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21968,7 +21968,7 @@
         <v>90</v>
       </c>
       <c r="F73" t="n">
-        <v>909000</v>
+        <v>939000</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>569000</v>
+        <v>585000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22173,7 +22173,7 @@
         <v>80</v>
       </c>
       <c r="F78" t="n">
-        <v>578000</v>
+        <v>562000</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>70</v>
       </c>
       <c r="F79" t="n">
-        <v>391000</v>
+        <v>415000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22296,7 +22296,7 @@
         <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>588000</v>
+        <v>586000</v>
       </c>
       <c r="G81" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>869000</v>
+        <v>890000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>90</v>
       </c>
       <c r="F83" t="n">
-        <v>581000</v>
+        <v>600000</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>130</v>
       </c>
       <c r="F84" t="n">
-        <v>500000</v>
+        <v>498000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22501,7 +22501,7 @@
         <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>690000</v>
+        <v>704000</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
@@ -22665,7 +22665,7 @@
         <v>20</v>
       </c>
       <c r="F90" t="n">
-        <v>898000</v>
+        <v>932000</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>140</v>
       </c>
       <c r="F91" t="n">
-        <v>548000</v>
+        <v>552000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>100</v>
       </c>
       <c r="F92" t="n">
-        <v>658000</v>
+        <v>663000</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -22788,7 +22788,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>755000</v>
+        <v>745000</v>
       </c>
       <c r="G93" t="n">
         <v>1</v>
@@ -22829,7 +22829,7 @@
         <v>160</v>
       </c>
       <c r="F94" t="n">
-        <v>511000</v>
+        <v>462000</v>
       </c>
       <c r="G94" t="n">
         <v>1</v>
@@ -22911,7 +22911,7 @@
         <v>130</v>
       </c>
       <c r="F96" t="n">
-        <v>484000</v>
+        <v>461000</v>
       </c>
       <c r="G96" t="n">
         <v>1</v>
@@ -22993,7 +22993,7 @@
         <v>40</v>
       </c>
       <c r="F98" t="n">
-        <v>485000</v>
+        <v>501000</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -23075,7 +23075,7 @@
         <v>70</v>
       </c>
       <c r="F100" t="n">
-        <v>800000</v>
+        <v>777000</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>110</v>
       </c>
       <c r="F101" t="n">
-        <v>432000</v>
+        <v>430000</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -23239,7 +23239,7 @@
         <v>90</v>
       </c>
       <c r="F104" t="n">
-        <v>671000</v>
+        <v>648000</v>
       </c>
       <c r="G104" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
         <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>638000</v>
+        <v>634000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>150</v>
       </c>
       <c r="F106" t="n">
-        <v>570000</v>
+        <v>558000</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -23362,7 +23362,7 @@
         <v>160</v>
       </c>
       <c r="F107" t="n">
-        <v>378000</v>
+        <v>337000</v>
       </c>
       <c r="G107" t="n">
         <v>1</v>
@@ -23444,7 +23444,7 @@
         <v>150</v>
       </c>
       <c r="F109" t="n">
-        <v>793000</v>
+        <v>791000</v>
       </c>
       <c r="G109" t="n">
         <v>1</v>
@@ -23485,7 +23485,7 @@
         <v>160</v>
       </c>
       <c r="F110" t="n">
-        <v>655000</v>
+        <v>697000</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>140</v>
       </c>
       <c r="F111" t="n">
-        <v>586000</v>
+        <v>593000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23567,7 +23567,7 @@
         <v>120</v>
       </c>
       <c r="F112" t="n">
-        <v>788000</v>
+        <v>755000</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
@@ -23608,7 +23608,7 @@
         <v>1010</v>
       </c>
       <c r="F113" t="n">
-        <v>556000</v>
+        <v>569000</v>
       </c>
       <c r="G113" t="n">
         <v>1</v>
@@ -23649,7 +23649,7 @@
         <v>130</v>
       </c>
       <c r="F114" t="n">
-        <v>378000</v>
+        <v>349000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1000</v>
       </c>
       <c r="F115" t="n">
-        <v>413000</v>
+        <v>424000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>80</v>
       </c>
       <c r="F117" t="n">
-        <v>696000</v>
+        <v>722000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>520000</v>
+        <v>500000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23977,7 +23977,7 @@
         <v>1010</v>
       </c>
       <c r="F122" t="n">
-        <v>605000</v>
+        <v>603000</v>
       </c>
       <c r="G122" t="n">
         <v>1</v>
@@ -24018,7 +24018,7 @@
         <v>30</v>
       </c>
       <c r="F123" t="n">
-        <v>575000</v>
+        <v>601000</v>
       </c>
       <c r="G123" t="n">
         <v>1</v>
@@ -24141,7 +24141,7 @@
         <v>10</v>
       </c>
       <c r="F126" t="n">
-        <v>619000</v>
+        <v>618000</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>120</v>
       </c>
       <c r="F128" t="n">
-        <v>622000</v>
+        <v>600000</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -24264,7 +24264,7 @@
         <v>110</v>
       </c>
       <c r="F129" t="n">
-        <v>460000</v>
+        <v>465000</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -24305,7 +24305,7 @@
         <v>90</v>
       </c>
       <c r="F130" t="n">
-        <v>889000</v>
+        <v>867000</v>
       </c>
       <c r="G130" t="n">
         <v>1</v>
@@ -24387,7 +24387,7 @@
         <v>120</v>
       </c>
       <c r="F132" t="n">
-        <v>420000</v>
+        <v>431000</v>
       </c>
       <c r="G132" t="n">
         <v>1</v>
@@ -24469,7 +24469,7 @@
         <v>90</v>
       </c>
       <c r="F134" t="n">
-        <v>593000</v>
+        <v>608000</v>
       </c>
       <c r="G134" t="n">
         <v>1</v>
@@ -24551,7 +24551,7 @@
         <v>30</v>
       </c>
       <c r="F136" t="n">
-        <v>580000</v>
+        <v>562000</v>
       </c>
       <c r="G136" t="n">
         <v>1</v>
@@ -24838,7 +24838,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>663000</v>
+        <v>634000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24920,7 +24920,7 @@
         <v>60</v>
       </c>
       <c r="F145" t="n">
-        <v>458000</v>
+        <v>483000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -24961,7 +24961,7 @@
         <v>110</v>
       </c>
       <c r="F146" t="n">
-        <v>950000</v>
+        <v>953000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25084,7 +25084,7 @@
         <v>140</v>
       </c>
       <c r="F149" t="n">
-        <v>445000</v>
+        <v>468000</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -25166,7 +25166,7 @@
         <v>110</v>
       </c>
       <c r="F151" t="n">
-        <v>441000</v>
+        <v>464000</v>
       </c>
       <c r="G151" t="n">
         <v>1</v>
@@ -25248,7 +25248,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>955000</v>
+        <v>954000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>60</v>
       </c>
       <c r="F155" t="n">
-        <v>738000</v>
+        <v>708000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25371,7 +25371,7 @@
         <v>90</v>
       </c>
       <c r="F156" t="n">
-        <v>485000</v>
+        <v>481000</v>
       </c>
       <c r="G156" t="n">
         <v>1</v>
@@ -25494,7 +25494,7 @@
         <v>80</v>
       </c>
       <c r="F159" t="n">
-        <v>796000</v>
+        <v>779000</v>
       </c>
       <c r="G159" t="n">
         <v>1</v>
@@ -25658,7 +25658,7 @@
         <v>160</v>
       </c>
       <c r="F163" t="n">
-        <v>593000</v>
+        <v>589000</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
@@ -25699,7 +25699,7 @@
         <v>160</v>
       </c>
       <c r="F164" t="n">
-        <v>577000</v>
+        <v>545000</v>
       </c>
       <c r="G164" t="n">
         <v>1</v>
@@ -25740,7 +25740,7 @@
         <v>160</v>
       </c>
       <c r="F165" t="n">
-        <v>580000</v>
+        <v>554000</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
@@ -25904,7 +25904,7 @@
         <v>140</v>
       </c>
       <c r="F169" t="n">
-        <v>374000</v>
+        <v>366000</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>20</v>
       </c>
       <c r="F170" t="n">
-        <v>653000</v>
+        <v>705000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>1010</v>
       </c>
       <c r="F171" t="n">
-        <v>573000</v>
+        <v>581000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26109,7 +26109,7 @@
         <v>40</v>
       </c>
       <c r="F174" t="n">
-        <v>448000</v>
+        <v>458000</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
@@ -26150,7 +26150,7 @@
         <v>50</v>
       </c>
       <c r="F175" t="n">
-        <v>793000</v>
+        <v>773000</v>
       </c>
       <c r="G175" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>70</v>
       </c>
       <c r="F179" t="n">
-        <v>608000</v>
+        <v>602000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>10</v>
       </c>
       <c r="F181" t="n">
-        <v>653000</v>
+        <v>632000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="F182" t="n">
-        <v>531000</v>
+        <v>490000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>80</v>
       </c>
       <c r="F183" t="n">
-        <v>827000</v>
+        <v>861000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>10</v>
       </c>
       <c r="F184" t="n">
-        <v>668000</v>
+        <v>686000</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
@@ -26560,7 +26560,7 @@
         <v>120</v>
       </c>
       <c r="F185" t="n">
-        <v>620000</v>
+        <v>616000</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
@@ -26601,7 +26601,7 @@
         <v>40</v>
       </c>
       <c r="F186" t="n">
-        <v>700000</v>
+        <v>696000</v>
       </c>
       <c r="G186" t="n">
         <v>1</v>
@@ -26683,7 +26683,7 @@
         <v>110</v>
       </c>
       <c r="F188" t="n">
-        <v>371000</v>
+        <v>398000</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
@@ -26724,7 +26724,7 @@
         <v>30</v>
       </c>
       <c r="F189" t="n">
-        <v>618000</v>
+        <v>652000</v>
       </c>
       <c r="G189" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>1000</v>
       </c>
       <c r="F190" t="n">
-        <v>235000</v>
+        <v>230000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26847,7 +26847,7 @@
         <v>90</v>
       </c>
       <c r="F192" t="n">
-        <v>719000</v>
+        <v>720000</v>
       </c>
       <c r="G192" t="n">
         <v>1</v>
@@ -26888,7 +26888,7 @@
         <v>60</v>
       </c>
       <c r="F193" t="n">
-        <v>652000</v>
+        <v>634000</v>
       </c>
       <c r="G193" t="n">
         <v>1</v>
@@ -26929,7 +26929,7 @@
         <v>140</v>
       </c>
       <c r="F194" t="n">
-        <v>778000</v>
+        <v>750000</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
@@ -27257,7 +27257,7 @@
         <v>1010</v>
       </c>
       <c r="F202" t="n">
-        <v>572000</v>
+        <v>547000</v>
       </c>
       <c r="G202" t="n">
         <v>1</v>
@@ -27339,7 +27339,7 @@
         <v>130</v>
       </c>
       <c r="F204" t="n">
-        <v>710000</v>
+        <v>752000</v>
       </c>
       <c r="G204" t="n">
         <v>1</v>
@@ -27380,7 +27380,7 @@
         <v>150</v>
       </c>
       <c r="F205" t="n">
-        <v>490000</v>
+        <v>472000</v>
       </c>
       <c r="G205" t="n">
         <v>1</v>
@@ -27421,7 +27421,7 @@
         <v>140</v>
       </c>
       <c r="F206" t="n">
-        <v>498000</v>
+        <v>477000</v>
       </c>
       <c r="G206" t="n">
         <v>1</v>
@@ -27462,7 +27462,7 @@
         <v>60</v>
       </c>
       <c r="F207" t="n">
-        <v>548000</v>
+        <v>569000</v>
       </c>
       <c r="G207" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>130</v>
       </c>
       <c r="F209" t="n">
-        <v>912000</v>
+        <v>907000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>70</v>
       </c>
       <c r="F211" t="n">
-        <v>437000</v>
+        <v>460000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27667,7 +27667,7 @@
         <v>90</v>
       </c>
       <c r="F212" t="n">
-        <v>379000</v>
+        <v>381000</v>
       </c>
       <c r="G212" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>100</v>
       </c>
       <c r="F213" t="n">
-        <v>304000</v>
+        <v>320000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n">
-        <v>430000</v>
+        <v>416000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>633000</v>
+        <v>640000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -28077,7 +28077,7 @@
         <v>90</v>
       </c>
       <c r="F222" t="n">
-        <v>345000</v>
+        <v>328000</v>
       </c>
       <c r="G222" t="n">
         <v>1</v>
@@ -28282,7 +28282,7 @@
         <v>130</v>
       </c>
       <c r="F227" t="n">
-        <v>565000</v>
+        <v>564000</v>
       </c>
       <c r="G227" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>120</v>
       </c>
       <c r="F228" t="n">
-        <v>600000</v>
+        <v>576000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28405,7 +28405,7 @@
         <v>80</v>
       </c>
       <c r="F230" t="n">
-        <v>619000</v>
+        <v>632000</v>
       </c>
       <c r="G230" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>90</v>
       </c>
       <c r="F231" t="n">
-        <v>416000</v>
+        <v>408000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28610,7 +28610,7 @@
         <v>1000</v>
       </c>
       <c r="F235" t="n">
-        <v>484000</v>
+        <v>506000</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
@@ -28651,7 +28651,7 @@
         <v>100</v>
       </c>
       <c r="F236" t="n">
-        <v>1238000</v>
+        <v>1233000</v>
       </c>
       <c r="G236" t="n">
         <v>1</v>
@@ -28733,7 +28733,7 @@
         <v>70</v>
       </c>
       <c r="F238" t="n">
-        <v>478000</v>
+        <v>519000</v>
       </c>
       <c r="G238" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>90</v>
       </c>
       <c r="F240" t="n">
-        <v>579000</v>
+        <v>588000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>1000</v>
       </c>
       <c r="F241" t="n">
-        <v>411000</v>
+        <v>384000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>40</v>
       </c>
       <c r="F242" t="n">
-        <v>501000</v>
+        <v>497000</v>
       </c>
       <c r="G242" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>50</v>
       </c>
       <c r="F254" t="n">
-        <v>590000</v>
+        <v>646000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>120</v>
       </c>
       <c r="F255" t="n">
-        <v>238000</v>
+        <v>260000</v>
       </c>
       <c r="G255" t="n">
         <v>1</v>
@@ -29471,7 +29471,7 @@
         <v>40</v>
       </c>
       <c r="F256" t="n">
-        <v>276000</v>
+        <v>296000</v>
       </c>
       <c r="G256" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>70</v>
       </c>
       <c r="F258" t="n">
-        <v>265000</v>
+        <v>318000</v>
       </c>
       <c r="G258" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>140</v>
       </c>
       <c r="F261" t="n">
-        <v>634000</v>
+        <v>626000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>130</v>
       </c>
       <c r="F264" t="n">
-        <v>884000</v>
+        <v>913000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>50</v>
       </c>
       <c r="F266" t="n">
-        <v>525000</v>
+        <v>507000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -29922,7 +29922,7 @@
         <v>1010</v>
       </c>
       <c r="F267" t="n">
-        <v>460000</v>
+        <v>462000</v>
       </c>
       <c r="G267" t="n">
         <v>1</v>
@@ -29963,7 +29963,7 @@
         <v>1010</v>
       </c>
       <c r="F268" t="n">
-        <v>689000</v>
+        <v>657000</v>
       </c>
       <c r="G268" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>20</v>
       </c>
       <c r="F271" t="n">
-        <v>691000</v>
+        <v>677000</v>
       </c>
       <c r="G271" t="n">
         <v>1</v>
@@ -30168,7 +30168,7 @@
         <v>120</v>
       </c>
       <c r="F273" t="n">
-        <v>642000</v>
+        <v>618000</v>
       </c>
       <c r="G273" t="n">
         <v>1</v>
@@ -30250,7 +30250,7 @@
         <v>60</v>
       </c>
       <c r="F275" t="n">
-        <v>795000</v>
+        <v>769000</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
@@ -30332,7 +30332,7 @@
         <v>30</v>
       </c>
       <c r="F277" t="n">
-        <v>764000</v>
+        <v>801000</v>
       </c>
       <c r="G277" t="n">
         <v>1</v>
@@ -30414,7 +30414,7 @@
         <v>110</v>
       </c>
       <c r="F279" t="n">
-        <v>460000</v>
+        <v>430000</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
@@ -30578,7 +30578,7 @@
         <v>100</v>
       </c>
       <c r="F283" t="n">
-        <v>251000</v>
+        <v>259000</v>
       </c>
       <c r="G283" t="n">
         <v>1</v>
@@ -30619,7 +30619,7 @@
         <v>50</v>
       </c>
       <c r="F284" t="n">
-        <v>364000</v>
+        <v>362000</v>
       </c>
       <c r="G284" t="n">
         <v>1</v>
@@ -30701,7 +30701,7 @@
         <v>110</v>
       </c>
       <c r="F286" t="n">
-        <v>476000</v>
+        <v>459000</v>
       </c>
       <c r="G286" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>1010</v>
       </c>
       <c r="F290" t="n">
-        <v>304000</v>
+        <v>313000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>50</v>
       </c>
       <c r="F296" t="n">
-        <v>426000</v>
+        <v>419000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31152,7 +31152,7 @@
         <v>1000</v>
       </c>
       <c r="F297" t="n">
-        <v>589000</v>
+        <v>581000</v>
       </c>
       <c r="G297" t="n">
         <v>1</v>
@@ -31316,7 +31316,7 @@
         <v>140</v>
       </c>
       <c r="F301" t="n">
-        <v>541000</v>
+        <v>526000</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -31398,7 +31398,7 @@
         <v>110</v>
       </c>
       <c r="F303" t="n">
-        <v>240000</v>
+        <v>261000</v>
       </c>
       <c r="G303" t="n">
         <v>1</v>
@@ -31439,7 +31439,7 @@
         <v>50</v>
       </c>
       <c r="F304" t="n">
-        <v>308000</v>
+        <v>333000</v>
       </c>
       <c r="G304" t="n">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>10</v>
       </c>
       <c r="F309" t="n">
-        <v>395000</v>
+        <v>383000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31685,7 +31685,7 @@
         <v>150</v>
       </c>
       <c r="F310" t="n">
-        <v>524000</v>
+        <v>508000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>100</v>
       </c>
       <c r="F311" t="n">
-        <v>595000</v>
+        <v>614000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>110</v>
       </c>
       <c r="F315" t="n">
-        <v>444000</v>
+        <v>435000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>120</v>
       </c>
       <c r="F317" t="n">
-        <v>472000</v>
+        <v>478000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>140</v>
       </c>
       <c r="F335" t="n">
-        <v>395000</v>
+        <v>422000</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -32751,7 +32751,7 @@
         <v>20</v>
       </c>
       <c r="F336" t="n">
-        <v>529000</v>
+        <v>531000</v>
       </c>
       <c r="G336" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>140</v>
       </c>
       <c r="F339" t="n">
-        <v>496000</v>
+        <v>483000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32956,7 +32956,7 @@
         <v>30</v>
       </c>
       <c r="F341" t="n">
-        <v>473000</v>
+        <v>524000</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>50</v>
       </c>
       <c r="F350" t="n">
-        <v>605000</v>
+        <v>600000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33459,7 +33459,7 @@
         <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>763000</v>
+        <v>767000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33500,7 +33500,7 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>647000</v>
+        <v>653000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33541,7 +33541,7 @@
         <v>140</v>
       </c>
       <c r="F4" t="n">
-        <v>863000</v>
+        <v>816000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>1007000</v>
+        <v>995000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>750000</v>
+        <v>732000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
         <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>834000</v>
+        <v>804000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>711000</v>
+        <v>716000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>821000</v>
+        <v>840000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -33992,7 +33992,7 @@
         <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>973000</v>
+        <v>980000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>160</v>
       </c>
       <c r="F18" t="n">
-        <v>1029000</v>
+        <v>986000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -34156,7 +34156,7 @@
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>913000</v>
+        <v>932000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>994000</v>
+        <v>966000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>1116000</v>
+        <v>1087000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34361,7 +34361,7 @@
         <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>934000</v>
+        <v>958000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -34443,7 +34443,7 @@
         <v>70</v>
       </c>
       <c r="F26" t="n">
-        <v>646000</v>
+        <v>669000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -34484,7 +34484,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>978000</v>
+        <v>958000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>667000</v>
+        <v>654000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34607,7 +34607,7 @@
         <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>918000</v>
+        <v>922000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -34648,7 +34648,7 @@
         <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>889000</v>
+        <v>813000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>697000</v>
+        <v>723000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34771,7 +34771,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>696000</v>
+        <v>652000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -34812,7 +34812,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>657000</v>
+        <v>666000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -34853,7 +34853,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>572000</v>
+        <v>581000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>140</v>
       </c>
       <c r="F37" t="n">
-        <v>822000</v>
+        <v>803000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34935,7 +34935,7 @@
         <v>70</v>
       </c>
       <c r="F38" t="n">
-        <v>718000</v>
+        <v>735000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>60</v>
       </c>
       <c r="F39" t="n">
-        <v>968000</v>
+        <v>957000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35017,7 +35017,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>798000</v>
+        <v>773000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -35099,7 +35099,7 @@
         <v>130</v>
       </c>
       <c r="F42" t="n">
-        <v>618000</v>
+        <v>592000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>100</v>
       </c>
       <c r="F43" t="n">
-        <v>841000</v>
+        <v>818000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>100</v>
       </c>
       <c r="F44" t="n">
-        <v>647000</v>
+        <v>649000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -35222,7 +35222,7 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>754000</v>
+        <v>755000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -35304,7 +35304,7 @@
         <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>773000</v>
+        <v>758000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35345,7 +35345,7 @@
         <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>492000</v>
+        <v>479000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>923000</v>
+        <v>941000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35550,7 +35550,7 @@
         <v>70</v>
       </c>
       <c r="F53" t="n">
-        <v>1113000</v>
+        <v>1095000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -35632,7 +35632,7 @@
         <v>160</v>
       </c>
       <c r="F55" t="n">
-        <v>320000</v>
+        <v>349000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -35714,7 +35714,7 @@
         <v>140</v>
       </c>
       <c r="F57" t="n">
-        <v>945000</v>
+        <v>948000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>80</v>
       </c>
       <c r="F58" t="n">
-        <v>826000</v>
+        <v>829000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35878,7 +35878,7 @@
         <v>1000</v>
       </c>
       <c r="F61" t="n">
-        <v>1018000</v>
+        <v>991000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>1000</v>
       </c>
       <c r="F62" t="n">
-        <v>877000</v>
+        <v>885000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>60</v>
       </c>
       <c r="F66" t="n">
-        <v>844000</v>
+        <v>872000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -36206,7 +36206,7 @@
         <v>120</v>
       </c>
       <c r="F69" t="n">
-        <v>485000</v>
+        <v>470000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>907000</v>
+        <v>913000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>160</v>
       </c>
       <c r="F71" t="n">
-        <v>961000</v>
+        <v>965000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36329,7 +36329,7 @@
         <v>60</v>
       </c>
       <c r="F72" t="n">
-        <v>624000</v>
+        <v>639000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>570000</v>
+        <v>597000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -36493,7 +36493,7 @@
         <v>150</v>
       </c>
       <c r="F76" t="n">
-        <v>504000</v>
+        <v>587000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -36534,7 +36534,7 @@
         <v>50</v>
       </c>
       <c r="F77" t="n">
-        <v>431000</v>
+        <v>436000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -36575,7 +36575,7 @@
         <v>60</v>
       </c>
       <c r="F78" t="n">
-        <v>613000</v>
+        <v>662000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>90</v>
       </c>
       <c r="F80" t="n">
-        <v>526000</v>
+        <v>550000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36698,7 +36698,7 @@
         <v>80</v>
       </c>
       <c r="F81" t="n">
-        <v>806000</v>
+        <v>838000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>60</v>
       </c>
       <c r="F83" t="n">
-        <v>684000</v>
+        <v>668000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>80</v>
       </c>
       <c r="F87" t="n">
-        <v>821000</v>
+        <v>800000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37026,7 +37026,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>458000</v>
+        <v>486000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>1010</v>
       </c>
       <c r="F90" t="n">
-        <v>597000</v>
+        <v>589000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37190,7 +37190,7 @@
         <v>40</v>
       </c>
       <c r="F93" t="n">
-        <v>641000</v>
+        <v>656000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>40</v>
       </c>
       <c r="F94" t="n">
-        <v>1144000</v>
+        <v>1122000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37272,7 +37272,7 @@
         <v>1010</v>
       </c>
       <c r="F95" t="n">
-        <v>940000</v>
+        <v>905000</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -37354,7 +37354,7 @@
         <v>80</v>
       </c>
       <c r="F97" t="n">
-        <v>699000</v>
+        <v>708000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>150</v>
       </c>
       <c r="F98" t="n">
-        <v>709000</v>
+        <v>714000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>20</v>
       </c>
       <c r="F99" t="n">
-        <v>1105000</v>
+        <v>1120000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>10</v>
       </c>
       <c r="F103" t="n">
-        <v>664000</v>
+        <v>681000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>70</v>
       </c>
       <c r="F106" t="n">
-        <v>731000</v>
+        <v>734000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37846,7 +37846,7 @@
         <v>120</v>
       </c>
       <c r="F109" t="n">
-        <v>585000</v>
+        <v>598000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -37887,7 +37887,7 @@
         <v>150</v>
       </c>
       <c r="F110" t="n">
-        <v>422000</v>
+        <v>484000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>130</v>
       </c>
       <c r="F115" t="n">
-        <v>951000</v>
+        <v>937000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>1010</v>
       </c>
       <c r="F118" t="n">
-        <v>309000</v>
+        <v>341000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38256,7 +38256,7 @@
         <v>90</v>
       </c>
       <c r="F119" t="n">
-        <v>583000</v>
+        <v>584000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>20</v>
       </c>
       <c r="F120" t="n">
-        <v>706000</v>
+        <v>702000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38420,7 +38420,7 @@
         <v>130</v>
       </c>
       <c r="F123" t="n">
-        <v>555000</v>
+        <v>562000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>474000</v>
+        <v>471000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38666,7 +38666,7 @@
         <v>120</v>
       </c>
       <c r="F129" t="n">
-        <v>642000</v>
+        <v>661000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -38707,7 +38707,7 @@
         <v>30</v>
       </c>
       <c r="F130" t="n">
-        <v>667000</v>
+        <v>678000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>1000</v>
       </c>
       <c r="F133" t="n">
-        <v>499000</v>
+        <v>519000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38871,7 +38871,7 @@
         <v>150</v>
       </c>
       <c r="F134" t="n">
-        <v>432000</v>
+        <v>446000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>110</v>
       </c>
       <c r="F137" t="n">
-        <v>402000</v>
+        <v>411000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -39117,7 +39117,7 @@
         <v>80</v>
       </c>
       <c r="F140" t="n">
-        <v>304000</v>
+        <v>366000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -39199,7 +39199,7 @@
         <v>150</v>
       </c>
       <c r="F142" t="n">
-        <v>724000</v>
+        <v>714000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>1014000</v>
+        <v>1005000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>160</v>
       </c>
       <c r="F6" t="n">
-        <v>930000</v>
+        <v>924000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -39825,7 +39825,7 @@
         <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>523000</v>
+        <v>531000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -39907,7 +39907,7 @@
         <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>774000</v>
+        <v>761000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -39948,7 +39948,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>581000</v>
+        <v>557000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -39989,7 +39989,7 @@
         <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>634000</v>
+        <v>624000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -40030,7 +40030,7 @@
         <v>40</v>
       </c>
       <c r="F12" t="n">
-        <v>810000</v>
+        <v>869000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>746000</v>
+        <v>738000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40235,7 +40235,7 @@
         <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>744000</v>
+        <v>775000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>140</v>
       </c>
       <c r="F19" t="n">
-        <v>801000</v>
+        <v>807000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40358,7 +40358,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>623000</v>
+        <v>622000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -40399,7 +40399,7 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>895000</v>
+        <v>867000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>942000</v>
+        <v>917000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40727,7 +40727,7 @@
         <v>1000</v>
       </c>
       <c r="F29" t="n">
-        <v>695000</v>
+        <v>686000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>821000</v>
+        <v>802000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         <v>1010</v>
       </c>
       <c r="F31" t="n">
-        <v>639000</v>
+        <v>645000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -40850,7 +40850,7 @@
         <v>70</v>
       </c>
       <c r="F32" t="n">
-        <v>529000</v>
+        <v>530000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8345,7 +8345,7 @@
         <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>643000</v>
+        <v>644000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>504000</v>
+        <v>488000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>819000</v>
+        <v>760000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>1000</v>
       </c>
       <c r="F8" t="n">
-        <v>714000</v>
+        <v>704000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>683000</v>
+        <v>693000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>395000</v>
+        <v>408000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>572000</v>
+        <v>566000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>316000</v>
+        <v>374000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>1010</v>
       </c>
       <c r="F16" t="n">
-        <v>934000</v>
+        <v>902000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>568000</v>
+        <v>555000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>1000</v>
       </c>
       <c r="F18" t="n">
-        <v>302000</v>
+        <v>305000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>587000</v>
+        <v>571000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>341000</v>
+        <v>335000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>740000</v>
+        <v>733000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>150</v>
       </c>
       <c r="F23" t="n">
-        <v>437000</v>
+        <v>434000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>722000</v>
+        <v>766000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9247,7 +9247,7 @@
         <v>160</v>
       </c>
       <c r="F27" t="n">
-        <v>683000</v>
+        <v>686000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>160</v>
       </c>
       <c r="F28" t="n">
-        <v>819000</v>
+        <v>840000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>551000</v>
+        <v>522000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="n">
-        <v>906000</v>
+        <v>913000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>120</v>
       </c>
       <c r="F39" t="n">
-        <v>537000</v>
+        <v>544000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>609000</v>
+        <v>623000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>70</v>
       </c>
       <c r="F42" t="n">
-        <v>727000</v>
+        <v>721000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9944,7 +9944,7 @@
         <v>110</v>
       </c>
       <c r="F44" t="n">
-        <v>858000</v>
+        <v>910000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>130</v>
       </c>
       <c r="F48" t="n">
-        <v>617000</v>
+        <v>620000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>60</v>
       </c>
       <c r="F52" t="n">
-        <v>494000</v>
+        <v>501000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>60</v>
       </c>
       <c r="F54" t="n">
-        <v>743000</v>
+        <v>733000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10518,7 +10518,7 @@
         <v>140</v>
       </c>
       <c r="F58" t="n">
-        <v>571000</v>
+        <v>564000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>483000</v>
+        <v>481000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>479000</v>
+        <v>465000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>635000</v>
+        <v>643000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>60</v>
       </c>
       <c r="F65" t="n">
-        <v>466000</v>
+        <v>459000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>935000</v>
+        <v>954000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>831000</v>
+        <v>836000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
         <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>332000</v>
+        <v>357000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>70</v>
       </c>
       <c r="F73" t="n">
-        <v>517000</v>
+        <v>525000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>520000</v>
+        <v>508000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>487000</v>
+        <v>517000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
         <v>150</v>
       </c>
       <c r="F80" t="n">
-        <v>729000</v>
+        <v>708000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -11707,7 +11707,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>693000</v>
+        <v>686000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11789,7 +11789,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>732000</v>
+        <v>743000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>706000</v>
+        <v>750000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>1010</v>
       </c>
       <c r="F91" t="n">
-        <v>671000</v>
+        <v>647000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>429000</v>
+        <v>427000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="n">
-        <v>483000</v>
+        <v>458000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>120</v>
       </c>
       <c r="F102" t="n">
-        <v>462000</v>
+        <v>447000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>70</v>
       </c>
       <c r="F103" t="n">
-        <v>626000</v>
+        <v>601000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>636000</v>
+        <v>645000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>160</v>
       </c>
       <c r="F105" t="n">
-        <v>348000</v>
+        <v>330000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>449000</v>
+        <v>450000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>801000</v>
+        <v>795000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         <v>30</v>
       </c>
       <c r="F110" t="n">
-        <v>698000</v>
+        <v>713000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>1010</v>
       </c>
       <c r="F112" t="n">
-        <v>688000</v>
+        <v>663000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>150</v>
       </c>
       <c r="F117" t="n">
-        <v>524000</v>
+        <v>561000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>795000</v>
+        <v>771000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>70</v>
       </c>
       <c r="F122" t="n">
-        <v>770000</v>
+        <v>760000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -13183,7 +13183,7 @@
         <v>1010</v>
       </c>
       <c r="F123" t="n">
-        <v>789000</v>
+        <v>759000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>80</v>
       </c>
       <c r="F124" t="n">
-        <v>912000</v>
+        <v>924000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>140</v>
       </c>
       <c r="F125" t="n">
-        <v>529000</v>
+        <v>508000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>658000</v>
+        <v>612000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>559000</v>
+        <v>552000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13429,7 +13429,7 @@
         <v>50</v>
       </c>
       <c r="F129" t="n">
-        <v>563000</v>
+        <v>529000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -13634,7 +13634,7 @@
         <v>10</v>
       </c>
       <c r="F134" t="n">
-        <v>540000</v>
+        <v>506000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>50</v>
       </c>
       <c r="F136" t="n">
-        <v>321000</v>
+        <v>324000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>160</v>
       </c>
       <c r="F137" t="n">
-        <v>384000</v>
+        <v>392000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>110</v>
       </c>
       <c r="F138" t="n">
-        <v>554000</v>
+        <v>546000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>905000</v>
+        <v>868000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>1010</v>
       </c>
       <c r="F140" t="n">
-        <v>527000</v>
+        <v>505000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>20</v>
       </c>
       <c r="F141" t="n">
-        <v>632000</v>
+        <v>605000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>90</v>
       </c>
       <c r="F142" t="n">
-        <v>576000</v>
+        <v>555000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>150</v>
       </c>
       <c r="F143" t="n">
-        <v>679000</v>
+        <v>666000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>140</v>
       </c>
       <c r="F145" t="n">
-        <v>680000</v>
+        <v>658000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>100</v>
       </c>
       <c r="F146" t="n">
-        <v>362000</v>
+        <v>398000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>150</v>
       </c>
       <c r="F152" t="n">
-        <v>849000</v>
+        <v>851000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>702000</v>
+        <v>680000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>60</v>
       </c>
       <c r="F156" t="n">
-        <v>550000</v>
+        <v>553000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>90</v>
       </c>
       <c r="F157" t="n">
-        <v>526000</v>
+        <v>496000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>50</v>
       </c>
       <c r="F158" t="n">
-        <v>603000</v>
+        <v>620000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>518000</v>
+        <v>496000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         <v>160</v>
       </c>
       <c r="F162" t="n">
-        <v>479000</v>
+        <v>486000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>10</v>
       </c>
       <c r="F163" t="n">
-        <v>566000</v>
+        <v>556000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -14946,7 +14946,7 @@
         <v>120</v>
       </c>
       <c r="F166" t="n">
-        <v>527000</v>
+        <v>534000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>160</v>
       </c>
       <c r="F167" t="n">
-        <v>860000</v>
+        <v>835000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>70</v>
       </c>
       <c r="F172" t="n">
-        <v>523000</v>
+        <v>530000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15479,7 +15479,7 @@
         <v>1000</v>
       </c>
       <c r="F179" t="n">
-        <v>924000</v>
+        <v>928000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>110</v>
       </c>
       <c r="F180" t="n">
-        <v>248000</v>
+        <v>253000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>130</v>
       </c>
       <c r="F181" t="n">
-        <v>436000</v>
+        <v>419000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15602,7 +15602,7 @@
         <v>70</v>
       </c>
       <c r="F182" t="n">
-        <v>582000</v>
+        <v>581000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         <v>140</v>
       </c>
       <c r="F183" t="n">
-        <v>442000</v>
+        <v>466000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>70</v>
       </c>
       <c r="F185" t="n">
-        <v>637000</v>
+        <v>627000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>100</v>
       </c>
       <c r="F186" t="n">
-        <v>658000</v>
+        <v>646000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15848,7 +15848,7 @@
         <v>100</v>
       </c>
       <c r="F188" t="n">
-        <v>892000</v>
+        <v>897000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -16176,7 +16176,7 @@
         <v>1000</v>
       </c>
       <c r="F196" t="n">
-        <v>645000</v>
+        <v>667000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
         <v>50</v>
       </c>
       <c r="F197" t="n">
-        <v>596000</v>
+        <v>586000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>40</v>
       </c>
       <c r="F198" t="n">
-        <v>250000</v>
+        <v>270000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>40</v>
       </c>
       <c r="F199" t="n">
-        <v>685000</v>
+        <v>676000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>50</v>
       </c>
       <c r="F203" t="n">
-        <v>734000</v>
+        <v>698000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>50</v>
       </c>
       <c r="F204" t="n">
-        <v>495000</v>
+        <v>475000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
         <v>1000</v>
       </c>
       <c r="F206" t="n">
-        <v>665000</v>
+        <v>644000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>90</v>
       </c>
       <c r="F207" t="n">
-        <v>773000</v>
+        <v>794000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -16668,7 +16668,7 @@
         <v>50</v>
       </c>
       <c r="F208" t="n">
-        <v>766000</v>
+        <v>752000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -16709,7 +16709,7 @@
         <v>160</v>
       </c>
       <c r="F209" t="n">
-        <v>643000</v>
+        <v>639000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>60</v>
       </c>
       <c r="F213" t="n">
-        <v>724000</v>
+        <v>721000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -16914,7 +16914,7 @@
         <v>10</v>
       </c>
       <c r="F214" t="n">
-        <v>268000</v>
+        <v>329000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -16996,7 +16996,7 @@
         <v>90</v>
       </c>
       <c r="F216" t="n">
-        <v>741000</v>
+        <v>664000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>140</v>
       </c>
       <c r="F218" t="n">
-        <v>587000</v>
+        <v>586000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>160</v>
       </c>
       <c r="F219" t="n">
-        <v>584000</v>
+        <v>607000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>120</v>
       </c>
       <c r="F220" t="n">
-        <v>773000</v>
+        <v>759000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>769000</v>
+        <v>754000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17242,7 +17242,7 @@
         <v>130</v>
       </c>
       <c r="F222" t="n">
-        <v>626000</v>
+        <v>590000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         <v>150</v>
       </c>
       <c r="F227" t="n">
-        <v>502000</v>
+        <v>503000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -17488,7 +17488,7 @@
         <v>70</v>
       </c>
       <c r="F228" t="n">
-        <v>740000</v>
+        <v>758000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>130</v>
       </c>
       <c r="F229" t="n">
-        <v>586000</v>
+        <v>631000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>557000</v>
+        <v>529000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17939,7 +17939,7 @@
         <v>90</v>
       </c>
       <c r="F239" t="n">
-        <v>646000</v>
+        <v>611000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         <v>1000</v>
       </c>
       <c r="F240" t="n">
-        <v>795000</v>
+        <v>788000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -18021,7 +18021,7 @@
         <v>1000</v>
       </c>
       <c r="F241" t="n">
-        <v>722000</v>
+        <v>666000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>613000</v>
+        <v>633000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18226,7 +18226,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>1162000</v>
+        <v>1074000</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>80</v>
       </c>
       <c r="F247" t="n">
-        <v>674000</v>
+        <v>649000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>110</v>
       </c>
       <c r="F248" t="n">
-        <v>436000</v>
+        <v>431000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>1010</v>
       </c>
       <c r="F250" t="n">
-        <v>913000</v>
+        <v>937000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>160</v>
       </c>
       <c r="F251" t="n">
-        <v>654000</v>
+        <v>626000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         <v>130</v>
       </c>
       <c r="F252" t="n">
-        <v>879000</v>
+        <v>823000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -18513,7 +18513,7 @@
         <v>140</v>
       </c>
       <c r="F253" t="n">
-        <v>700000</v>
+        <v>705000</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>20</v>
       </c>
       <c r="F254" t="n">
-        <v>768000</v>
+        <v>745000</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
         <v>30</v>
       </c>
       <c r="F255" t="n">
-        <v>701000</v>
+        <v>706000</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -18636,7 +18636,7 @@
         <v>130</v>
       </c>
       <c r="F256" t="n">
-        <v>793000</v>
+        <v>777000</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>90</v>
       </c>
       <c r="F257" t="n">
-        <v>498000</v>
+        <v>493000</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>60</v>
       </c>
       <c r="F258" t="n">
-        <v>771000</v>
+        <v>779000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -18759,7 +18759,7 @@
         <v>10</v>
       </c>
       <c r="F259" t="n">
-        <v>706000</v>
+        <v>690000</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -18800,7 +18800,7 @@
         <v>30</v>
       </c>
       <c r="F260" t="n">
-        <v>401000</v>
+        <v>414000</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -18841,7 +18841,7 @@
         <v>150</v>
       </c>
       <c r="F261" t="n">
-        <v>520000</v>
+        <v>487000</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -18964,7 +18964,7 @@
         <v>20</v>
       </c>
       <c r="F264" t="n">
-        <v>882000</v>
+        <v>888000</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -19098,7 +19098,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>520000</v>
+        <v>511000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>731000</v>
+        <v>708000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19221,7 +19221,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>500000</v>
+        <v>472000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -19344,7 +19344,7 @@
         <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>562000</v>
+        <v>566000</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -19385,7 +19385,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>292000</v>
+        <v>335000</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>504000</v>
+        <v>506000</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -19549,7 +19549,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>921000</v>
+        <v>908000</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>332000</v>
+        <v>370000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19836,7 +19836,7 @@
         <v>1010</v>
       </c>
       <c r="F21" t="n">
-        <v>622000</v>
+        <v>605000</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>435000</v>
+        <v>465000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>774000</v>
+        <v>741000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>140</v>
       </c>
       <c r="F26" t="n">
-        <v>616000</v>
+        <v>644000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>1010</v>
       </c>
       <c r="F28" t="n">
-        <v>558000</v>
+        <v>559000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20287,7 +20287,7 @@
         <v>80</v>
       </c>
       <c r="F32" t="n">
-        <v>574000</v>
+        <v>571000</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>551000</v>
+        <v>573000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20369,7 +20369,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>783000</v>
+        <v>772000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>484000</v>
+        <v>482000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20451,7 +20451,7 @@
         <v>1010</v>
       </c>
       <c r="F36" t="n">
-        <v>528000</v>
+        <v>506000</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -20492,7 +20492,7 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>553000</v>
+        <v>570000</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -20574,7 +20574,7 @@
         <v>130</v>
       </c>
       <c r="F39" t="n">
-        <v>377000</v>
+        <v>360000</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>160</v>
       </c>
       <c r="F40" t="n">
-        <v>592000</v>
+        <v>614000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>561000</v>
+        <v>554000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>648000</v>
+        <v>617000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>80</v>
       </c>
       <c r="F46" t="n">
-        <v>647000</v>
+        <v>617000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>568000</v>
+        <v>627000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>120</v>
       </c>
       <c r="F48" t="n">
-        <v>230000</v>
+        <v>241000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>70</v>
       </c>
       <c r="F50" t="n">
-        <v>473000</v>
+        <v>467000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>150</v>
       </c>
       <c r="F52" t="n">
-        <v>511000</v>
+        <v>524000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>1010</v>
       </c>
       <c r="F54" t="n">
-        <v>604000</v>
+        <v>644000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>594000</v>
+        <v>596000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>621000</v>
+        <v>631000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>434000</v>
+        <v>439000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>140</v>
       </c>
       <c r="F60" t="n">
-        <v>348000</v>
+        <v>356000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21517,7 +21517,7 @@
         <v>160</v>
       </c>
       <c r="F62" t="n">
-        <v>708000</v>
+        <v>691000</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>666000</v>
+        <v>695000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>556000</v>
+        <v>583000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>160</v>
       </c>
       <c r="F70" t="n">
-        <v>273000</v>
+        <v>325000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>140</v>
       </c>
       <c r="F71" t="n">
-        <v>475000</v>
+        <v>491000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21927,7 +21927,7 @@
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>428000</v>
+        <v>420000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -22050,7 +22050,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>268000</v>
+        <v>325000</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>440000</v>
+        <v>455000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F79" t="n">
-        <v>554000</v>
+        <v>584000</v>
       </c>
       <c r="G79" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>631000</v>
+        <v>619000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>498000</v>
+        <v>499000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>150</v>
       </c>
       <c r="F83" t="n">
-        <v>412000</v>
+        <v>429000</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>110</v>
       </c>
       <c r="F84" t="n">
-        <v>472000</v>
+        <v>488000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22460,7 +22460,7 @@
         <v>50</v>
       </c>
       <c r="F85" t="n">
-        <v>768000</v>
+        <v>745000</v>
       </c>
       <c r="G85" t="n">
         <v>1</v>
@@ -22624,7 +22624,7 @@
         <v>50</v>
       </c>
       <c r="F89" t="n">
-        <v>358000</v>
+        <v>368000</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="F91" t="n">
-        <v>646000</v>
+        <v>673000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22747,7 +22747,7 @@
         <v>1000</v>
       </c>
       <c r="F92" t="n">
-        <v>511000</v>
+        <v>446000</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -23034,7 +23034,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>635000</v>
+        <v>622000</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -23075,7 +23075,7 @@
         <v>140</v>
       </c>
       <c r="F100" t="n">
-        <v>634000</v>
+        <v>648000</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>90</v>
       </c>
       <c r="F101" t="n">
-        <v>621000</v>
+        <v>650000</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>80</v>
       </c>
       <c r="F106" t="n">
-        <v>759000</v>
+        <v>736000</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>150</v>
       </c>
       <c r="F108" t="n">
-        <v>683000</v>
+        <v>695000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23485,7 +23485,7 @@
         <v>120</v>
       </c>
       <c r="F110" t="n">
-        <v>474000</v>
+        <v>444000</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>1010</v>
       </c>
       <c r="F111" t="n">
-        <v>858000</v>
+        <v>838000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23649,7 +23649,7 @@
         <v>150</v>
       </c>
       <c r="F114" t="n">
-        <v>344000</v>
+        <v>370000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>459000</v>
+        <v>456000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>1000</v>
       </c>
       <c r="F117" t="n">
-        <v>392000</v>
+        <v>398000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23813,7 +23813,7 @@
         <v>80</v>
       </c>
       <c r="F118" t="n">
-        <v>719000</v>
+        <v>714000</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>130</v>
       </c>
       <c r="F119" t="n">
-        <v>914000</v>
+        <v>929000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23895,7 +23895,7 @@
         <v>1010</v>
       </c>
       <c r="F120" t="n">
-        <v>322000</v>
+        <v>335000</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -24059,7 +24059,7 @@
         <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>479000</v>
+        <v>489000</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -24182,7 +24182,7 @@
         <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>323000</v>
+        <v>325000</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>30</v>
       </c>
       <c r="F128" t="n">
-        <v>638000</v>
+        <v>663000</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -24346,7 +24346,7 @@
         <v>70</v>
       </c>
       <c r="F131" t="n">
-        <v>434000</v>
+        <v>474000</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -24428,7 +24428,7 @@
         <v>70</v>
       </c>
       <c r="F133" t="n">
-        <v>540000</v>
+        <v>583000</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -24510,7 +24510,7 @@
         <v>130</v>
       </c>
       <c r="F135" t="n">
-        <v>485000</v>
+        <v>491000</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -24592,7 +24592,7 @@
         <v>130</v>
       </c>
       <c r="F137" t="n">
-        <v>1050000</v>
+        <v>1040000</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -24674,7 +24674,7 @@
         <v>20</v>
       </c>
       <c r="F139" t="n">
-        <v>474000</v>
+        <v>480000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24838,7 +24838,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>970000</v>
+        <v>965000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24879,7 +24879,7 @@
         <v>120</v>
       </c>
       <c r="F144" t="n">
-        <v>474000</v>
+        <v>471000</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -24961,7 +24961,7 @@
         <v>1000</v>
       </c>
       <c r="F146" t="n">
-        <v>535000</v>
+        <v>563000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25002,7 +25002,7 @@
         <v>140</v>
       </c>
       <c r="F147" t="n">
-        <v>537000</v>
+        <v>540000</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -25043,7 +25043,7 @@
         <v>90</v>
       </c>
       <c r="F148" t="n">
-        <v>393000</v>
+        <v>363000</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -25125,7 +25125,7 @@
         <v>140</v>
       </c>
       <c r="F150" t="n">
-        <v>465000</v>
+        <v>453000</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -25248,7 +25248,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>540000</v>
+        <v>549000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F154" t="n">
-        <v>369000</v>
+        <v>371000</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>655000</v>
+        <v>623000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25412,7 +25412,7 @@
         <v>150</v>
       </c>
       <c r="F157" t="n">
-        <v>819000</v>
+        <v>842000</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -25453,7 +25453,7 @@
         <v>30</v>
       </c>
       <c r="F158" t="n">
-        <v>575000</v>
+        <v>588000</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>140</v>
       </c>
       <c r="F160" t="n">
-        <v>483000</v>
+        <v>492000</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
@@ -25617,7 +25617,7 @@
         <v>1000</v>
       </c>
       <c r="F162" t="n">
-        <v>440000</v>
+        <v>455000</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
@@ -25822,7 +25822,7 @@
         <v>130</v>
       </c>
       <c r="F167" t="n">
-        <v>448000</v>
+        <v>449000</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -25863,7 +25863,7 @@
         <v>120</v>
       </c>
       <c r="F168" t="n">
-        <v>618000</v>
+        <v>580000</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
@@ -25904,7 +25904,7 @@
         <v>90</v>
       </c>
       <c r="F169" t="n">
-        <v>760000</v>
+        <v>723000</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>50</v>
       </c>
       <c r="F170" t="n">
-        <v>617000</v>
+        <v>595000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>100</v>
       </c>
       <c r="F171" t="n">
-        <v>593000</v>
+        <v>588000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26027,7 +26027,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>473000</v>
+        <v>484000</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
@@ -26109,7 +26109,7 @@
         <v>120</v>
       </c>
       <c r="F174" t="n">
-        <v>436000</v>
+        <v>448000</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
@@ -26191,7 +26191,7 @@
         <v>80</v>
       </c>
       <c r="F176" t="n">
-        <v>562000</v>
+        <v>561000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>160</v>
       </c>
       <c r="F179" t="n">
-        <v>564000</v>
+        <v>589000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>20</v>
       </c>
       <c r="F181" t="n">
-        <v>724000</v>
+        <v>765000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>1000</v>
       </c>
       <c r="F182" t="n">
-        <v>571000</v>
+        <v>572000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>1000</v>
       </c>
       <c r="F183" t="n">
-        <v>499000</v>
+        <v>484000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>40</v>
       </c>
       <c r="F184" t="n">
-        <v>678000</v>
+        <v>679000</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
@@ -26642,7 +26642,7 @@
         <v>10</v>
       </c>
       <c r="F187" t="n">
-        <v>248000</v>
+        <v>257000</v>
       </c>
       <c r="G187" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>120</v>
       </c>
       <c r="F190" t="n">
-        <v>445000</v>
+        <v>454000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26806,7 +26806,7 @@
         <v>80</v>
       </c>
       <c r="F191" t="n">
-        <v>871000</v>
+        <v>863000</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>70</v>
       </c>
       <c r="F196" t="n">
-        <v>698000</v>
+        <v>706000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>130</v>
       </c>
       <c r="F199" t="n">
-        <v>953000</v>
+        <v>963000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27175,7 +27175,7 @@
         <v>110</v>
       </c>
       <c r="F200" t="n">
-        <v>430000</v>
+        <v>448000</v>
       </c>
       <c r="G200" t="n">
         <v>1</v>
@@ -27216,7 +27216,7 @@
         <v>70</v>
       </c>
       <c r="F201" t="n">
-        <v>455000</v>
+        <v>448000</v>
       </c>
       <c r="G201" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>40</v>
       </c>
       <c r="F209" t="n">
-        <v>521000</v>
+        <v>551000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27585,7 +27585,7 @@
         <v>160</v>
       </c>
       <c r="F210" t="n">
-        <v>536000</v>
+        <v>532000</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>30</v>
       </c>
       <c r="F211" t="n">
-        <v>560000</v>
+        <v>564000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>30</v>
       </c>
       <c r="F213" t="n">
-        <v>616000</v>
+        <v>610000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>20</v>
       </c>
       <c r="F214" t="n">
-        <v>491000</v>
+        <v>463000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>725000</v>
+        <v>734000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -27872,7 +27872,7 @@
         <v>160</v>
       </c>
       <c r="F217" t="n">
-        <v>415000</v>
+        <v>388000</v>
       </c>
       <c r="G217" t="n">
         <v>1</v>
@@ -27995,7 +27995,7 @@
         <v>40</v>
       </c>
       <c r="F220" t="n">
-        <v>670000</v>
+        <v>740000</v>
       </c>
       <c r="G220" t="n">
         <v>1</v>
@@ -28118,7 +28118,7 @@
         <v>40</v>
       </c>
       <c r="F223" t="n">
-        <v>631000</v>
+        <v>645000</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
@@ -28200,7 +28200,7 @@
         <v>70</v>
       </c>
       <c r="F225" t="n">
-        <v>747000</v>
+        <v>696000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>1000</v>
       </c>
       <c r="F228" t="n">
-        <v>826000</v>
+        <v>850000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>80</v>
       </c>
       <c r="F231" t="n">
-        <v>712000</v>
+        <v>710000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28487,7 +28487,7 @@
         <v>110</v>
       </c>
       <c r="F232" t="n">
-        <v>423000</v>
+        <v>401000</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
@@ -28528,7 +28528,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="n">
-        <v>640000</v>
+        <v>646000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28774,7 +28774,7 @@
         <v>140</v>
       </c>
       <c r="F239" t="n">
-        <v>552000</v>
+        <v>560000</v>
       </c>
       <c r="G239" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="n">
-        <v>670000</v>
+        <v>668000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>70</v>
       </c>
       <c r="F241" t="n">
-        <v>606000</v>
+        <v>630000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28979,7 +28979,7 @@
         <v>1010</v>
       </c>
       <c r="F244" t="n">
-        <v>588000</v>
+        <v>595000</v>
       </c>
       <c r="G244" t="n">
         <v>1</v>
@@ -29061,7 +29061,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>569000</v>
+        <v>584000</v>
       </c>
       <c r="G246" t="n">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>160</v>
       </c>
       <c r="F248" t="n">
-        <v>608000</v>
+        <v>617000</v>
       </c>
       <c r="G248" t="n">
         <v>1</v>
@@ -29225,7 +29225,7 @@
         <v>50</v>
       </c>
       <c r="F250" t="n">
-        <v>582000</v>
+        <v>568000</v>
       </c>
       <c r="G250" t="n">
         <v>1</v>
@@ -29266,7 +29266,7 @@
         <v>1000</v>
       </c>
       <c r="F251" t="n">
-        <v>706000</v>
+        <v>665000</v>
       </c>
       <c r="G251" t="n">
         <v>1</v>
@@ -29307,7 +29307,7 @@
         <v>90</v>
       </c>
       <c r="F252" t="n">
-        <v>627000</v>
+        <v>645000</v>
       </c>
       <c r="G252" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>130</v>
       </c>
       <c r="F254" t="n">
-        <v>761000</v>
+        <v>737000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>90</v>
       </c>
       <c r="F255" t="n">
-        <v>853000</v>
+        <v>865000</v>
       </c>
       <c r="G255" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>70</v>
       </c>
       <c r="F258" t="n">
-        <v>369000</v>
+        <v>381000</v>
       </c>
       <c r="G258" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>120</v>
       </c>
       <c r="F261" t="n">
-        <v>654000</v>
+        <v>644000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29717,7 +29717,7 @@
         <v>10</v>
       </c>
       <c r="F262" t="n">
-        <v>619000</v>
+        <v>585000</v>
       </c>
       <c r="G262" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>10</v>
       </c>
       <c r="F264" t="n">
-        <v>929000</v>
+        <v>984000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29840,7 +29840,7 @@
         <v>20</v>
       </c>
       <c r="F265" t="n">
-        <v>720000</v>
+        <v>719000</v>
       </c>
       <c r="G265" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>1000</v>
       </c>
       <c r="F266" t="n">
-        <v>342000</v>
+        <v>343000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -29963,7 +29963,7 @@
         <v>60</v>
       </c>
       <c r="F268" t="n">
-        <v>747000</v>
+        <v>708000</v>
       </c>
       <c r="G268" t="n">
         <v>1</v>
@@ -30291,7 +30291,7 @@
         <v>1000</v>
       </c>
       <c r="F276" t="n">
-        <v>363000</v>
+        <v>345000</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
@@ -30373,7 +30373,7 @@
         <v>120</v>
       </c>
       <c r="F278" t="n">
-        <v>748000</v>
+        <v>752000</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -30455,7 +30455,7 @@
         <v>130</v>
       </c>
       <c r="F280" t="n">
-        <v>436000</v>
+        <v>414000</v>
       </c>
       <c r="G280" t="n">
         <v>1</v>
@@ -30537,7 +30537,7 @@
         <v>140</v>
       </c>
       <c r="F282" t="n">
-        <v>740000</v>
+        <v>729000</v>
       </c>
       <c r="G282" t="n">
         <v>1</v>
@@ -30742,7 +30742,7 @@
         <v>40</v>
       </c>
       <c r="F287" t="n">
-        <v>644000</v>
+        <v>643000</v>
       </c>
       <c r="G287" t="n">
         <v>1</v>
@@ -30783,7 +30783,7 @@
         <v>150</v>
       </c>
       <c r="F288" t="n">
-        <v>512000</v>
+        <v>503000</v>
       </c>
       <c r="G288" t="n">
         <v>1</v>
@@ -30824,7 +30824,7 @@
         <v>130</v>
       </c>
       <c r="F289" t="n">
-        <v>562000</v>
+        <v>541000</v>
       </c>
       <c r="G289" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>50</v>
       </c>
       <c r="F290" t="n">
-        <v>697000</v>
+        <v>750000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>90</v>
       </c>
       <c r="F291" t="n">
-        <v>500000</v>
+        <v>518000</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -30947,7 +30947,7 @@
         <v>100</v>
       </c>
       <c r="F292" t="n">
-        <v>1220000</v>
+        <v>1201000</v>
       </c>
       <c r="G292" t="n">
         <v>1</v>
@@ -30988,7 +30988,7 @@
         <v>100</v>
       </c>
       <c r="F293" t="n">
-        <v>816000</v>
+        <v>813000</v>
       </c>
       <c r="G293" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>30</v>
       </c>
       <c r="F296" t="n">
-        <v>830000</v>
+        <v>834000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31275,7 +31275,7 @@
         <v>120</v>
       </c>
       <c r="F300" t="n">
-        <v>624000</v>
+        <v>595000</v>
       </c>
       <c r="G300" t="n">
         <v>1</v>
@@ -31316,7 +31316,7 @@
         <v>100</v>
       </c>
       <c r="F301" t="n">
-        <v>547000</v>
+        <v>553000</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -31357,7 +31357,7 @@
         <v>90</v>
       </c>
       <c r="F302" t="n">
-        <v>979000</v>
+        <v>998000</v>
       </c>
       <c r="G302" t="n">
         <v>1</v>
@@ -31521,7 +31521,7 @@
         <v>1010</v>
       </c>
       <c r="F306" t="n">
-        <v>640000</v>
+        <v>653000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31603,7 +31603,7 @@
         <v>40</v>
       </c>
       <c r="F308" t="n">
-        <v>440000</v>
+        <v>441000</v>
       </c>
       <c r="G308" t="n">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>60</v>
       </c>
       <c r="F309" t="n">
-        <v>509000</v>
+        <v>505000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>10</v>
       </c>
       <c r="F311" t="n">
-        <v>466000</v>
+        <v>450000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31767,7 +31767,7 @@
         <v>10</v>
       </c>
       <c r="F312" t="n">
-        <v>669000</v>
+        <v>675000</v>
       </c>
       <c r="G312" t="n">
         <v>1</v>
@@ -31808,7 +31808,7 @@
         <v>90</v>
       </c>
       <c r="F313" t="n">
-        <v>610000</v>
+        <v>632000</v>
       </c>
       <c r="G313" t="n">
         <v>1</v>
@@ -31849,7 +31849,7 @@
         <v>1010</v>
       </c>
       <c r="F314" t="n">
-        <v>644000</v>
+        <v>637000</v>
       </c>
       <c r="G314" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>60</v>
       </c>
       <c r="F315" t="n">
-        <v>710000</v>
+        <v>727000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>100</v>
       </c>
       <c r="F317" t="n">
-        <v>633000</v>
+        <v>629000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32054,7 +32054,7 @@
         <v>50</v>
       </c>
       <c r="F319" t="n">
-        <v>239000</v>
+        <v>232000</v>
       </c>
       <c r="G319" t="n">
         <v>1</v>
@@ -32136,7 +32136,7 @@
         <v>110</v>
       </c>
       <c r="F321" t="n">
-        <v>422000</v>
+        <v>429000</v>
       </c>
       <c r="G321" t="n">
         <v>1</v>
@@ -32177,7 +32177,7 @@
         <v>60</v>
       </c>
       <c r="F322" t="n">
-        <v>608000</v>
+        <v>600000</v>
       </c>
       <c r="G322" t="n">
         <v>1</v>
@@ -32218,7 +32218,7 @@
         <v>10</v>
       </c>
       <c r="F323" t="n">
-        <v>583000</v>
+        <v>584000</v>
       </c>
       <c r="G323" t="n">
         <v>1</v>
@@ -32300,7 +32300,7 @@
         <v>1000</v>
       </c>
       <c r="F325" t="n">
-        <v>398000</v>
+        <v>410000</v>
       </c>
       <c r="G325" t="n">
         <v>1</v>
@@ -32382,7 +32382,7 @@
         <v>160</v>
       </c>
       <c r="F327" t="n">
-        <v>952000</v>
+        <v>961000</v>
       </c>
       <c r="G327" t="n">
         <v>1</v>
@@ -32464,7 +32464,7 @@
         <v>150</v>
       </c>
       <c r="F329" t="n">
-        <v>660000</v>
+        <v>652000</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
@@ -32546,7 +32546,7 @@
         <v>80</v>
       </c>
       <c r="F331" t="n">
-        <v>660000</v>
+        <v>647000</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -32587,7 +32587,7 @@
         <v>140</v>
       </c>
       <c r="F332" t="n">
-        <v>468000</v>
+        <v>479000</v>
       </c>
       <c r="G332" t="n">
         <v>1</v>
@@ -32669,7 +32669,7 @@
         <v>40</v>
       </c>
       <c r="F334" t="n">
-        <v>314000</v>
+        <v>312000</v>
       </c>
       <c r="G334" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>140</v>
       </c>
       <c r="F335" t="n">
-        <v>582000</v>
+        <v>588000</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -32792,7 +32792,7 @@
         <v>110</v>
       </c>
       <c r="F337" t="n">
-        <v>408000</v>
+        <v>409000</v>
       </c>
       <c r="G337" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>150</v>
       </c>
       <c r="F339" t="n">
-        <v>789000</v>
+        <v>806000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32915,7 +32915,7 @@
         <v>150</v>
       </c>
       <c r="F340" t="n">
-        <v>451000</v>
+        <v>435000</v>
       </c>
       <c r="G340" t="n">
         <v>1</v>
@@ -33038,7 +33038,7 @@
         <v>130</v>
       </c>
       <c r="F343" t="n">
-        <v>904000</v>
+        <v>889000</v>
       </c>
       <c r="G343" t="n">
         <v>1</v>
@@ -33079,7 +33079,7 @@
         <v>70</v>
       </c>
       <c r="F344" t="n">
-        <v>463000</v>
+        <v>455000</v>
       </c>
       <c r="G344" t="n">
         <v>1</v>
@@ -33120,7 +33120,7 @@
         <v>130</v>
       </c>
       <c r="F345" t="n">
-        <v>813000</v>
+        <v>782000</v>
       </c>
       <c r="G345" t="n">
         <v>1</v>
@@ -33161,7 +33161,7 @@
         <v>50</v>
       </c>
       <c r="F346" t="n">
-        <v>700000</v>
+        <v>696000</v>
       </c>
       <c r="G346" t="n">
         <v>1</v>
@@ -33202,7 +33202,7 @@
         <v>150</v>
       </c>
       <c r="F347" t="n">
-        <v>555000</v>
+        <v>608000</v>
       </c>
       <c r="G347" t="n">
         <v>1</v>
@@ -33284,7 +33284,7 @@
         <v>110</v>
       </c>
       <c r="F349" t="n">
-        <v>284000</v>
+        <v>299000</v>
       </c>
       <c r="G349" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>100</v>
       </c>
       <c r="F350" t="n">
-        <v>631000</v>
+        <v>644000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33366,7 +33366,7 @@
         <v>90</v>
       </c>
       <c r="F351" t="n">
-        <v>722000</v>
+        <v>673000</v>
       </c>
       <c r="G351" t="n">
         <v>1</v>
@@ -33459,7 +33459,7 @@
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>792000</v>
+        <v>790000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33541,7 +33541,7 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>659000</v>
+        <v>669000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>1000</v>
       </c>
       <c r="F6" t="n">
-        <v>965000</v>
+        <v>959000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>1010</v>
       </c>
       <c r="F7" t="n">
-        <v>615000</v>
+        <v>624000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>346000</v>
+        <v>349000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>666000</v>
+        <v>667000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33787,7 +33787,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>1118000</v>
+        <v>1120000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -33828,7 +33828,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>684000</v>
+        <v>675000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -34033,7 +34033,7 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>641000</v>
+        <v>658000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -34074,7 +34074,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>913000</v>
+        <v>921000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>140</v>
       </c>
       <c r="F18" t="n">
-        <v>949000</v>
+        <v>935000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>549000</v>
+        <v>545000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>938000</v>
+        <v>909000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34402,7 +34402,7 @@
         <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>611000</v>
+        <v>630000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>763000</v>
+        <v>764000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34648,7 +34648,7 @@
         <v>130</v>
       </c>
       <c r="F31" t="n">
-        <v>583000</v>
+        <v>561000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>596000</v>
+        <v>597000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>160</v>
       </c>
       <c r="F33" t="n">
-        <v>390000</v>
+        <v>424000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34853,7 +34853,7 @@
         <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>915000</v>
+        <v>906000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>40</v>
       </c>
       <c r="F37" t="n">
-        <v>728000</v>
+        <v>716000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>583000</v>
+        <v>589000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35058,7 +35058,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>698000</v>
+        <v>690000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -35099,7 +35099,7 @@
         <v>80</v>
       </c>
       <c r="F42" t="n">
-        <v>744000</v>
+        <v>758000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>1102000</v>
+        <v>1091000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>810000</v>
+        <v>850000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35345,7 +35345,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>1057000</v>
+        <v>1053000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>80</v>
       </c>
       <c r="F49" t="n">
-        <v>825000</v>
+        <v>794000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>776000</v>
+        <v>806000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35550,7 +35550,7 @@
         <v>110</v>
       </c>
       <c r="F53" t="n">
-        <v>629000</v>
+        <v>656000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>150</v>
       </c>
       <c r="F56" t="n">
-        <v>685000</v>
+        <v>657000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>665000</v>
+        <v>643000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>90</v>
       </c>
       <c r="F62" t="n">
-        <v>601000</v>
+        <v>628000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -36001,7 +36001,7 @@
         <v>130</v>
       </c>
       <c r="F64" t="n">
-        <v>899000</v>
+        <v>854000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -36124,7 +36124,7 @@
         <v>160</v>
       </c>
       <c r="F67" t="n">
-        <v>974000</v>
+        <v>1010000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>160</v>
       </c>
       <c r="F70" t="n">
-        <v>960000</v>
+        <v>934000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>150</v>
       </c>
       <c r="F71" t="n">
-        <v>668000</v>
+        <v>717000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>828000</v>
+        <v>851000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>60</v>
       </c>
       <c r="F80" t="n">
-        <v>701000</v>
+        <v>753000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>140</v>
       </c>
       <c r="F83" t="n">
-        <v>754000</v>
+        <v>718000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>90</v>
       </c>
       <c r="F85" t="n">
-        <v>595000</v>
+        <v>625000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>140</v>
       </c>
       <c r="F87" t="n">
-        <v>795000</v>
+        <v>758000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37026,7 +37026,7 @@
         <v>30</v>
       </c>
       <c r="F89" t="n">
-        <v>705000</v>
+        <v>726000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -37067,7 +37067,7 @@
         <v>110</v>
       </c>
       <c r="F90" t="n">
-        <v>471000</v>
+        <v>507000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>80</v>
       </c>
       <c r="F91" t="n">
-        <v>733000</v>
+        <v>759000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37354,7 +37354,7 @@
         <v>110</v>
       </c>
       <c r="F97" t="n">
-        <v>479000</v>
+        <v>477000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>942000</v>
+        <v>928000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>80</v>
       </c>
       <c r="F99" t="n">
-        <v>707000</v>
+        <v>692000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37559,7 +37559,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="n">
-        <v>972000</v>
+        <v>993000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>818000</v>
+        <v>836000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37641,7 +37641,7 @@
         <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>658000</v>
+        <v>657000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>918000</v>
+        <v>891000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37887,7 +37887,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>758000</v>
+        <v>740000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -38051,7 +38051,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>492000</v>
+        <v>513000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>150</v>
       </c>
       <c r="F115" t="n">
-        <v>749000</v>
+        <v>771000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38133,7 +38133,7 @@
         <v>120</v>
       </c>
       <c r="F116" t="n">
-        <v>676000</v>
+        <v>696000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>140</v>
       </c>
       <c r="F118" t="n">
-        <v>942000</v>
+        <v>948000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>1000</v>
       </c>
       <c r="F120" t="n">
-        <v>919000</v>
+        <v>1010000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38338,7 +38338,7 @@
         <v>1010</v>
       </c>
       <c r="F121" t="n">
-        <v>585000</v>
+        <v>594000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -38420,7 +38420,7 @@
         <v>60</v>
       </c>
       <c r="F123" t="n">
-        <v>894000</v>
+        <v>906000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -38461,7 +38461,7 @@
         <v>50</v>
       </c>
       <c r="F124" t="n">
-        <v>781000</v>
+        <v>748000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -38625,7 +38625,7 @@
         <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>642000</v>
+        <v>612000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -38707,7 +38707,7 @@
         <v>70</v>
       </c>
       <c r="F130" t="n">
-        <v>1052000</v>
+        <v>1042000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>90</v>
       </c>
       <c r="F131" t="n">
-        <v>815000</v>
+        <v>777000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -38789,7 +38789,7 @@
         <v>40</v>
       </c>
       <c r="F132" t="n">
-        <v>537000</v>
+        <v>513000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>100</v>
       </c>
       <c r="F133" t="n">
-        <v>639000</v>
+        <v>668000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38912,7 +38912,7 @@
         <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>399000</v>
+        <v>424000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -39240,7 +39240,7 @@
         <v>30</v>
       </c>
       <c r="F143" t="n">
-        <v>941000</v>
+        <v>937000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -39281,7 +39281,7 @@
         <v>80</v>
       </c>
       <c r="F144" t="n">
-        <v>851000</v>
+        <v>862000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>659000</v>
+        <v>658000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39486,7 +39486,7 @@
         <v>70</v>
       </c>
       <c r="F149" t="n">
-        <v>759000</v>
+        <v>784000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -39527,7 +39527,7 @@
         <v>60</v>
       </c>
       <c r="F150" t="n">
-        <v>650000</v>
+        <v>651000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -39661,7 +39661,7 @@
         <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>540000</v>
+        <v>569000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>1010</v>
       </c>
       <c r="F4" t="n">
-        <v>764000</v>
+        <v>758000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>930000</v>
+        <v>988000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>618000</v>
+        <v>598000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40194,7 +40194,7 @@
         <v>140</v>
       </c>
       <c r="F16" t="n">
-        <v>822000</v>
+        <v>806000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -40276,7 +40276,7 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>542000</v>
+        <v>526000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>1023000</v>
+        <v>1020000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>230000</v>
+        <v>253000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>910000</v>
+        <v>918000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -40645,7 +40645,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>637000</v>
+        <v>610000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>796000</v>
+        <v>788000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -40891,7 +40891,7 @@
         <v>1000</v>
       </c>
       <c r="F33" t="n">
-        <v>668000</v>
+        <v>672000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -40932,7 +40932,7 @@
         <v>120</v>
       </c>
       <c r="F34" t="n">
-        <v>768000</v>
+        <v>776000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -40973,7 +40973,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>872000</v>
+        <v>834000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -41055,7 +41055,7 @@
         <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>627000</v>
+        <v>656000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -41096,7 +41096,7 @@
         <v>80</v>
       </c>
       <c r="F38" t="n">
-        <v>518000</v>
+        <v>500000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -41219,7 +41219,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>378000</v>
+        <v>372000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -41424,7 +41424,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>733000</v>
+        <v>711000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -41506,7 +41506,7 @@
         <v>110</v>
       </c>
       <c r="F48" t="n">
-        <v>230000</v>
+        <v>246000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -41547,7 +41547,7 @@
         <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>395000</v>
+        <v>435000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -41629,7 +41629,7 @@
         <v>100</v>
       </c>
       <c r="F51" t="n">
-        <v>855000</v>
+        <v>851000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8345,7 +8345,7 @@
         <v>110</v>
       </c>
       <c r="F5" t="n">
-        <v>644000</v>
+        <v>617000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>760000</v>
+        <v>714000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>1000</v>
       </c>
       <c r="F8" t="n">
-        <v>704000</v>
+        <v>675000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>693000</v>
+        <v>677000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>408000</v>
+        <v>409000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>566000</v>
+        <v>552000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>374000</v>
+        <v>412000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>1010</v>
       </c>
       <c r="F16" t="n">
-        <v>902000</v>
+        <v>908000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>555000</v>
+        <v>549000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>1000</v>
       </c>
       <c r="F18" t="n">
-        <v>305000</v>
+        <v>312000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>571000</v>
+        <v>551000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>335000</v>
+        <v>339000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>733000</v>
+        <v>731000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>150</v>
       </c>
       <c r="F23" t="n">
-        <v>434000</v>
+        <v>427000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>766000</v>
+        <v>799000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9247,7 +9247,7 @@
         <v>160</v>
       </c>
       <c r="F27" t="n">
-        <v>686000</v>
+        <v>670000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>160</v>
       </c>
       <c r="F28" t="n">
-        <v>840000</v>
+        <v>851000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>522000</v>
+        <v>512000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>411000</v>
+        <v>395000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="n">
-        <v>913000</v>
+        <v>892000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -9739,7 +9739,7 @@
         <v>120</v>
       </c>
       <c r="F39" t="n">
-        <v>544000</v>
+        <v>552000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>623000</v>
+        <v>619000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>70</v>
       </c>
       <c r="F42" t="n">
-        <v>721000</v>
+        <v>735000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9944,7 +9944,7 @@
         <v>110</v>
       </c>
       <c r="F44" t="n">
-        <v>910000</v>
+        <v>933000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>130</v>
       </c>
       <c r="F48" t="n">
-        <v>620000</v>
+        <v>629000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>140</v>
       </c>
       <c r="F49" t="n">
-        <v>270000</v>
+        <v>265000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>60</v>
       </c>
       <c r="F52" t="n">
-        <v>501000</v>
+        <v>513000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>60</v>
       </c>
       <c r="F54" t="n">
-        <v>733000</v>
+        <v>726000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10395,7 +10395,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>581000</v>
+        <v>540000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -10600,7 +10600,7 @@
         <v>1000</v>
       </c>
       <c r="F60" t="n">
-        <v>529000</v>
+        <v>494000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>481000</v>
+        <v>462000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>465000</v>
+        <v>441000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>643000</v>
+        <v>640000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>60</v>
       </c>
       <c r="F65" t="n">
-        <v>459000</v>
+        <v>437000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>954000</v>
+        <v>960000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>836000</v>
+        <v>824000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
         <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>357000</v>
+        <v>372000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>508000</v>
+        <v>513000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>517000</v>
+        <v>527000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -11420,7 +11420,7 @@
         <v>150</v>
       </c>
       <c r="F80" t="n">
-        <v>708000</v>
+        <v>683000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -11707,7 +11707,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>686000</v>
+        <v>674000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11789,7 +11789,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>743000</v>
+        <v>735000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>750000</v>
+        <v>811000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>1010</v>
       </c>
       <c r="F91" t="n">
-        <v>647000</v>
+        <v>636000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>427000</v>
+        <v>411000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="n">
-        <v>458000</v>
+        <v>424000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>120</v>
       </c>
       <c r="F102" t="n">
-        <v>447000</v>
+        <v>443000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>70</v>
       </c>
       <c r="F103" t="n">
-        <v>601000</v>
+        <v>578000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>645000</v>
+        <v>651000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>160</v>
       </c>
       <c r="F105" t="n">
-        <v>330000</v>
+        <v>326000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>450000</v>
+        <v>455000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>795000</v>
+        <v>763000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12568,7 +12568,7 @@
         <v>130</v>
       </c>
       <c r="F108" t="n">
-        <v>443000</v>
+        <v>457000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         <v>30</v>
       </c>
       <c r="F110" t="n">
-        <v>713000</v>
+        <v>754000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>1010</v>
       </c>
       <c r="F112" t="n">
-        <v>663000</v>
+        <v>641000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>150</v>
       </c>
       <c r="F117" t="n">
-        <v>561000</v>
+        <v>559000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>771000</v>
+        <v>759000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>70</v>
       </c>
       <c r="F122" t="n">
-        <v>760000</v>
+        <v>763000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>80</v>
       </c>
       <c r="F124" t="n">
-        <v>924000</v>
+        <v>923000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         <v>140</v>
       </c>
       <c r="F125" t="n">
-        <v>508000</v>
+        <v>484000</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>612000</v>
+        <v>577000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>552000</v>
+        <v>544000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>110</v>
       </c>
       <c r="F132" t="n">
-        <v>508000</v>
+        <v>523000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -13634,7 +13634,7 @@
         <v>10</v>
       </c>
       <c r="F134" t="n">
-        <v>506000</v>
+        <v>495000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>50</v>
       </c>
       <c r="F136" t="n">
-        <v>324000</v>
+        <v>336000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>160</v>
       </c>
       <c r="F137" t="n">
-        <v>392000</v>
+        <v>385000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>110</v>
       </c>
       <c r="F138" t="n">
-        <v>546000</v>
+        <v>527000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>868000</v>
+        <v>832000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>20</v>
       </c>
       <c r="F141" t="n">
-        <v>605000</v>
+        <v>592000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>90</v>
       </c>
       <c r="F142" t="n">
-        <v>555000</v>
+        <v>547000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>150</v>
       </c>
       <c r="F143" t="n">
-        <v>666000</v>
+        <v>638000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>140</v>
       </c>
       <c r="F145" t="n">
-        <v>658000</v>
+        <v>635000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>100</v>
       </c>
       <c r="F146" t="n">
-        <v>398000</v>
+        <v>423000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>80</v>
       </c>
       <c r="F147" t="n">
-        <v>489000</v>
+        <v>487000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>150</v>
       </c>
       <c r="F152" t="n">
-        <v>851000</v>
+        <v>856000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>680000</v>
+        <v>648000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>60</v>
       </c>
       <c r="F156" t="n">
-        <v>553000</v>
+        <v>549000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>90</v>
       </c>
       <c r="F157" t="n">
-        <v>496000</v>
+        <v>467000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>50</v>
       </c>
       <c r="F158" t="n">
-        <v>620000</v>
+        <v>635000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>10</v>
       </c>
       <c r="F163" t="n">
-        <v>556000</v>
+        <v>534000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -14946,7 +14946,7 @@
         <v>120</v>
       </c>
       <c r="F166" t="n">
-        <v>534000</v>
+        <v>547000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>160</v>
       </c>
       <c r="F167" t="n">
-        <v>835000</v>
+        <v>800000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>70</v>
       </c>
       <c r="F172" t="n">
-        <v>530000</v>
+        <v>552000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>10</v>
       </c>
       <c r="F176" t="n">
-        <v>660000</v>
+        <v>643000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15479,7 +15479,7 @@
         <v>1000</v>
       </c>
       <c r="F179" t="n">
-        <v>928000</v>
+        <v>915000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>110</v>
       </c>
       <c r="F180" t="n">
-        <v>253000</v>
+        <v>269000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>130</v>
       </c>
       <c r="F181" t="n">
-        <v>419000</v>
+        <v>434000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15602,7 +15602,7 @@
         <v>70</v>
       </c>
       <c r="F182" t="n">
-        <v>581000</v>
+        <v>583000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         <v>140</v>
       </c>
       <c r="F183" t="n">
-        <v>466000</v>
+        <v>455000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>70</v>
       </c>
       <c r="F185" t="n">
-        <v>627000</v>
+        <v>616000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>100</v>
       </c>
       <c r="F186" t="n">
-        <v>646000</v>
+        <v>656000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15848,7 +15848,7 @@
         <v>100</v>
       </c>
       <c r="F188" t="n">
-        <v>897000</v>
+        <v>867000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -16012,7 +16012,7 @@
         <v>60</v>
       </c>
       <c r="F192" t="n">
-        <v>335000</v>
+        <v>312000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16176,7 +16176,7 @@
         <v>1000</v>
       </c>
       <c r="F196" t="n">
-        <v>667000</v>
+        <v>671000</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
         <v>50</v>
       </c>
       <c r="F197" t="n">
-        <v>586000</v>
+        <v>610000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>40</v>
       </c>
       <c r="F198" t="n">
-        <v>270000</v>
+        <v>265000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -16299,7 +16299,7 @@
         <v>40</v>
       </c>
       <c r="F199" t="n">
-        <v>676000</v>
+        <v>650000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -16381,7 +16381,7 @@
         <v>160</v>
       </c>
       <c r="F201" t="n">
-        <v>418000</v>
+        <v>420000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>50</v>
       </c>
       <c r="F203" t="n">
-        <v>698000</v>
+        <v>681000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>50</v>
       </c>
       <c r="F204" t="n">
-        <v>475000</v>
+        <v>502000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
         <v>1000</v>
       </c>
       <c r="F206" t="n">
-        <v>644000</v>
+        <v>632000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>90</v>
       </c>
       <c r="F207" t="n">
-        <v>794000</v>
+        <v>787000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -16668,7 +16668,7 @@
         <v>50</v>
       </c>
       <c r="F208" t="n">
-        <v>752000</v>
+        <v>761000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>60</v>
       </c>
       <c r="F213" t="n">
-        <v>721000</v>
+        <v>720000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -16996,7 +16996,7 @@
         <v>90</v>
       </c>
       <c r="F216" t="n">
-        <v>664000</v>
+        <v>603000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>160</v>
       </c>
       <c r="F219" t="n">
-        <v>607000</v>
+        <v>613000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>120</v>
       </c>
       <c r="F220" t="n">
-        <v>759000</v>
+        <v>751000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>754000</v>
+        <v>732000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17242,7 +17242,7 @@
         <v>130</v>
       </c>
       <c r="F222" t="n">
-        <v>590000</v>
+        <v>586000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         <v>150</v>
       </c>
       <c r="F227" t="n">
-        <v>503000</v>
+        <v>495000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -17488,7 +17488,7 @@
         <v>70</v>
       </c>
       <c r="F228" t="n">
-        <v>758000</v>
+        <v>755000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>130</v>
       </c>
       <c r="F229" t="n">
-        <v>631000</v>
+        <v>671000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -17570,7 +17570,7 @@
         <v>1010</v>
       </c>
       <c r="F230" t="n">
-        <v>452000</v>
+        <v>461000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>529000</v>
+        <v>515000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>120</v>
       </c>
       <c r="F236" t="n">
-        <v>507000</v>
+        <v>491000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>130</v>
       </c>
       <c r="F237" t="n">
-        <v>433000</v>
+        <v>436000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -17939,7 +17939,7 @@
         <v>90</v>
       </c>
       <c r="F239" t="n">
-        <v>611000</v>
+        <v>599000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         <v>1000</v>
       </c>
       <c r="F240" t="n">
-        <v>788000</v>
+        <v>783000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>633000</v>
+        <v>644000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>80</v>
       </c>
       <c r="F247" t="n">
-        <v>649000</v>
+        <v>611000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>110</v>
       </c>
       <c r="F248" t="n">
-        <v>431000</v>
+        <v>447000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>30</v>
       </c>
       <c r="F249" t="n">
-        <v>571000</v>
+        <v>582000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>1010</v>
       </c>
       <c r="F250" t="n">
-        <v>937000</v>
+        <v>963000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>160</v>
       </c>
       <c r="F251" t="n">
-        <v>626000</v>
+        <v>604000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         <v>130</v>
       </c>
       <c r="F252" t="n">
-        <v>823000</v>
+        <v>789000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -18513,7 +18513,7 @@
         <v>140</v>
       </c>
       <c r="F253" t="n">
-        <v>705000</v>
+        <v>697000</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>20</v>
       </c>
       <c r="F254" t="n">
-        <v>745000</v>
+        <v>727000</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
         <v>30</v>
       </c>
       <c r="F255" t="n">
-        <v>706000</v>
+        <v>728000</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -18636,7 +18636,7 @@
         <v>130</v>
       </c>
       <c r="F256" t="n">
-        <v>777000</v>
+        <v>770000</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>90</v>
       </c>
       <c r="F257" t="n">
-        <v>493000</v>
+        <v>503000</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>60</v>
       </c>
       <c r="F258" t="n">
-        <v>779000</v>
+        <v>772000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -18759,7 +18759,7 @@
         <v>10</v>
       </c>
       <c r="F259" t="n">
-        <v>690000</v>
+        <v>654000</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -18841,7 +18841,7 @@
         <v>150</v>
       </c>
       <c r="F261" t="n">
-        <v>487000</v>
+        <v>476000</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -18964,7 +18964,7 @@
         <v>20</v>
       </c>
       <c r="F264" t="n">
-        <v>888000</v>
+        <v>908000</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -19098,7 +19098,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>511000</v>
+        <v>505000</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -19139,7 +19139,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>708000</v>
+        <v>682000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19221,7 +19221,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>472000</v>
+        <v>448000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -19344,7 +19344,7 @@
         <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>566000</v>
+        <v>578000</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -19385,7 +19385,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>335000</v>
+        <v>370000</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>506000</v>
+        <v>505000</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -19467,7 +19467,7 @@
         <v>1010</v>
       </c>
       <c r="F12" t="n">
-        <v>361000</v>
+        <v>363000</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -19508,7 +19508,7 @@
         <v>120</v>
       </c>
       <c r="F13" t="n">
-        <v>282000</v>
+        <v>240000</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -19549,7 +19549,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>908000</v>
+        <v>902000</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>370000</v>
+        <v>408000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19795,7 +19795,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>230000</v>
+        <v>249000</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>465000</v>
+        <v>488000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>741000</v>
+        <v>732000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>140</v>
       </c>
       <c r="F26" t="n">
-        <v>644000</v>
+        <v>654000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>1010</v>
       </c>
       <c r="F28" t="n">
-        <v>559000</v>
+        <v>569000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>130</v>
       </c>
       <c r="F31" t="n">
-        <v>372000</v>
+        <v>427000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>573000</v>
+        <v>578000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>482000</v>
+        <v>489000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20451,7 +20451,7 @@
         <v>1010</v>
       </c>
       <c r="F36" t="n">
-        <v>506000</v>
+        <v>516000</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -20492,7 +20492,7 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>570000</v>
+        <v>600000</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>160</v>
       </c>
       <c r="F40" t="n">
-        <v>614000</v>
+        <v>611000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>554000</v>
+        <v>543000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>617000</v>
+        <v>640000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>80</v>
       </c>
       <c r="F46" t="n">
-        <v>617000</v>
+        <v>597000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>627000</v>
+        <v>636000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>120</v>
       </c>
       <c r="F48" t="n">
-        <v>241000</v>
+        <v>276000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>70</v>
       </c>
       <c r="F50" t="n">
-        <v>467000</v>
+        <v>456000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>150</v>
       </c>
       <c r="F52" t="n">
-        <v>524000</v>
+        <v>537000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>1010</v>
       </c>
       <c r="F54" t="n">
-        <v>644000</v>
+        <v>682000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>596000</v>
+        <v>593000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>631000</v>
+        <v>632000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>439000</v>
+        <v>454000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21435,7 +21435,7 @@
         <v>140</v>
       </c>
       <c r="F60" t="n">
-        <v>356000</v>
+        <v>349000</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -21517,7 +21517,7 @@
         <v>160</v>
       </c>
       <c r="F62" t="n">
-        <v>691000</v>
+        <v>659000</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>695000</v>
+        <v>701000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21640,7 +21640,7 @@
         <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>622000</v>
+        <v>583000</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>583000</v>
+        <v>599000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>160</v>
       </c>
       <c r="F70" t="n">
-        <v>325000</v>
+        <v>380000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>140</v>
       </c>
       <c r="F71" t="n">
-        <v>491000</v>
+        <v>522000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21927,7 +21927,7 @@
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>420000</v>
+        <v>424000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -21968,7 +21968,7 @@
         <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>862000</v>
+        <v>826000</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -22050,7 +22050,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>325000</v>
+        <v>372000</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>455000</v>
+        <v>461000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>619000</v>
+        <v>588000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>499000</v>
+        <v>489000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>150</v>
       </c>
       <c r="F83" t="n">
-        <v>429000</v>
+        <v>437000</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>110</v>
       </c>
       <c r="F84" t="n">
-        <v>488000</v>
+        <v>485000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="F91" t="n">
-        <v>673000</v>
+        <v>688000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22952,7 +22952,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="n">
-        <v>671000</v>
+        <v>668000</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -23034,7 +23034,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>622000</v>
+        <v>603000</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -23075,7 +23075,7 @@
         <v>140</v>
       </c>
       <c r="F100" t="n">
-        <v>648000</v>
+        <v>663000</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>90</v>
       </c>
       <c r="F101" t="n">
-        <v>650000</v>
+        <v>664000</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
         <v>110</v>
       </c>
       <c r="F105" t="n">
-        <v>630000</v>
+        <v>639000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23321,7 +23321,7 @@
         <v>80</v>
       </c>
       <c r="F106" t="n">
-        <v>736000</v>
+        <v>701000</v>
       </c>
       <c r="G106" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>150</v>
       </c>
       <c r="F108" t="n">
-        <v>695000</v>
+        <v>725000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23485,7 +23485,7 @@
         <v>120</v>
       </c>
       <c r="F110" t="n">
-        <v>444000</v>
+        <v>417000</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>1010</v>
       </c>
       <c r="F111" t="n">
-        <v>838000</v>
+        <v>835000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23649,7 +23649,7 @@
         <v>150</v>
       </c>
       <c r="F114" t="n">
-        <v>370000</v>
+        <v>392000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>456000</v>
+        <v>463000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>1000</v>
       </c>
       <c r="F117" t="n">
-        <v>398000</v>
+        <v>413000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23813,7 +23813,7 @@
         <v>80</v>
       </c>
       <c r="F118" t="n">
-        <v>714000</v>
+        <v>700000</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>130</v>
       </c>
       <c r="F119" t="n">
-        <v>929000</v>
+        <v>987000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23895,7 +23895,7 @@
         <v>1010</v>
       </c>
       <c r="F120" t="n">
-        <v>335000</v>
+        <v>339000</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -24059,7 +24059,7 @@
         <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>489000</v>
+        <v>503000</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -24182,7 +24182,7 @@
         <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>325000</v>
+        <v>326000</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -24223,7 +24223,7 @@
         <v>30</v>
       </c>
       <c r="F128" t="n">
-        <v>663000</v>
+        <v>685000</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
@@ -24346,7 +24346,7 @@
         <v>70</v>
       </c>
       <c r="F131" t="n">
-        <v>474000</v>
+        <v>479000</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -24428,7 +24428,7 @@
         <v>70</v>
       </c>
       <c r="F133" t="n">
-        <v>583000</v>
+        <v>596000</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -24510,7 +24510,7 @@
         <v>130</v>
       </c>
       <c r="F135" t="n">
-        <v>491000</v>
+        <v>505000</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -24592,7 +24592,7 @@
         <v>130</v>
       </c>
       <c r="F137" t="n">
-        <v>1040000</v>
+        <v>1055000</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -24674,7 +24674,7 @@
         <v>20</v>
       </c>
       <c r="F139" t="n">
-        <v>480000</v>
+        <v>490000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24838,7 +24838,7 @@
         <v>110</v>
       </c>
       <c r="F143" t="n">
-        <v>965000</v>
+        <v>946000</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -24879,7 +24879,7 @@
         <v>120</v>
       </c>
       <c r="F144" t="n">
-        <v>471000</v>
+        <v>460000</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -24920,7 +24920,7 @@
         <v>40</v>
       </c>
       <c r="F145" t="n">
-        <v>230000</v>
+        <v>233000</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -24961,7 +24961,7 @@
         <v>1000</v>
       </c>
       <c r="F146" t="n">
-        <v>563000</v>
+        <v>586000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25002,7 +25002,7 @@
         <v>140</v>
       </c>
       <c r="F147" t="n">
-        <v>540000</v>
+        <v>554000</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -25043,7 +25043,7 @@
         <v>90</v>
       </c>
       <c r="F148" t="n">
-        <v>363000</v>
+        <v>353000</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -25125,7 +25125,7 @@
         <v>140</v>
       </c>
       <c r="F150" t="n">
-        <v>453000</v>
+        <v>470000</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -25207,7 +25207,7 @@
         <v>50</v>
       </c>
       <c r="F152" t="n">
-        <v>436000</v>
+        <v>424000</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -25248,7 +25248,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>549000</v>
+        <v>547000</v>
       </c>
       <c r="G153" t="n">
         <v>1</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F154" t="n">
-        <v>371000</v>
+        <v>381000</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>623000</v>
+        <v>576000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25412,7 +25412,7 @@
         <v>150</v>
       </c>
       <c r="F157" t="n">
-        <v>842000</v>
+        <v>860000</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -25453,7 +25453,7 @@
         <v>30</v>
       </c>
       <c r="F158" t="n">
-        <v>588000</v>
+        <v>585000</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>140</v>
       </c>
       <c r="F160" t="n">
-        <v>492000</v>
+        <v>512000</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
@@ -25617,7 +25617,7 @@
         <v>1000</v>
       </c>
       <c r="F162" t="n">
-        <v>455000</v>
+        <v>453000</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
@@ -25822,7 +25822,7 @@
         <v>130</v>
       </c>
       <c r="F167" t="n">
-        <v>449000</v>
+        <v>462000</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -25863,7 +25863,7 @@
         <v>120</v>
       </c>
       <c r="F168" t="n">
-        <v>580000</v>
+        <v>560000</v>
       </c>
       <c r="G168" t="n">
         <v>1</v>
@@ -25904,7 +25904,7 @@
         <v>90</v>
       </c>
       <c r="F169" t="n">
-        <v>723000</v>
+        <v>673000</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>50</v>
       </c>
       <c r="F170" t="n">
-        <v>595000</v>
+        <v>568000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>100</v>
       </c>
       <c r="F171" t="n">
-        <v>588000</v>
+        <v>590000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26027,7 +26027,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>484000</v>
+        <v>517000</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
@@ -26109,7 +26109,7 @@
         <v>120</v>
       </c>
       <c r="F174" t="n">
-        <v>448000</v>
+        <v>472000</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
@@ -26191,7 +26191,7 @@
         <v>80</v>
       </c>
       <c r="F176" t="n">
-        <v>561000</v>
+        <v>570000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>160</v>
       </c>
       <c r="F179" t="n">
-        <v>589000</v>
+        <v>627000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>20</v>
       </c>
       <c r="F181" t="n">
-        <v>765000</v>
+        <v>749000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>1000</v>
       </c>
       <c r="F182" t="n">
-        <v>572000</v>
+        <v>576000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>1000</v>
       </c>
       <c r="F183" t="n">
-        <v>484000</v>
+        <v>466000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>40</v>
       </c>
       <c r="F184" t="n">
-        <v>679000</v>
+        <v>664000</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>120</v>
       </c>
       <c r="F190" t="n">
-        <v>454000</v>
+        <v>461000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26806,7 +26806,7 @@
         <v>80</v>
       </c>
       <c r="F191" t="n">
-        <v>863000</v>
+        <v>807000</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>70</v>
       </c>
       <c r="F196" t="n">
-        <v>706000</v>
+        <v>723000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>130</v>
       </c>
       <c r="F199" t="n">
-        <v>963000</v>
+        <v>950000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27175,7 +27175,7 @@
         <v>110</v>
       </c>
       <c r="F200" t="n">
-        <v>448000</v>
+        <v>473000</v>
       </c>
       <c r="G200" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>40</v>
       </c>
       <c r="F209" t="n">
-        <v>551000</v>
+        <v>619000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27585,7 +27585,7 @@
         <v>160</v>
       </c>
       <c r="F210" t="n">
-        <v>532000</v>
+        <v>543000</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>30</v>
       </c>
       <c r="F211" t="n">
-        <v>564000</v>
+        <v>569000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>30</v>
       </c>
       <c r="F213" t="n">
-        <v>610000</v>
+        <v>627000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>20</v>
       </c>
       <c r="F214" t="n">
-        <v>463000</v>
+        <v>434000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>734000</v>
+        <v>738000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -27995,7 +27995,7 @@
         <v>40</v>
       </c>
       <c r="F220" t="n">
-        <v>740000</v>
+        <v>781000</v>
       </c>
       <c r="G220" t="n">
         <v>1</v>
@@ -28118,7 +28118,7 @@
         <v>40</v>
       </c>
       <c r="F223" t="n">
-        <v>645000</v>
+        <v>628000</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
@@ -28200,7 +28200,7 @@
         <v>70</v>
       </c>
       <c r="F225" t="n">
-        <v>696000</v>
+        <v>648000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>1000</v>
       </c>
       <c r="F228" t="n">
-        <v>850000</v>
+        <v>836000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>80</v>
       </c>
       <c r="F231" t="n">
-        <v>710000</v>
+        <v>716000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28528,7 +28528,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="n">
-        <v>646000</v>
+        <v>662000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28610,7 +28610,7 @@
         <v>150</v>
       </c>
       <c r="F235" t="n">
-        <v>554000</v>
+        <v>557000</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
@@ -28651,7 +28651,7 @@
         <v>10</v>
       </c>
       <c r="F236" t="n">
-        <v>416000</v>
+        <v>383000</v>
       </c>
       <c r="G236" t="n">
         <v>1</v>
@@ -28774,7 +28774,7 @@
         <v>140</v>
       </c>
       <c r="F239" t="n">
-        <v>560000</v>
+        <v>558000</v>
       </c>
       <c r="G239" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>70</v>
       </c>
       <c r="F241" t="n">
-        <v>630000</v>
+        <v>650000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -29061,7 +29061,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>584000</v>
+        <v>618000</v>
       </c>
       <c r="G246" t="n">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>160</v>
       </c>
       <c r="F248" t="n">
-        <v>617000</v>
+        <v>593000</v>
       </c>
       <c r="G248" t="n">
         <v>1</v>
@@ -29225,7 +29225,7 @@
         <v>50</v>
       </c>
       <c r="F250" t="n">
-        <v>568000</v>
+        <v>553000</v>
       </c>
       <c r="G250" t="n">
         <v>1</v>
@@ -29266,7 +29266,7 @@
         <v>1000</v>
       </c>
       <c r="F251" t="n">
-        <v>665000</v>
+        <v>625000</v>
       </c>
       <c r="G251" t="n">
         <v>1</v>
@@ -29307,7 +29307,7 @@
         <v>90</v>
       </c>
       <c r="F252" t="n">
-        <v>645000</v>
+        <v>651000</v>
       </c>
       <c r="G252" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>130</v>
       </c>
       <c r="F254" t="n">
-        <v>737000</v>
+        <v>687000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>90</v>
       </c>
       <c r="F255" t="n">
-        <v>865000</v>
+        <v>868000</v>
       </c>
       <c r="G255" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>70</v>
       </c>
       <c r="F258" t="n">
-        <v>381000</v>
+        <v>391000</v>
       </c>
       <c r="G258" t="n">
         <v>1</v>
@@ -29676,7 +29676,7 @@
         <v>120</v>
       </c>
       <c r="F261" t="n">
-        <v>644000</v>
+        <v>660000</v>
       </c>
       <c r="G261" t="n">
         <v>1</v>
@@ -29717,7 +29717,7 @@
         <v>10</v>
       </c>
       <c r="F262" t="n">
-        <v>585000</v>
+        <v>549000</v>
       </c>
       <c r="G262" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>10</v>
       </c>
       <c r="F264" t="n">
-        <v>984000</v>
+        <v>1057000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29840,7 +29840,7 @@
         <v>20</v>
       </c>
       <c r="F265" t="n">
-        <v>719000</v>
+        <v>706000</v>
       </c>
       <c r="G265" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>1000</v>
       </c>
       <c r="F266" t="n">
-        <v>343000</v>
+        <v>362000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>110</v>
       </c>
       <c r="F271" t="n">
-        <v>782000</v>
+        <v>816000</v>
       </c>
       <c r="G271" t="n">
         <v>1</v>
@@ -30291,7 +30291,7 @@
         <v>1000</v>
       </c>
       <c r="F276" t="n">
-        <v>345000</v>
+        <v>335000</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
@@ -30373,7 +30373,7 @@
         <v>120</v>
       </c>
       <c r="F278" t="n">
-        <v>752000</v>
+        <v>733000</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -30537,7 +30537,7 @@
         <v>140</v>
       </c>
       <c r="F282" t="n">
-        <v>729000</v>
+        <v>709000</v>
       </c>
       <c r="G282" t="n">
         <v>1</v>
@@ -30619,7 +30619,7 @@
         <v>60</v>
       </c>
       <c r="F284" t="n">
-        <v>266000</v>
+        <v>279000</v>
       </c>
       <c r="G284" t="n">
         <v>1</v>
@@ -30742,7 +30742,7 @@
         <v>40</v>
       </c>
       <c r="F287" t="n">
-        <v>643000</v>
+        <v>653000</v>
       </c>
       <c r="G287" t="n">
         <v>1</v>
@@ -30783,7 +30783,7 @@
         <v>150</v>
       </c>
       <c r="F288" t="n">
-        <v>503000</v>
+        <v>475000</v>
       </c>
       <c r="G288" t="n">
         <v>1</v>
@@ -30824,7 +30824,7 @@
         <v>130</v>
       </c>
       <c r="F289" t="n">
-        <v>541000</v>
+        <v>533000</v>
       </c>
       <c r="G289" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>50</v>
       </c>
       <c r="F290" t="n">
-        <v>750000</v>
+        <v>789000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>90</v>
       </c>
       <c r="F291" t="n">
-        <v>518000</v>
+        <v>526000</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -30947,7 +30947,7 @@
         <v>100</v>
       </c>
       <c r="F292" t="n">
-        <v>1201000</v>
+        <v>1126000</v>
       </c>
       <c r="G292" t="n">
         <v>1</v>
@@ -30988,7 +30988,7 @@
         <v>100</v>
       </c>
       <c r="F293" t="n">
-        <v>813000</v>
+        <v>801000</v>
       </c>
       <c r="G293" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>30</v>
       </c>
       <c r="F296" t="n">
-        <v>834000</v>
+        <v>826000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31234,7 +31234,7 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>708000</v>
+        <v>710000</v>
       </c>
       <c r="G299" t="n">
         <v>1</v>
@@ -31316,7 +31316,7 @@
         <v>100</v>
       </c>
       <c r="F301" t="n">
-        <v>553000</v>
+        <v>547000</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -31357,7 +31357,7 @@
         <v>90</v>
       </c>
       <c r="F302" t="n">
-        <v>998000</v>
+        <v>975000</v>
       </c>
       <c r="G302" t="n">
         <v>1</v>
@@ -31521,7 +31521,7 @@
         <v>1010</v>
       </c>
       <c r="F306" t="n">
-        <v>653000</v>
+        <v>634000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31644,7 +31644,7 @@
         <v>60</v>
       </c>
       <c r="F309" t="n">
-        <v>505000</v>
+        <v>497000</v>
       </c>
       <c r="G309" t="n">
         <v>1</v>
@@ -31685,7 +31685,7 @@
         <v>130</v>
       </c>
       <c r="F310" t="n">
-        <v>391000</v>
+        <v>375000</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>10</v>
       </c>
       <c r="F311" t="n">
-        <v>450000</v>
+        <v>455000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31767,7 +31767,7 @@
         <v>10</v>
       </c>
       <c r="F312" t="n">
-        <v>675000</v>
+        <v>665000</v>
       </c>
       <c r="G312" t="n">
         <v>1</v>
@@ -31808,7 +31808,7 @@
         <v>90</v>
       </c>
       <c r="F313" t="n">
-        <v>632000</v>
+        <v>652000</v>
       </c>
       <c r="G313" t="n">
         <v>1</v>
@@ -31849,7 +31849,7 @@
         <v>1010</v>
       </c>
       <c r="F314" t="n">
-        <v>637000</v>
+        <v>649000</v>
       </c>
       <c r="G314" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>60</v>
       </c>
       <c r="F315" t="n">
-        <v>727000</v>
+        <v>740000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>100</v>
       </c>
       <c r="F317" t="n">
-        <v>629000</v>
+        <v>628000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32054,7 +32054,7 @@
         <v>50</v>
       </c>
       <c r="F319" t="n">
-        <v>232000</v>
+        <v>265000</v>
       </c>
       <c r="G319" t="n">
         <v>1</v>
@@ -32136,7 +32136,7 @@
         <v>110</v>
       </c>
       <c r="F321" t="n">
-        <v>429000</v>
+        <v>422000</v>
       </c>
       <c r="G321" t="n">
         <v>1</v>
@@ -32177,7 +32177,7 @@
         <v>60</v>
       </c>
       <c r="F322" t="n">
-        <v>600000</v>
+        <v>580000</v>
       </c>
       <c r="G322" t="n">
         <v>1</v>
@@ -32300,7 +32300,7 @@
         <v>1000</v>
       </c>
       <c r="F325" t="n">
-        <v>410000</v>
+        <v>424000</v>
       </c>
       <c r="G325" t="n">
         <v>1</v>
@@ -32382,7 +32382,7 @@
         <v>160</v>
       </c>
       <c r="F327" t="n">
-        <v>961000</v>
+        <v>968000</v>
       </c>
       <c r="G327" t="n">
         <v>1</v>
@@ -32464,7 +32464,7 @@
         <v>150</v>
       </c>
       <c r="F329" t="n">
-        <v>652000</v>
+        <v>647000</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
@@ -32546,7 +32546,7 @@
         <v>80</v>
       </c>
       <c r="F331" t="n">
-        <v>647000</v>
+        <v>633000</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -32587,7 +32587,7 @@
         <v>140</v>
       </c>
       <c r="F332" t="n">
-        <v>479000</v>
+        <v>493000</v>
       </c>
       <c r="G332" t="n">
         <v>1</v>
@@ -32669,7 +32669,7 @@
         <v>40</v>
       </c>
       <c r="F334" t="n">
-        <v>312000</v>
+        <v>317000</v>
       </c>
       <c r="G334" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>140</v>
       </c>
       <c r="F335" t="n">
-        <v>588000</v>
+        <v>568000</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -32792,7 +32792,7 @@
         <v>110</v>
       </c>
       <c r="F337" t="n">
-        <v>409000</v>
+        <v>390000</v>
       </c>
       <c r="G337" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>150</v>
       </c>
       <c r="F339" t="n">
-        <v>806000</v>
+        <v>808000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32915,7 +32915,7 @@
         <v>150</v>
       </c>
       <c r="F340" t="n">
-        <v>435000</v>
+        <v>428000</v>
       </c>
       <c r="G340" t="n">
         <v>1</v>
@@ -33038,7 +33038,7 @@
         <v>130</v>
       </c>
       <c r="F343" t="n">
-        <v>889000</v>
+        <v>837000</v>
       </c>
       <c r="G343" t="n">
         <v>1</v>
@@ -33079,7 +33079,7 @@
         <v>70</v>
       </c>
       <c r="F344" t="n">
-        <v>455000</v>
+        <v>415000</v>
       </c>
       <c r="G344" t="n">
         <v>1</v>
@@ -33161,7 +33161,7 @@
         <v>50</v>
       </c>
       <c r="F346" t="n">
-        <v>696000</v>
+        <v>672000</v>
       </c>
       <c r="G346" t="n">
         <v>1</v>
@@ -33202,7 +33202,7 @@
         <v>150</v>
       </c>
       <c r="F347" t="n">
-        <v>608000</v>
+        <v>651000</v>
       </c>
       <c r="G347" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>100</v>
       </c>
       <c r="F350" t="n">
-        <v>644000</v>
+        <v>660000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33366,7 +33366,7 @@
         <v>90</v>
       </c>
       <c r="F351" t="n">
-        <v>673000</v>
+        <v>649000</v>
       </c>
       <c r="G351" t="n">
         <v>1</v>
@@ -33459,7 +33459,7 @@
         <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>790000</v>
+        <v>821000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -33500,7 +33500,7 @@
         <v>1000</v>
       </c>
       <c r="F3" t="n">
-        <v>535000</v>
+        <v>520000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33541,7 +33541,7 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>669000</v>
+        <v>694000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>1000</v>
       </c>
       <c r="F6" t="n">
-        <v>959000</v>
+        <v>942000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>1010</v>
       </c>
       <c r="F7" t="n">
-        <v>624000</v>
+        <v>615000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>349000</v>
+        <v>353000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>667000</v>
+        <v>703000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33787,7 +33787,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>1120000</v>
+        <v>1112000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -33828,7 +33828,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>675000</v>
+        <v>666000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>438000</v>
+        <v>458000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -34033,7 +34033,7 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>658000</v>
+        <v>694000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -34074,7 +34074,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>921000</v>
+        <v>880000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>545000</v>
+        <v>577000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>909000</v>
+        <v>890000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34402,7 +34402,7 @@
         <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>630000</v>
+        <v>665000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>764000</v>
+        <v>768000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>597000</v>
+        <v>605000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>160</v>
       </c>
       <c r="F33" t="n">
-        <v>424000</v>
+        <v>437000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34853,7 +34853,7 @@
         <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>906000</v>
+        <v>905000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>40</v>
       </c>
       <c r="F37" t="n">
-        <v>716000</v>
+        <v>698000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>589000</v>
+        <v>580000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35058,7 +35058,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>690000</v>
+        <v>679000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>1091000</v>
+        <v>1083000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>850000</v>
+        <v>859000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35345,7 +35345,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>1053000</v>
+        <v>1049000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>80</v>
       </c>
       <c r="F49" t="n">
-        <v>794000</v>
+        <v>748000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>806000</v>
+        <v>835000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35550,7 +35550,7 @@
         <v>110</v>
       </c>
       <c r="F53" t="n">
-        <v>656000</v>
+        <v>672000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -35632,7 +35632,7 @@
         <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>978000</v>
+        <v>974000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>150</v>
       </c>
       <c r="F56" t="n">
-        <v>657000</v>
+        <v>597000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>643000</v>
+        <v>630000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>90</v>
       </c>
       <c r="F62" t="n">
-        <v>628000</v>
+        <v>643000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -36124,7 +36124,7 @@
         <v>160</v>
       </c>
       <c r="F67" t="n">
-        <v>1010000</v>
+        <v>1061000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -36247,7 +36247,7 @@
         <v>160</v>
       </c>
       <c r="F70" t="n">
-        <v>934000</v>
+        <v>952000</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>150</v>
       </c>
       <c r="F71" t="n">
-        <v>717000</v>
+        <v>728000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>851000</v>
+        <v>907000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>60</v>
       </c>
       <c r="F80" t="n">
-        <v>753000</v>
+        <v>762000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>140</v>
       </c>
       <c r="F82" t="n">
-        <v>308000</v>
+        <v>320000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>140</v>
       </c>
       <c r="F83" t="n">
-        <v>718000</v>
+        <v>712000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>90</v>
       </c>
       <c r="F85" t="n">
-        <v>625000</v>
+        <v>633000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -36944,7 +36944,7 @@
         <v>140</v>
       </c>
       <c r="F87" t="n">
-        <v>758000</v>
+        <v>763000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -37026,7 +37026,7 @@
         <v>30</v>
       </c>
       <c r="F89" t="n">
-        <v>726000</v>
+        <v>742000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>80</v>
       </c>
       <c r="F91" t="n">
-        <v>759000</v>
+        <v>757000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37149,7 +37149,7 @@
         <v>130</v>
       </c>
       <c r="F92" t="n">
-        <v>732000</v>
+        <v>759000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>1010</v>
       </c>
       <c r="F96" t="n">
-        <v>350000</v>
+        <v>362000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>928000</v>
+        <v>901000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>80</v>
       </c>
       <c r="F99" t="n">
-        <v>692000</v>
+        <v>689000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37559,7 +37559,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="n">
-        <v>993000</v>
+        <v>956000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>836000</v>
+        <v>843000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37641,7 +37641,7 @@
         <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>657000</v>
+        <v>628000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>891000</v>
+        <v>860000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37887,7 +37887,7 @@
         <v>10</v>
       </c>
       <c r="F110" t="n">
-        <v>740000</v>
+        <v>689000</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -37928,7 +37928,7 @@
         <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>771000</v>
+        <v>772000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -38051,7 +38051,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>513000</v>
+        <v>534000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>150</v>
       </c>
       <c r="F115" t="n">
-        <v>771000</v>
+        <v>785000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38133,7 +38133,7 @@
         <v>120</v>
       </c>
       <c r="F116" t="n">
-        <v>696000</v>
+        <v>709000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>140</v>
       </c>
       <c r="F118" t="n">
-        <v>948000</v>
+        <v>955000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>1000</v>
       </c>
       <c r="F120" t="n">
-        <v>1010000</v>
+        <v>1046000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38338,7 +38338,7 @@
         <v>1010</v>
       </c>
       <c r="F121" t="n">
-        <v>594000</v>
+        <v>583000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -38420,7 +38420,7 @@
         <v>60</v>
       </c>
       <c r="F123" t="n">
-        <v>906000</v>
+        <v>920000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -38461,7 +38461,7 @@
         <v>50</v>
       </c>
       <c r="F124" t="n">
-        <v>748000</v>
+        <v>766000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -38707,7 +38707,7 @@
         <v>70</v>
       </c>
       <c r="F130" t="n">
-        <v>1042000</v>
+        <v>1038000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>90</v>
       </c>
       <c r="F131" t="n">
-        <v>777000</v>
+        <v>767000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -38789,7 +38789,7 @@
         <v>40</v>
       </c>
       <c r="F132" t="n">
-        <v>513000</v>
+        <v>535000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>100</v>
       </c>
       <c r="F133" t="n">
-        <v>668000</v>
+        <v>667000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38912,7 +38912,7 @@
         <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>424000</v>
+        <v>484000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>120</v>
       </c>
       <c r="F137" t="n">
-        <v>952000</v>
+        <v>947000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -39240,7 +39240,7 @@
         <v>30</v>
       </c>
       <c r="F143" t="n">
-        <v>937000</v>
+        <v>939000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -39281,7 +39281,7 @@
         <v>80</v>
       </c>
       <c r="F144" t="n">
-        <v>862000</v>
+        <v>857000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>658000</v>
+        <v>661000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39445,7 +39445,7 @@
         <v>110</v>
       </c>
       <c r="F148" t="n">
-        <v>726000</v>
+        <v>756000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -39486,7 +39486,7 @@
         <v>70</v>
       </c>
       <c r="F149" t="n">
-        <v>784000</v>
+        <v>780000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -39527,7 +39527,7 @@
         <v>60</v>
       </c>
       <c r="F150" t="n">
-        <v>651000</v>
+        <v>661000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -39661,7 +39661,7 @@
         <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>569000</v>
+        <v>614000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>1010</v>
       </c>
       <c r="F4" t="n">
-        <v>758000</v>
+        <v>726000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39743,7 +39743,7 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>607000</v>
+        <v>623000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>988000</v>
+        <v>1012000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>598000</v>
+        <v>594000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40112,7 +40112,7 @@
         <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>540000</v>
+        <v>559000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -40153,7 +40153,7 @@
         <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>299000</v>
+        <v>262000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -40276,7 +40276,7 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>526000</v>
+        <v>523000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>1020000</v>
+        <v>1014000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>253000</v>
+        <v>279000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>160</v>
       </c>
       <c r="F23" t="n">
-        <v>922000</v>
+        <v>920000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>918000</v>
+        <v>942000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -40645,7 +40645,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>610000</v>
+        <v>605000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="n">
-        <v>792000</v>
+        <v>790000</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>788000</v>
+        <v>791000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -40891,7 +40891,7 @@
         <v>1000</v>
       </c>
       <c r="F33" t="n">
-        <v>672000</v>
+        <v>684000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -40932,7 +40932,7 @@
         <v>120</v>
       </c>
       <c r="F34" t="n">
-        <v>776000</v>
+        <v>779000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -41055,7 +41055,7 @@
         <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>656000</v>
+        <v>687000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -41424,7 +41424,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>711000</v>
+        <v>728000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -41506,7 +41506,7 @@
         <v>110</v>
       </c>
       <c r="F48" t="n">
-        <v>246000</v>
+        <v>272000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -41547,7 +41547,7 @@
         <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>435000</v>
+        <v>524000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -41629,7 +41629,7 @@
         <v>100</v>
       </c>
       <c r="F51" t="n">
-        <v>851000</v>
+        <v>860000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>

--- a/players_by_position.xlsx
+++ b/players_by_position.xlsx
@@ -8386,7 +8386,7 @@
         <v>150</v>
       </c>
       <c r="F6" t="n">
-        <v>488000</v>
+        <v>470000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>714000</v>
+        <v>668000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -8468,7 +8468,7 @@
         <v>1000</v>
       </c>
       <c r="F8" t="n">
-        <v>675000</v>
+        <v>647000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -8550,7 +8550,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>677000</v>
+        <v>636000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         <v>120</v>
       </c>
       <c r="F11" t="n">
-        <v>409000</v>
+        <v>412000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -8632,7 +8632,7 @@
         <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>552000</v>
+        <v>528000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -8755,7 +8755,7 @@
         <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>412000</v>
+        <v>422000</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>1010</v>
       </c>
       <c r="F16" t="n">
-        <v>908000</v>
+        <v>914000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>549000</v>
+        <v>536000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -8878,7 +8878,7 @@
         <v>1000</v>
       </c>
       <c r="F18" t="n">
-        <v>312000</v>
+        <v>336000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>60</v>
       </c>
       <c r="F19" t="n">
-        <v>556000</v>
+        <v>544000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -8960,7 +8960,7 @@
         <v>120</v>
       </c>
       <c r="F20" t="n">
-        <v>551000</v>
+        <v>502000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -9001,7 +9001,7 @@
         <v>80</v>
       </c>
       <c r="F21" t="n">
-        <v>339000</v>
+        <v>338000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
         <v>80</v>
       </c>
       <c r="F22" t="n">
-        <v>731000</v>
+        <v>700000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
         <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>799000</v>
+        <v>816000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -9493,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>395000</v>
+        <v>376000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -9575,7 +9575,7 @@
         <v>90</v>
       </c>
       <c r="F35" t="n">
-        <v>892000</v>
+        <v>859000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -9821,7 +9821,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>619000</v>
+        <v>588000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -9862,7 +9862,7 @@
         <v>70</v>
       </c>
       <c r="F42" t="n">
-        <v>735000</v>
+        <v>753000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -9944,7 +9944,7 @@
         <v>110</v>
       </c>
       <c r="F44" t="n">
-        <v>933000</v>
+        <v>975000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>130</v>
       </c>
       <c r="F48" t="n">
-        <v>629000</v>
+        <v>642000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>140</v>
       </c>
       <c r="F49" t="n">
-        <v>265000</v>
+        <v>266000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
         <v>60</v>
       </c>
       <c r="F54" t="n">
-        <v>726000</v>
+        <v>737000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10395,7 +10395,7 @@
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>540000</v>
+        <v>532000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -10641,7 +10641,7 @@
         <v>100</v>
       </c>
       <c r="F61" t="n">
-        <v>462000</v>
+        <v>472000</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -10723,7 +10723,7 @@
         <v>100</v>
       </c>
       <c r="F63" t="n">
-        <v>441000</v>
+        <v>426000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -10764,7 +10764,7 @@
         <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>640000</v>
+        <v>643000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
         <v>60</v>
       </c>
       <c r="F65" t="n">
-        <v>437000</v>
+        <v>391000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -10846,7 +10846,7 @@
         <v>160</v>
       </c>
       <c r="F66" t="n">
-        <v>464000</v>
+        <v>457000</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>960000</v>
+        <v>963000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
         <v>140</v>
       </c>
       <c r="F68" t="n">
-        <v>977000</v>
+        <v>972000</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -10969,7 +10969,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>824000</v>
+        <v>809000</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -11092,7 +11092,7 @@
         <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>372000</v>
+        <v>376000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>70</v>
       </c>
       <c r="F73" t="n">
-        <v>525000</v>
+        <v>527000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -11174,7 +11174,7 @@
         <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>513000</v>
+        <v>518000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>527000</v>
+        <v>548000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -11707,7 +11707,7 @@
         <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>674000</v>
+        <v>651000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11789,7 +11789,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>735000</v>
+        <v>738000</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
         <v>30</v>
       </c>
       <c r="F90" t="n">
-        <v>811000</v>
+        <v>849000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -11871,7 +11871,7 @@
         <v>1010</v>
       </c>
       <c r="F91" t="n">
-        <v>636000</v>
+        <v>630000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>40</v>
       </c>
       <c r="F92" t="n">
-        <v>411000</v>
+        <v>404000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11994,7 +11994,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="n">
-        <v>424000</v>
+        <v>389000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -12158,7 +12158,7 @@
         <v>100</v>
       </c>
       <c r="F98" t="n">
-        <v>400000</v>
+        <v>432000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -12240,7 +12240,7 @@
         <v>120</v>
       </c>
       <c r="F100" t="n">
-        <v>324000</v>
+        <v>336000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -12322,7 +12322,7 @@
         <v>120</v>
       </c>
       <c r="F102" t="n">
-        <v>443000</v>
+        <v>446000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>70</v>
       </c>
       <c r="F103" t="n">
-        <v>578000</v>
+        <v>570000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="n">
-        <v>651000</v>
+        <v>658000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -12445,7 +12445,7 @@
         <v>160</v>
       </c>
       <c r="F105" t="n">
-        <v>326000</v>
+        <v>324000</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -12486,7 +12486,7 @@
         <v>100</v>
       </c>
       <c r="F106" t="n">
-        <v>455000</v>
+        <v>486000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -12527,7 +12527,7 @@
         <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>763000</v>
+        <v>749000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -12568,7 +12568,7 @@
         <v>130</v>
       </c>
       <c r="F108" t="n">
-        <v>457000</v>
+        <v>447000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
         <v>1010</v>
       </c>
       <c r="F112" t="n">
-        <v>641000</v>
+        <v>611000</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -12855,7 +12855,7 @@
         <v>30</v>
       </c>
       <c r="F115" t="n">
-        <v>695000</v>
+        <v>673000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
         <v>150</v>
       </c>
       <c r="F117" t="n">
-        <v>559000</v>
+        <v>569000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -12978,7 +12978,7 @@
         <v>40</v>
       </c>
       <c r="F118" t="n">
-        <v>759000</v>
+        <v>751000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -13019,7 +13019,7 @@
         <v>130</v>
       </c>
       <c r="F119" t="n">
-        <v>502000</v>
+        <v>448000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -13060,7 +13060,7 @@
         <v>40</v>
       </c>
       <c r="F120" t="n">
-        <v>644000</v>
+        <v>603000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
         <v>70</v>
       </c>
       <c r="F122" t="n">
-        <v>763000</v>
+        <v>767000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -13183,7 +13183,7 @@
         <v>1010</v>
       </c>
       <c r="F123" t="n">
-        <v>759000</v>
+        <v>757000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -13224,7 +13224,7 @@
         <v>80</v>
       </c>
       <c r="F124" t="n">
-        <v>923000</v>
+        <v>882000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -13306,7 +13306,7 @@
         <v>1000</v>
       </c>
       <c r="F126" t="n">
-        <v>577000</v>
+        <v>567000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>90</v>
       </c>
       <c r="F127" t="n">
-        <v>544000</v>
+        <v>551000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -13552,7 +13552,7 @@
         <v>110</v>
       </c>
       <c r="F132" t="n">
-        <v>523000</v>
+        <v>549000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -13634,7 +13634,7 @@
         <v>10</v>
       </c>
       <c r="F134" t="n">
-        <v>495000</v>
+        <v>500000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>50</v>
       </c>
       <c r="F136" t="n">
-        <v>336000</v>
+        <v>353000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -13757,7 +13757,7 @@
         <v>160</v>
       </c>
       <c r="F137" t="n">
-        <v>385000</v>
+        <v>384000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -13798,7 +13798,7 @@
         <v>110</v>
       </c>
       <c r="F138" t="n">
-        <v>527000</v>
+        <v>504000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -13839,7 +13839,7 @@
         <v>10</v>
       </c>
       <c r="F139" t="n">
-        <v>832000</v>
+        <v>800000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -13921,7 +13921,7 @@
         <v>20</v>
       </c>
       <c r="F141" t="n">
-        <v>592000</v>
+        <v>559000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>90</v>
       </c>
       <c r="F142" t="n">
-        <v>547000</v>
+        <v>528000</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -14003,7 +14003,7 @@
         <v>150</v>
       </c>
       <c r="F143" t="n">
-        <v>638000</v>
+        <v>597000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -14044,7 +14044,7 @@
         <v>90</v>
       </c>
       <c r="F144" t="n">
-        <v>589000</v>
+        <v>537000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -14085,7 +14085,7 @@
         <v>140</v>
       </c>
       <c r="F145" t="n">
-        <v>635000</v>
+        <v>624000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>100</v>
       </c>
       <c r="F146" t="n">
-        <v>423000</v>
+        <v>459000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
         <v>80</v>
       </c>
       <c r="F147" t="n">
-        <v>487000</v>
+        <v>491000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -14372,7 +14372,7 @@
         <v>150</v>
       </c>
       <c r="F152" t="n">
-        <v>856000</v>
+        <v>843000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -14413,7 +14413,7 @@
         <v>160</v>
       </c>
       <c r="F153" t="n">
-        <v>648000</v>
+        <v>597000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -14495,7 +14495,7 @@
         <v>100</v>
       </c>
       <c r="F155" t="n">
-        <v>563000</v>
+        <v>567000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -14536,7 +14536,7 @@
         <v>60</v>
       </c>
       <c r="F156" t="n">
-        <v>549000</v>
+        <v>545000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>90</v>
       </c>
       <c r="F157" t="n">
-        <v>467000</v>
+        <v>450000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -14618,7 +14618,7 @@
         <v>50</v>
       </c>
       <c r="F158" t="n">
-        <v>635000</v>
+        <v>684000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>496000</v>
+        <v>473000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
         <v>10</v>
       </c>
       <c r="F163" t="n">
-        <v>534000</v>
+        <v>526000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -14864,7 +14864,7 @@
         <v>10</v>
       </c>
       <c r="F164" t="n">
-        <v>926000</v>
+        <v>917000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -14946,7 +14946,7 @@
         <v>120</v>
       </c>
       <c r="F166" t="n">
-        <v>547000</v>
+        <v>534000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -14987,7 +14987,7 @@
         <v>160</v>
       </c>
       <c r="F167" t="n">
-        <v>800000</v>
+        <v>781000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         <v>70</v>
       </c>
       <c r="F172" t="n">
-        <v>552000</v>
+        <v>570000</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -15356,7 +15356,7 @@
         <v>10</v>
       </c>
       <c r="F176" t="n">
-        <v>643000</v>
+        <v>607000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -15479,7 +15479,7 @@
         <v>1000</v>
       </c>
       <c r="F179" t="n">
-        <v>915000</v>
+        <v>949000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -15520,7 +15520,7 @@
         <v>110</v>
       </c>
       <c r="F180" t="n">
-        <v>269000</v>
+        <v>268000</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -15561,7 +15561,7 @@
         <v>130</v>
       </c>
       <c r="F181" t="n">
-        <v>434000</v>
+        <v>444000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -15602,7 +15602,7 @@
         <v>70</v>
       </c>
       <c r="F182" t="n">
-        <v>583000</v>
+        <v>572000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -15643,7 +15643,7 @@
         <v>140</v>
       </c>
       <c r="F183" t="n">
-        <v>455000</v>
+        <v>436000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
         <v>70</v>
       </c>
       <c r="F185" t="n">
-        <v>616000</v>
+        <v>606000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -15766,7 +15766,7 @@
         <v>100</v>
       </c>
       <c r="F186" t="n">
-        <v>656000</v>
+        <v>659000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -15848,7 +15848,7 @@
         <v>100</v>
       </c>
       <c r="F188" t="n">
-        <v>867000</v>
+        <v>856000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -16012,7 +16012,7 @@
         <v>60</v>
       </c>
       <c r="F192" t="n">
-        <v>312000</v>
+        <v>287000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
         <v>50</v>
       </c>
       <c r="F197" t="n">
-        <v>610000</v>
+        <v>642000</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -16258,7 +16258,7 @@
         <v>40</v>
       </c>
       <c r="F198" t="n">
-        <v>265000</v>
+        <v>252000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -16381,7 +16381,7 @@
         <v>160</v>
       </c>
       <c r="F201" t="n">
-        <v>420000</v>
+        <v>414000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -16463,7 +16463,7 @@
         <v>50</v>
       </c>
       <c r="F203" t="n">
-        <v>681000</v>
+        <v>645000</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -16504,7 +16504,7 @@
         <v>50</v>
       </c>
       <c r="F204" t="n">
-        <v>502000</v>
+        <v>554000</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
         <v>1000</v>
       </c>
       <c r="F206" t="n">
-        <v>632000</v>
+        <v>628000</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -16627,7 +16627,7 @@
         <v>90</v>
       </c>
       <c r="F207" t="n">
-        <v>787000</v>
+        <v>758000</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -16668,7 +16668,7 @@
         <v>50</v>
       </c>
       <c r="F208" t="n">
-        <v>761000</v>
+        <v>769000</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -16709,7 +16709,7 @@
         <v>160</v>
       </c>
       <c r="F209" t="n">
-        <v>639000</v>
+        <v>616000</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -16873,7 +16873,7 @@
         <v>60</v>
       </c>
       <c r="F213" t="n">
-        <v>720000</v>
+        <v>704000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -16996,7 +16996,7 @@
         <v>90</v>
       </c>
       <c r="F216" t="n">
-        <v>603000</v>
+        <v>550000</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -17078,7 +17078,7 @@
         <v>140</v>
       </c>
       <c r="F218" t="n">
-        <v>586000</v>
+        <v>580000</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -17119,7 +17119,7 @@
         <v>160</v>
       </c>
       <c r="F219" t="n">
-        <v>613000</v>
+        <v>650000</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>120</v>
       </c>
       <c r="F220" t="n">
-        <v>751000</v>
+        <v>735000</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>80</v>
       </c>
       <c r="F221" t="n">
-        <v>732000</v>
+        <v>712000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -17242,7 +17242,7 @@
         <v>130</v>
       </c>
       <c r="F222" t="n">
-        <v>586000</v>
+        <v>549000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -17447,7 +17447,7 @@
         <v>150</v>
       </c>
       <c r="F227" t="n">
-        <v>495000</v>
+        <v>458000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -17488,7 +17488,7 @@
         <v>70</v>
       </c>
       <c r="F228" t="n">
-        <v>755000</v>
+        <v>749000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -17529,7 +17529,7 @@
         <v>130</v>
       </c>
       <c r="F229" t="n">
-        <v>671000</v>
+        <v>685000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -17570,7 +17570,7 @@
         <v>1010</v>
       </c>
       <c r="F230" t="n">
-        <v>461000</v>
+        <v>455000</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -17652,7 +17652,7 @@
         <v>1010</v>
       </c>
       <c r="F232" t="n">
-        <v>515000</v>
+        <v>478000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -17816,7 +17816,7 @@
         <v>120</v>
       </c>
       <c r="F236" t="n">
-        <v>491000</v>
+        <v>470000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>130</v>
       </c>
       <c r="F237" t="n">
-        <v>436000</v>
+        <v>447000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -17939,7 +17939,7 @@
         <v>90</v>
       </c>
       <c r="F239" t="n">
-        <v>599000</v>
+        <v>586000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -17980,7 +17980,7 @@
         <v>1000</v>
       </c>
       <c r="F240" t="n">
-        <v>783000</v>
+        <v>779000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -18062,7 +18062,7 @@
         <v>120</v>
       </c>
       <c r="F242" t="n">
-        <v>644000</v>
+        <v>640000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
         <v>80</v>
       </c>
       <c r="F247" t="n">
-        <v>611000</v>
+        <v>587000</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -18308,7 +18308,7 @@
         <v>110</v>
       </c>
       <c r="F248" t="n">
-        <v>447000</v>
+        <v>458000</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>30</v>
       </c>
       <c r="F249" t="n">
-        <v>582000</v>
+        <v>599000</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -18390,7 +18390,7 @@
         <v>1010</v>
       </c>
       <c r="F250" t="n">
-        <v>963000</v>
+        <v>950000</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -18431,7 +18431,7 @@
         <v>160</v>
       </c>
       <c r="F251" t="n">
-        <v>604000</v>
+        <v>579000</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -18472,7 +18472,7 @@
         <v>130</v>
       </c>
       <c r="F252" t="n">
-        <v>789000</v>
+        <v>767000</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -18513,7 +18513,7 @@
         <v>140</v>
       </c>
       <c r="F253" t="n">
-        <v>697000</v>
+        <v>662000</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -18554,7 +18554,7 @@
         <v>20</v>
       </c>
       <c r="F254" t="n">
-        <v>727000</v>
+        <v>708000</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -18595,7 +18595,7 @@
         <v>30</v>
       </c>
       <c r="F255" t="n">
-        <v>728000</v>
+        <v>744000</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -18636,7 +18636,7 @@
         <v>130</v>
       </c>
       <c r="F256" t="n">
-        <v>770000</v>
+        <v>769000</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
         <v>90</v>
       </c>
       <c r="F257" t="n">
-        <v>503000</v>
+        <v>501000</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -18718,7 +18718,7 @@
         <v>60</v>
       </c>
       <c r="F258" t="n">
-        <v>772000</v>
+        <v>746000</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -18759,7 +18759,7 @@
         <v>10</v>
       </c>
       <c r="F259" t="n">
-        <v>654000</v>
+        <v>626000</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -18800,7 +18800,7 @@
         <v>30</v>
       </c>
       <c r="F260" t="n">
-        <v>414000</v>
+        <v>443000</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -18841,7 +18841,7 @@
         <v>150</v>
       </c>
       <c r="F261" t="n">
-        <v>476000</v>
+        <v>494000</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -18964,7 +18964,7 @@
         <v>20</v>
       </c>
       <c r="F264" t="n">
-        <v>908000</v>
+        <v>904000</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>682000</v>
+        <v>689000</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -19221,7 +19221,7 @@
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>448000</v>
+        <v>442000</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -19385,7 +19385,7 @@
         <v>110</v>
       </c>
       <c r="F10" t="n">
-        <v>370000</v>
+        <v>396000</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -19426,7 +19426,7 @@
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>505000</v>
+        <v>522000</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -19549,7 +19549,7 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>902000</v>
+        <v>896000</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>408000</v>
+        <v>435000</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -19795,7 +19795,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>249000</v>
+        <v>295000</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -19918,7 +19918,7 @@
         <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>488000</v>
+        <v>503000</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -19959,7 +19959,7 @@
         <v>60</v>
       </c>
       <c r="F24" t="n">
-        <v>732000</v>
+        <v>727000</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -20041,7 +20041,7 @@
         <v>140</v>
       </c>
       <c r="F26" t="n">
-        <v>654000</v>
+        <v>652000</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -20123,7 +20123,7 @@
         <v>1010</v>
       </c>
       <c r="F28" t="n">
-        <v>569000</v>
+        <v>558000</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -20164,7 +20164,7 @@
         <v>140</v>
       </c>
       <c r="F29" t="n">
-        <v>635000</v>
+        <v>570000</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -20246,7 +20246,7 @@
         <v>130</v>
       </c>
       <c r="F31" t="n">
-        <v>427000</v>
+        <v>467000</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -20328,7 +20328,7 @@
         <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>578000</v>
+        <v>553000</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -20369,7 +20369,7 @@
         <v>110</v>
       </c>
       <c r="F34" t="n">
-        <v>772000</v>
+        <v>765000</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -20410,7 +20410,7 @@
         <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>489000</v>
+        <v>535000</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -20451,7 +20451,7 @@
         <v>1010</v>
       </c>
       <c r="F36" t="n">
-        <v>516000</v>
+        <v>525000</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -20492,7 +20492,7 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>600000</v>
+        <v>611000</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -20533,7 +20533,7 @@
         <v>70</v>
       </c>
       <c r="F38" t="n">
-        <v>602000</v>
+        <v>593000</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -20615,7 +20615,7 @@
         <v>160</v>
       </c>
       <c r="F40" t="n">
-        <v>611000</v>
+        <v>628000</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -20656,7 +20656,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>543000</v>
+        <v>556000</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -20820,7 +20820,7 @@
         <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>640000</v>
+        <v>657000</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -20861,7 +20861,7 @@
         <v>80</v>
       </c>
       <c r="F46" t="n">
-        <v>597000</v>
+        <v>572000</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -20902,7 +20902,7 @@
         <v>70</v>
       </c>
       <c r="F47" t="n">
-        <v>636000</v>
+        <v>641000</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         <v>120</v>
       </c>
       <c r="F48" t="n">
-        <v>276000</v>
+        <v>297000</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -20984,7 +20984,7 @@
         <v>160</v>
       </c>
       <c r="F49" t="n">
-        <v>476000</v>
+        <v>477000</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -21025,7 +21025,7 @@
         <v>70</v>
       </c>
       <c r="F50" t="n">
-        <v>456000</v>
+        <v>447000</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -21107,7 +21107,7 @@
         <v>150</v>
       </c>
       <c r="F52" t="n">
-        <v>537000</v>
+        <v>541000</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -21189,7 +21189,7 @@
         <v>1010</v>
       </c>
       <c r="F54" t="n">
-        <v>682000</v>
+        <v>686000</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -21230,7 +21230,7 @@
         <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>593000</v>
+        <v>594000</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -21312,7 +21312,7 @@
         <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>632000</v>
+        <v>625000</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -21353,7 +21353,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>454000</v>
+        <v>463000</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -21517,7 +21517,7 @@
         <v>160</v>
       </c>
       <c r="F62" t="n">
-        <v>659000</v>
+        <v>656000</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -21599,7 +21599,7 @@
         <v>100</v>
       </c>
       <c r="F64" t="n">
-        <v>701000</v>
+        <v>674000</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -21640,7 +21640,7 @@
         <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>583000</v>
+        <v>588000</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -21804,7 +21804,7 @@
         <v>100</v>
       </c>
       <c r="F69" t="n">
-        <v>599000</v>
+        <v>580000</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -21845,7 +21845,7 @@
         <v>160</v>
       </c>
       <c r="F70" t="n">
-        <v>380000</v>
+        <v>448000</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -21886,7 +21886,7 @@
         <v>140</v>
       </c>
       <c r="F71" t="n">
-        <v>522000</v>
+        <v>546000</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -21927,7 +21927,7 @@
         <v>50</v>
       </c>
       <c r="F72" t="n">
-        <v>424000</v>
+        <v>445000</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -21968,7 +21968,7 @@
         <v>40</v>
       </c>
       <c r="F73" t="n">
-        <v>826000</v>
+        <v>825000</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -22050,7 +22050,7 @@
         <v>1010</v>
       </c>
       <c r="F75" t="n">
-        <v>372000</v>
+        <v>415000</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
@@ -22132,7 +22132,7 @@
         <v>140</v>
       </c>
       <c r="F77" t="n">
-        <v>461000</v>
+        <v>451000</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -22255,7 +22255,7 @@
         <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>588000</v>
+        <v>587000</v>
       </c>
       <c r="G80" t="n">
         <v>1</v>
@@ -22337,7 +22337,7 @@
         <v>60</v>
       </c>
       <c r="F82" t="n">
-        <v>489000</v>
+        <v>466000</v>
       </c>
       <c r="G82" t="n">
         <v>1</v>
@@ -22378,7 +22378,7 @@
         <v>150</v>
       </c>
       <c r="F83" t="n">
-        <v>437000</v>
+        <v>433000</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -22419,7 +22419,7 @@
         <v>110</v>
       </c>
       <c r="F84" t="n">
-        <v>485000</v>
+        <v>474000</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -22706,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="F91" t="n">
-        <v>688000</v>
+        <v>701000</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
@@ -22952,7 +22952,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="n">
-        <v>668000</v>
+        <v>687000</v>
       </c>
       <c r="G97" t="n">
         <v>1</v>
@@ -23034,7 +23034,7 @@
         <v>60</v>
       </c>
       <c r="F99" t="n">
-        <v>603000</v>
+        <v>581000</v>
       </c>
       <c r="G99" t="n">
         <v>1</v>
@@ -23075,7 +23075,7 @@
         <v>140</v>
       </c>
       <c r="F100" t="n">
-        <v>663000</v>
+        <v>699000</v>
       </c>
       <c r="G100" t="n">
         <v>1</v>
@@ -23116,7 +23116,7 @@
         <v>90</v>
       </c>
       <c r="F101" t="n">
-        <v>664000</v>
+        <v>667000</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
@@ -23157,7 +23157,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="n">
-        <v>531000</v>
+        <v>507000</v>
       </c>
       <c r="G102" t="n">
         <v>1</v>
@@ -23280,7 +23280,7 @@
         <v>110</v>
       </c>
       <c r="F105" t="n">
-        <v>639000</v>
+        <v>670000</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
@@ -23403,7 +23403,7 @@
         <v>150</v>
       </c>
       <c r="F108" t="n">
-        <v>725000</v>
+        <v>742000</v>
       </c>
       <c r="G108" t="n">
         <v>1</v>
@@ -23485,7 +23485,7 @@
         <v>120</v>
       </c>
       <c r="F110" t="n">
-        <v>417000</v>
+        <v>400000</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -23526,7 +23526,7 @@
         <v>1010</v>
       </c>
       <c r="F111" t="n">
-        <v>835000</v>
+        <v>820000</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
@@ -23649,7 +23649,7 @@
         <v>150</v>
       </c>
       <c r="F114" t="n">
-        <v>392000</v>
+        <v>402000</v>
       </c>
       <c r="G114" t="n">
         <v>1</v>
@@ -23690,7 +23690,7 @@
         <v>1010</v>
       </c>
       <c r="F115" t="n">
-        <v>463000</v>
+        <v>457000</v>
       </c>
       <c r="G115" t="n">
         <v>1</v>
@@ -23772,7 +23772,7 @@
         <v>1000</v>
       </c>
       <c r="F117" t="n">
-        <v>413000</v>
+        <v>432000</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -23813,7 +23813,7 @@
         <v>80</v>
       </c>
       <c r="F118" t="n">
-        <v>700000</v>
+        <v>687000</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -23854,7 +23854,7 @@
         <v>130</v>
       </c>
       <c r="F119" t="n">
-        <v>987000</v>
+        <v>1045000</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -23895,7 +23895,7 @@
         <v>1010</v>
       </c>
       <c r="F120" t="n">
-        <v>339000</v>
+        <v>355000</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
@@ -23936,7 +23936,7 @@
         <v>160</v>
       </c>
       <c r="F121" t="n">
-        <v>386000</v>
+        <v>415000</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -24059,7 +24059,7 @@
         <v>40</v>
       </c>
       <c r="F124" t="n">
-        <v>503000</v>
+        <v>500000</v>
       </c>
       <c r="G124" t="n">
         <v>1</v>
@@ -24182,7 +24182,7 @@
         <v>40</v>
       </c>
       <c r="F127" t="n">
-        <v>326000</v>
+        <v>340000</v>
       </c>
       <c r="G127" t="n">
         <v>1</v>
@@ -24346,7 +24346,7 @@
         <v>70</v>
       </c>
       <c r="F131" t="n">
-        <v>479000</v>
+        <v>444000</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -24428,7 +24428,7 @@
         <v>70</v>
       </c>
       <c r="F133" t="n">
-        <v>596000</v>
+        <v>608000</v>
       </c>
       <c r="G133" t="n">
         <v>1</v>
@@ -24592,7 +24592,7 @@
         <v>130</v>
       </c>
       <c r="F137" t="n">
-        <v>1055000</v>
+        <v>1081000</v>
       </c>
       <c r="G137" t="n">
         <v>1</v>
@@ -24674,7 +24674,7 @@
         <v>20</v>
       </c>
       <c r="F139" t="n">
-        <v>490000</v>
+        <v>526000</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -24797,7 +24797,7 @@
         <v>1000</v>
       </c>
       <c r="F142" t="n">
-        <v>399000</v>
+        <v>408000</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -24879,7 +24879,7 @@
         <v>120</v>
       </c>
       <c r="F144" t="n">
-        <v>460000</v>
+        <v>459000</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -24961,7 +24961,7 @@
         <v>1000</v>
       </c>
       <c r="F146" t="n">
-        <v>586000</v>
+        <v>589000</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -25002,7 +25002,7 @@
         <v>140</v>
       </c>
       <c r="F147" t="n">
-        <v>554000</v>
+        <v>562000</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -25043,7 +25043,7 @@
         <v>90</v>
       </c>
       <c r="F148" t="n">
-        <v>353000</v>
+        <v>346000</v>
       </c>
       <c r="G148" t="n">
         <v>1</v>
@@ -25125,7 +25125,7 @@
         <v>140</v>
       </c>
       <c r="F150" t="n">
-        <v>470000</v>
+        <v>499000</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -25207,7 +25207,7 @@
         <v>50</v>
       </c>
       <c r="F152" t="n">
-        <v>424000</v>
+        <v>422000</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F154" t="n">
-        <v>381000</v>
+        <v>393000</v>
       </c>
       <c r="G154" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>10</v>
       </c>
       <c r="F155" t="n">
-        <v>576000</v>
+        <v>584000</v>
       </c>
       <c r="G155" t="n">
         <v>1</v>
@@ -25412,7 +25412,7 @@
         <v>150</v>
       </c>
       <c r="F157" t="n">
-        <v>860000</v>
+        <v>875000</v>
       </c>
       <c r="G157" t="n">
         <v>1</v>
@@ -25453,7 +25453,7 @@
         <v>30</v>
       </c>
       <c r="F158" t="n">
-        <v>585000</v>
+        <v>599000</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
@@ -25535,7 +25535,7 @@
         <v>140</v>
       </c>
       <c r="F160" t="n">
-        <v>512000</v>
+        <v>528000</v>
       </c>
       <c r="G160" t="n">
         <v>1</v>
@@ -25822,7 +25822,7 @@
         <v>130</v>
       </c>
       <c r="F167" t="n">
-        <v>462000</v>
+        <v>466000</v>
       </c>
       <c r="G167" t="n">
         <v>1</v>
@@ -25904,7 +25904,7 @@
         <v>90</v>
       </c>
       <c r="F169" t="n">
-        <v>673000</v>
+        <v>635000</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -25945,7 +25945,7 @@
         <v>50</v>
       </c>
       <c r="F170" t="n">
-        <v>568000</v>
+        <v>548000</v>
       </c>
       <c r="G170" t="n">
         <v>1</v>
@@ -25986,7 +25986,7 @@
         <v>100</v>
       </c>
       <c r="F171" t="n">
-        <v>590000</v>
+        <v>571000</v>
       </c>
       <c r="G171" t="n">
         <v>1</v>
@@ -26027,7 +26027,7 @@
         <v>90</v>
       </c>
       <c r="F172" t="n">
-        <v>517000</v>
+        <v>523000</v>
       </c>
       <c r="G172" t="n">
         <v>1</v>
@@ -26109,7 +26109,7 @@
         <v>120</v>
       </c>
       <c r="F174" t="n">
-        <v>472000</v>
+        <v>483000</v>
       </c>
       <c r="G174" t="n">
         <v>1</v>
@@ -26191,7 +26191,7 @@
         <v>80</v>
       </c>
       <c r="F176" t="n">
-        <v>570000</v>
+        <v>589000</v>
       </c>
       <c r="G176" t="n">
         <v>1</v>
@@ -26314,7 +26314,7 @@
         <v>160</v>
       </c>
       <c r="F179" t="n">
-        <v>627000</v>
+        <v>662000</v>
       </c>
       <c r="G179" t="n">
         <v>1</v>
@@ -26396,7 +26396,7 @@
         <v>20</v>
       </c>
       <c r="F181" t="n">
-        <v>749000</v>
+        <v>721000</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -26437,7 +26437,7 @@
         <v>1000</v>
       </c>
       <c r="F182" t="n">
-        <v>576000</v>
+        <v>581000</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
@@ -26478,7 +26478,7 @@
         <v>1000</v>
       </c>
       <c r="F183" t="n">
-        <v>466000</v>
+        <v>465000</v>
       </c>
       <c r="G183" t="n">
         <v>1</v>
@@ -26519,7 +26519,7 @@
         <v>40</v>
       </c>
       <c r="F184" t="n">
-        <v>664000</v>
+        <v>663000</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
@@ -26765,7 +26765,7 @@
         <v>120</v>
       </c>
       <c r="F190" t="n">
-        <v>461000</v>
+        <v>469000</v>
       </c>
       <c r="G190" t="n">
         <v>1</v>
@@ -26806,7 +26806,7 @@
         <v>80</v>
       </c>
       <c r="F191" t="n">
-        <v>807000</v>
+        <v>781000</v>
       </c>
       <c r="G191" t="n">
         <v>1</v>
@@ -27011,7 +27011,7 @@
         <v>70</v>
       </c>
       <c r="F196" t="n">
-        <v>723000</v>
+        <v>786000</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -27134,7 +27134,7 @@
         <v>130</v>
       </c>
       <c r="F199" t="n">
-        <v>950000</v>
+        <v>909000</v>
       </c>
       <c r="G199" t="n">
         <v>1</v>
@@ -27175,7 +27175,7 @@
         <v>110</v>
       </c>
       <c r="F200" t="n">
-        <v>473000</v>
+        <v>475000</v>
       </c>
       <c r="G200" t="n">
         <v>1</v>
@@ -27216,7 +27216,7 @@
         <v>70</v>
       </c>
       <c r="F201" t="n">
-        <v>448000</v>
+        <v>461000</v>
       </c>
       <c r="G201" t="n">
         <v>1</v>
@@ -27544,7 +27544,7 @@
         <v>40</v>
       </c>
       <c r="F209" t="n">
-        <v>619000</v>
+        <v>654000</v>
       </c>
       <c r="G209" t="n">
         <v>1</v>
@@ -27585,7 +27585,7 @@
         <v>160</v>
       </c>
       <c r="F210" t="n">
-        <v>543000</v>
+        <v>560000</v>
       </c>
       <c r="G210" t="n">
         <v>1</v>
@@ -27626,7 +27626,7 @@
         <v>30</v>
       </c>
       <c r="F211" t="n">
-        <v>569000</v>
+        <v>563000</v>
       </c>
       <c r="G211" t="n">
         <v>1</v>
@@ -27708,7 +27708,7 @@
         <v>30</v>
       </c>
       <c r="F213" t="n">
-        <v>627000</v>
+        <v>621000</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -27749,7 +27749,7 @@
         <v>20</v>
       </c>
       <c r="F214" t="n">
-        <v>434000</v>
+        <v>432000</v>
       </c>
       <c r="G214" t="n">
         <v>1</v>
@@ -27790,7 +27790,7 @@
         <v>100</v>
       </c>
       <c r="F215" t="n">
-        <v>738000</v>
+        <v>727000</v>
       </c>
       <c r="G215" t="n">
         <v>1</v>
@@ -27995,7 +27995,7 @@
         <v>40</v>
       </c>
       <c r="F220" t="n">
-        <v>781000</v>
+        <v>762000</v>
       </c>
       <c r="G220" t="n">
         <v>1</v>
@@ -28118,7 +28118,7 @@
         <v>40</v>
       </c>
       <c r="F223" t="n">
-        <v>628000</v>
+        <v>600000</v>
       </c>
       <c r="G223" t="n">
         <v>1</v>
@@ -28200,7 +28200,7 @@
         <v>70</v>
       </c>
       <c r="F225" t="n">
-        <v>648000</v>
+        <v>629000</v>
       </c>
       <c r="G225" t="n">
         <v>1</v>
@@ -28323,7 +28323,7 @@
         <v>1000</v>
       </c>
       <c r="F228" t="n">
-        <v>836000</v>
+        <v>865000</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -28446,7 +28446,7 @@
         <v>80</v>
       </c>
       <c r="F231" t="n">
-        <v>716000</v>
+        <v>734000</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -28487,7 +28487,7 @@
         <v>110</v>
       </c>
       <c r="F232" t="n">
-        <v>401000</v>
+        <v>409000</v>
       </c>
       <c r="G232" t="n">
         <v>1</v>
@@ -28528,7 +28528,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="n">
-        <v>662000</v>
+        <v>713000</v>
       </c>
       <c r="G233" t="n">
         <v>1</v>
@@ -28610,7 +28610,7 @@
         <v>150</v>
       </c>
       <c r="F235" t="n">
-        <v>557000</v>
+        <v>592000</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
@@ -28692,7 +28692,7 @@
         <v>60</v>
       </c>
       <c r="F237" t="n">
-        <v>230000</v>
+        <v>257000</v>
       </c>
       <c r="G237" t="n">
         <v>1</v>
@@ -28774,7 +28774,7 @@
         <v>140</v>
       </c>
       <c r="F239" t="n">
-        <v>558000</v>
+        <v>579000</v>
       </c>
       <c r="G239" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="n">
-        <v>668000</v>
+        <v>653000</v>
       </c>
       <c r="G240" t="n">
         <v>1</v>
@@ -28856,7 +28856,7 @@
         <v>70</v>
       </c>
       <c r="F241" t="n">
-        <v>650000</v>
+        <v>656000</v>
       </c>
       <c r="G241" t="n">
         <v>1</v>
@@ -28979,7 +28979,7 @@
         <v>1010</v>
       </c>
       <c r="F244" t="n">
-        <v>595000</v>
+        <v>575000</v>
       </c>
       <c r="G244" t="n">
         <v>1</v>
@@ -29061,7 +29061,7 @@
         <v>130</v>
       </c>
       <c r="F246" t="n">
-        <v>618000</v>
+        <v>632000</v>
       </c>
       <c r="G246" t="n">
         <v>1</v>
@@ -29143,7 +29143,7 @@
         <v>160</v>
       </c>
       <c r="F248" t="n">
-        <v>593000</v>
+        <v>584000</v>
       </c>
       <c r="G248" t="n">
         <v>1</v>
@@ -29225,7 +29225,7 @@
         <v>50</v>
       </c>
       <c r="F250" t="n">
-        <v>553000</v>
+        <v>559000</v>
       </c>
       <c r="G250" t="n">
         <v>1</v>
@@ -29307,7 +29307,7 @@
         <v>90</v>
       </c>
       <c r="F252" t="n">
-        <v>651000</v>
+        <v>697000</v>
       </c>
       <c r="G252" t="n">
         <v>1</v>
@@ -29389,7 +29389,7 @@
         <v>130</v>
       </c>
       <c r="F254" t="n">
-        <v>687000</v>
+        <v>653000</v>
       </c>
       <c r="G254" t="n">
         <v>1</v>
@@ -29430,7 +29430,7 @@
         <v>90</v>
       </c>
       <c r="F255" t="n">
-        <v>868000</v>
+        <v>871000</v>
       </c>
       <c r="G255" t="n">
         <v>1</v>
@@ -29553,7 +29553,7 @@
         <v>70</v>
       </c>
       <c r="F258" t="n">
-        <v>391000</v>
+        <v>394000</v>
       </c>
       <c r="G258" t="n">
         <v>1</v>
@@ -29717,7 +29717,7 @@
         <v>10</v>
       </c>
       <c r="F262" t="n">
-        <v>549000</v>
+        <v>524000</v>
       </c>
       <c r="G262" t="n">
         <v>1</v>
@@ -29799,7 +29799,7 @@
         <v>10</v>
       </c>
       <c r="F264" t="n">
-        <v>1057000</v>
+        <v>1114000</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
@@ -29840,7 +29840,7 @@
         <v>20</v>
       </c>
       <c r="F265" t="n">
-        <v>706000</v>
+        <v>705000</v>
       </c>
       <c r="G265" t="n">
         <v>1</v>
@@ -29881,7 +29881,7 @@
         <v>1000</v>
       </c>
       <c r="F266" t="n">
-        <v>362000</v>
+        <v>378000</v>
       </c>
       <c r="G266" t="n">
         <v>1</v>
@@ -30086,7 +30086,7 @@
         <v>110</v>
       </c>
       <c r="F271" t="n">
-        <v>816000</v>
+        <v>850000</v>
       </c>
       <c r="G271" t="n">
         <v>1</v>
@@ -30127,7 +30127,7 @@
         <v>120</v>
       </c>
       <c r="F272" t="n">
-        <v>324000</v>
+        <v>320000</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
@@ -30291,7 +30291,7 @@
         <v>1000</v>
       </c>
       <c r="F276" t="n">
-        <v>335000</v>
+        <v>342000</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
@@ -30373,7 +30373,7 @@
         <v>120</v>
       </c>
       <c r="F278" t="n">
-        <v>733000</v>
+        <v>752000</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -30414,7 +30414,7 @@
         <v>160</v>
       </c>
       <c r="F279" t="n">
-        <v>666000</v>
+        <v>669000</v>
       </c>
       <c r="G279" t="n">
         <v>1</v>
@@ -30455,7 +30455,7 @@
         <v>130</v>
       </c>
       <c r="F280" t="n">
-        <v>414000</v>
+        <v>386000</v>
       </c>
       <c r="G280" t="n">
         <v>1</v>
@@ -30537,7 +30537,7 @@
         <v>140</v>
       </c>
       <c r="F282" t="n">
-        <v>709000</v>
+        <v>697000</v>
       </c>
       <c r="G282" t="n">
         <v>1</v>
@@ -30619,7 +30619,7 @@
         <v>60</v>
       </c>
       <c r="F284" t="n">
-        <v>279000</v>
+        <v>284000</v>
       </c>
       <c r="G284" t="n">
         <v>1</v>
@@ -30742,7 +30742,7 @@
         <v>40</v>
       </c>
       <c r="F287" t="n">
-        <v>653000</v>
+        <v>656000</v>
       </c>
       <c r="G287" t="n">
         <v>1</v>
@@ -30783,7 +30783,7 @@
         <v>150</v>
       </c>
       <c r="F288" t="n">
-        <v>475000</v>
+        <v>433000</v>
       </c>
       <c r="G288" t="n">
         <v>1</v>
@@ -30824,7 +30824,7 @@
         <v>130</v>
       </c>
       <c r="F289" t="n">
-        <v>533000</v>
+        <v>516000</v>
       </c>
       <c r="G289" t="n">
         <v>1</v>
@@ -30865,7 +30865,7 @@
         <v>50</v>
       </c>
       <c r="F290" t="n">
-        <v>789000</v>
+        <v>802000</v>
       </c>
       <c r="G290" t="n">
         <v>1</v>
@@ -30906,7 +30906,7 @@
         <v>90</v>
       </c>
       <c r="F291" t="n">
-        <v>526000</v>
+        <v>511000</v>
       </c>
       <c r="G291" t="n">
         <v>1</v>
@@ -30988,7 +30988,7 @@
         <v>100</v>
       </c>
       <c r="F293" t="n">
-        <v>801000</v>
+        <v>822000</v>
       </c>
       <c r="G293" t="n">
         <v>1</v>
@@ -31111,7 +31111,7 @@
         <v>30</v>
       </c>
       <c r="F296" t="n">
-        <v>826000</v>
+        <v>830000</v>
       </c>
       <c r="G296" t="n">
         <v>1</v>
@@ -31234,7 +31234,7 @@
         <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>710000</v>
+        <v>676000</v>
       </c>
       <c r="G299" t="n">
         <v>1</v>
@@ -31316,7 +31316,7 @@
         <v>100</v>
       </c>
       <c r="F301" t="n">
-        <v>547000</v>
+        <v>560000</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -31357,7 +31357,7 @@
         <v>90</v>
       </c>
       <c r="F302" t="n">
-        <v>975000</v>
+        <v>918000</v>
       </c>
       <c r="G302" t="n">
         <v>1</v>
@@ -31521,7 +31521,7 @@
         <v>1010</v>
       </c>
       <c r="F306" t="n">
-        <v>634000</v>
+        <v>631000</v>
       </c>
       <c r="G306" t="n">
         <v>1</v>
@@ -31726,7 +31726,7 @@
         <v>10</v>
       </c>
       <c r="F311" t="n">
-        <v>455000</v>
+        <v>442000</v>
       </c>
       <c r="G311" t="n">
         <v>1</v>
@@ -31767,7 +31767,7 @@
         <v>10</v>
       </c>
       <c r="F312" t="n">
-        <v>665000</v>
+        <v>690000</v>
       </c>
       <c r="G312" t="n">
         <v>1</v>
@@ -31808,7 +31808,7 @@
         <v>90</v>
       </c>
       <c r="F313" t="n">
-        <v>652000</v>
+        <v>666000</v>
       </c>
       <c r="G313" t="n">
         <v>1</v>
@@ -31849,7 +31849,7 @@
         <v>1010</v>
       </c>
       <c r="F314" t="n">
-        <v>649000</v>
+        <v>652000</v>
       </c>
       <c r="G314" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>60</v>
       </c>
       <c r="F315" t="n">
-        <v>740000</v>
+        <v>734000</v>
       </c>
       <c r="G315" t="n">
         <v>1</v>
@@ -31972,7 +31972,7 @@
         <v>100</v>
       </c>
       <c r="F317" t="n">
-        <v>628000</v>
+        <v>607000</v>
       </c>
       <c r="G317" t="n">
         <v>1</v>
@@ -32054,7 +32054,7 @@
         <v>50</v>
       </c>
       <c r="F319" t="n">
-        <v>265000</v>
+        <v>293000</v>
       </c>
       <c r="G319" t="n">
         <v>1</v>
@@ -32136,7 +32136,7 @@
         <v>110</v>
       </c>
       <c r="F321" t="n">
-        <v>422000</v>
+        <v>406000</v>
       </c>
       <c r="G321" t="n">
         <v>1</v>
@@ -32177,7 +32177,7 @@
         <v>60</v>
       </c>
       <c r="F322" t="n">
-        <v>580000</v>
+        <v>543000</v>
       </c>
       <c r="G322" t="n">
         <v>1</v>
@@ -32218,7 +32218,7 @@
         <v>10</v>
       </c>
       <c r="F323" t="n">
-        <v>584000</v>
+        <v>596000</v>
       </c>
       <c r="G323" t="n">
         <v>1</v>
@@ -32300,7 +32300,7 @@
         <v>1000</v>
       </c>
       <c r="F325" t="n">
-        <v>424000</v>
+        <v>429000</v>
       </c>
       <c r="G325" t="n">
         <v>1</v>
@@ -32464,7 +32464,7 @@
         <v>150</v>
       </c>
       <c r="F329" t="n">
-        <v>647000</v>
+        <v>629000</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
@@ -32546,7 +32546,7 @@
         <v>80</v>
       </c>
       <c r="F331" t="n">
-        <v>633000</v>
+        <v>618000</v>
       </c>
       <c r="G331" t="n">
         <v>1</v>
@@ -32587,7 +32587,7 @@
         <v>140</v>
       </c>
       <c r="F332" t="n">
-        <v>493000</v>
+        <v>505000</v>
       </c>
       <c r="G332" t="n">
         <v>1</v>
@@ -32669,7 +32669,7 @@
         <v>40</v>
       </c>
       <c r="F334" t="n">
-        <v>317000</v>
+        <v>334000</v>
       </c>
       <c r="G334" t="n">
         <v>1</v>
@@ -32710,7 +32710,7 @@
         <v>140</v>
       </c>
       <c r="F335" t="n">
-        <v>568000</v>
+        <v>564000</v>
       </c>
       <c r="G335" t="n">
         <v>1</v>
@@ -32792,7 +32792,7 @@
         <v>110</v>
       </c>
       <c r="F337" t="n">
-        <v>390000</v>
+        <v>393000</v>
       </c>
       <c r="G337" t="n">
         <v>1</v>
@@ -32874,7 +32874,7 @@
         <v>150</v>
       </c>
       <c r="F339" t="n">
-        <v>808000</v>
+        <v>800000</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -32915,7 +32915,7 @@
         <v>150</v>
       </c>
       <c r="F340" t="n">
-        <v>428000</v>
+        <v>440000</v>
       </c>
       <c r="G340" t="n">
         <v>1</v>
@@ -33038,7 +33038,7 @@
         <v>130</v>
       </c>
       <c r="F343" t="n">
-        <v>837000</v>
+        <v>792000</v>
       </c>
       <c r="G343" t="n">
         <v>1</v>
@@ -33161,7 +33161,7 @@
         <v>50</v>
       </c>
       <c r="F346" t="n">
-        <v>672000</v>
+        <v>645000</v>
       </c>
       <c r="G346" t="n">
         <v>1</v>
@@ -33202,7 +33202,7 @@
         <v>150</v>
       </c>
       <c r="F347" t="n">
-        <v>651000</v>
+        <v>686000</v>
       </c>
       <c r="G347" t="n">
         <v>1</v>
@@ -33284,7 +33284,7 @@
         <v>110</v>
       </c>
       <c r="F349" t="n">
-        <v>299000</v>
+        <v>311000</v>
       </c>
       <c r="G349" t="n">
         <v>1</v>
@@ -33325,7 +33325,7 @@
         <v>100</v>
       </c>
       <c r="F350" t="n">
-        <v>660000</v>
+        <v>690000</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -33500,7 +33500,7 @@
         <v>1000</v>
       </c>
       <c r="F3" t="n">
-        <v>520000</v>
+        <v>522000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -33541,7 +33541,7 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>694000</v>
+        <v>709000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -33623,7 +33623,7 @@
         <v>1000</v>
       </c>
       <c r="F6" t="n">
-        <v>942000</v>
+        <v>954000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -33664,7 +33664,7 @@
         <v>1010</v>
       </c>
       <c r="F7" t="n">
-        <v>615000</v>
+        <v>595000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -33746,7 +33746,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>703000</v>
+        <v>727000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -33787,7 +33787,7 @@
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>1112000</v>
+        <v>1091000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -33828,7 +33828,7 @@
         <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>666000</v>
+        <v>640000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -33869,7 +33869,7 @@
         <v>110</v>
       </c>
       <c r="F12" t="n">
-        <v>458000</v>
+        <v>478000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -34033,7 +34033,7 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>694000</v>
+        <v>714000</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -34074,7 +34074,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>880000</v>
+        <v>841000</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -34115,7 +34115,7 @@
         <v>140</v>
       </c>
       <c r="F18" t="n">
-        <v>935000</v>
+        <v>936000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -34197,7 +34197,7 @@
         <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>577000</v>
+        <v>634000</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -34238,7 +34238,7 @@
         <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>890000</v>
+        <v>876000</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -34279,7 +34279,7 @@
         <v>110</v>
       </c>
       <c r="F22" t="n">
-        <v>456000</v>
+        <v>467000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -34402,7 +34402,7 @@
         <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>665000</v>
+        <v>691000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -34566,7 +34566,7 @@
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>768000</v>
+        <v>779000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
         <v>1000</v>
       </c>
       <c r="F32" t="n">
-        <v>605000</v>
+        <v>603000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -34730,7 +34730,7 @@
         <v>160</v>
       </c>
       <c r="F33" t="n">
-        <v>437000</v>
+        <v>471000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -34853,7 +34853,7 @@
         <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>905000</v>
+        <v>899000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -34894,7 +34894,7 @@
         <v>40</v>
       </c>
       <c r="F37" t="n">
-        <v>698000</v>
+        <v>672000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -34976,7 +34976,7 @@
         <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>580000</v>
+        <v>552000</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -35058,7 +35058,7 @@
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>679000</v>
+        <v>675000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -35099,7 +35099,7 @@
         <v>80</v>
       </c>
       <c r="F42" t="n">
-        <v>758000</v>
+        <v>741000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>1083000</v>
+        <v>1041000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>80</v>
       </c>
       <c r="F44" t="n">
-        <v>366000</v>
+        <v>411000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -35263,7 +35263,7 @@
         <v>100</v>
       </c>
       <c r="F46" t="n">
-        <v>859000</v>
+        <v>835000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -35304,7 +35304,7 @@
         <v>150</v>
       </c>
       <c r="F47" t="n">
-        <v>446000</v>
+        <v>470000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -35345,7 +35345,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>1049000</v>
+        <v>1044000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -35386,7 +35386,7 @@
         <v>80</v>
       </c>
       <c r="F49" t="n">
-        <v>748000</v>
+        <v>730000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -35468,7 +35468,7 @@
         <v>70</v>
       </c>
       <c r="F51" t="n">
-        <v>835000</v>
+        <v>870000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -35632,7 +35632,7 @@
         <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>974000</v>
+        <v>969000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>150</v>
       </c>
       <c r="F56" t="n">
-        <v>597000</v>
+        <v>556000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -35755,7 +35755,7 @@
         <v>60</v>
       </c>
       <c r="F58" t="n">
-        <v>630000</v>
+        <v>622000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -35919,7 +35919,7 @@
         <v>90</v>
       </c>
       <c r="F62" t="n">
-        <v>643000</v>
+        <v>671000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -36001,7 +36001,7 @@
         <v>130</v>
       </c>
       <c r="F64" t="n">
-        <v>854000</v>
+        <v>878000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -36124,7 +36124,7 @@
         <v>160</v>
       </c>
       <c r="F67" t="n">
-        <v>1061000</v>
+        <v>1110000</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -36288,7 +36288,7 @@
         <v>150</v>
       </c>
       <c r="F71" t="n">
-        <v>728000</v>
+        <v>713000</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>907000</v>
+        <v>933000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -36616,7 +36616,7 @@
         <v>1000</v>
       </c>
       <c r="F79" t="n">
-        <v>366000</v>
+        <v>391000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -36657,7 +36657,7 @@
         <v>60</v>
       </c>
       <c r="F80" t="n">
-        <v>762000</v>
+        <v>734000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -36739,7 +36739,7 @@
         <v>140</v>
       </c>
       <c r="F82" t="n">
-        <v>320000</v>
+        <v>343000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -36780,7 +36780,7 @@
         <v>140</v>
       </c>
       <c r="F83" t="n">
-        <v>712000</v>
+        <v>725000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36862,7 +36862,7 @@
         <v>90</v>
       </c>
       <c r="F85" t="n">
-        <v>633000</v>
+        <v>635000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -37108,7 +37108,7 @@
         <v>80</v>
       </c>
       <c r="F91" t="n">
-        <v>757000</v>
+        <v>733000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -37149,7 +37149,7 @@
         <v>130</v>
       </c>
       <c r="F92" t="n">
-        <v>759000</v>
+        <v>775000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -37231,7 +37231,7 @@
         <v>120</v>
       </c>
       <c r="F94" t="n">
-        <v>640000</v>
+        <v>623000</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
         <v>1010</v>
       </c>
       <c r="F96" t="n">
-        <v>362000</v>
+        <v>371000</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
         <v>50</v>
       </c>
       <c r="F98" t="n">
-        <v>901000</v>
+        <v>903000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -37436,7 +37436,7 @@
         <v>80</v>
       </c>
       <c r="F99" t="n">
-        <v>689000</v>
+        <v>691000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -37559,7 +37559,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="n">
-        <v>956000</v>
+        <v>936000</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -37600,7 +37600,7 @@
         <v>80</v>
       </c>
       <c r="F103" t="n">
-        <v>843000</v>
+        <v>837000</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -37641,7 +37641,7 @@
         <v>60</v>
       </c>
       <c r="F104" t="n">
-        <v>628000</v>
+        <v>588000</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>1010</v>
       </c>
       <c r="F106" t="n">
-        <v>860000</v>
+        <v>837000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -37928,7 +37928,7 @@
         <v>40</v>
       </c>
       <c r="F111" t="n">
-        <v>772000</v>
+        <v>728000</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -38051,7 +38051,7 @@
         <v>120</v>
       </c>
       <c r="F114" t="n">
-        <v>534000</v>
+        <v>547000</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -38092,7 +38092,7 @@
         <v>150</v>
       </c>
       <c r="F115" t="n">
-        <v>785000</v>
+        <v>786000</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -38133,7 +38133,7 @@
         <v>120</v>
       </c>
       <c r="F116" t="n">
-        <v>709000</v>
+        <v>706000</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -38215,7 +38215,7 @@
         <v>140</v>
       </c>
       <c r="F118" t="n">
-        <v>955000</v>
+        <v>963000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -38297,7 +38297,7 @@
         <v>1000</v>
       </c>
       <c r="F120" t="n">
-        <v>1046000</v>
+        <v>1065000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -38338,7 +38338,7 @@
         <v>1010</v>
       </c>
       <c r="F121" t="n">
-        <v>583000</v>
+        <v>578000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -38420,7 +38420,7 @@
         <v>60</v>
       </c>
       <c r="F123" t="n">
-        <v>920000</v>
+        <v>910000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -38461,7 +38461,7 @@
         <v>50</v>
       </c>
       <c r="F124" t="n">
-        <v>766000</v>
+        <v>831000</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -38543,7 +38543,7 @@
         <v>160</v>
       </c>
       <c r="F126" t="n">
-        <v>641000</v>
+        <v>615000</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -38625,7 +38625,7 @@
         <v>40</v>
       </c>
       <c r="F128" t="n">
-        <v>612000</v>
+        <v>595000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -38707,7 +38707,7 @@
         <v>70</v>
       </c>
       <c r="F130" t="n">
-        <v>1038000</v>
+        <v>1074000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -38748,7 +38748,7 @@
         <v>90</v>
       </c>
       <c r="F131" t="n">
-        <v>767000</v>
+        <v>771000</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -38789,7 +38789,7 @@
         <v>40</v>
       </c>
       <c r="F132" t="n">
-        <v>535000</v>
+        <v>573000</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -38830,7 +38830,7 @@
         <v>100</v>
       </c>
       <c r="F133" t="n">
-        <v>667000</v>
+        <v>668000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -38912,7 +38912,7 @@
         <v>40</v>
       </c>
       <c r="F135" t="n">
-        <v>484000</v>
+        <v>563000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -38994,7 +38994,7 @@
         <v>120</v>
       </c>
       <c r="F137" t="n">
-        <v>947000</v>
+        <v>967000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -39281,7 +39281,7 @@
         <v>80</v>
       </c>
       <c r="F144" t="n">
-        <v>857000</v>
+        <v>854000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -39322,7 +39322,7 @@
         <v>100</v>
       </c>
       <c r="F145" t="n">
-        <v>661000</v>
+        <v>666000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -39445,7 +39445,7 @@
         <v>110</v>
       </c>
       <c r="F148" t="n">
-        <v>756000</v>
+        <v>788000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -39527,7 +39527,7 @@
         <v>60</v>
       </c>
       <c r="F150" t="n">
-        <v>661000</v>
+        <v>667000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -39702,7 +39702,7 @@
         <v>1010</v>
       </c>
       <c r="F4" t="n">
-        <v>726000</v>
+        <v>699000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -39743,7 +39743,7 @@
         <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>623000</v>
+        <v>625000</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -39784,7 +39784,7 @@
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>1012000</v>
+        <v>1006000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -40071,7 +40071,7 @@
         <v>130</v>
       </c>
       <c r="F13" t="n">
-        <v>594000</v>
+        <v>575000</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -40112,7 +40112,7 @@
         <v>70</v>
       </c>
       <c r="F14" t="n">
-        <v>559000</v>
+        <v>599000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -40276,7 +40276,7 @@
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>523000</v>
+        <v>515000</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>1014000</v>
+        <v>1041000</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -40440,7 +40440,7 @@
         <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>279000</v>
+        <v>325000</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -40481,7 +40481,7 @@
         <v>160</v>
       </c>
       <c r="F23" t="n">
-        <v>920000</v>
+        <v>917000</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>942000</v>
+        <v>955000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -40645,7 +40645,7 @@
         <v>1010</v>
       </c>
       <c r="F27" t="n">
-        <v>605000</v>
+        <v>595000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
         <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>791000</v>
+        <v>793000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -40891,7 +40891,7 @@
         <v>1000</v>
       </c>
       <c r="F33" t="n">
-        <v>684000</v>
+        <v>691000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -40932,7 +40932,7 @@
         <v>120</v>
       </c>
       <c r="F34" t="n">
-        <v>779000</v>
+        <v>800000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -41055,7 +41055,7 @@
         <v>30</v>
       </c>
       <c r="F37" t="n">
-        <v>687000</v>
+        <v>702000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -41219,7 +41219,7 @@
         <v>120</v>
       </c>
       <c r="F41" t="n">
-        <v>372000</v>
+        <v>375000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -41424,7 +41424,7 @@
         <v>110</v>
       </c>
       <c r="F46" t="n">
-        <v>728000</v>
+        <v>732000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -41506,7 +41506,7 @@
         <v>110</v>
       </c>
       <c r="F48" t="n">
-        <v>272000</v>
+        <v>313000</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -41547,7 +41547,7 @@
         <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>524000</v>
+        <v>583000</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -41588,7 +41588,7 @@
         <v>1000</v>
       </c>
       <c r="F50" t="n">
-        <v>579000</v>
+        <v>517000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -41629,7 +41629,7 @@
         <v>100</v>
       </c>
       <c r="F51" t="n">
-        <v>860000</v>
+        <v>873000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
